--- a/public/docs/fase1/product_backlog_ajuptel.xlsx
+++ b/public/docs/fase1/product_backlog_ajuptel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natty\Downloads\Proyecto Ingenieria\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natty\Downloads\fase1-20260519T005130Z-3-001\Fase 1 modificada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547D44F6-FBD8-4A5F-B682-BC49D322B18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F86CE-A1B3-4654-B919-3C1A227BB27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,11 @@
     <sheet name="RESUMEN DE ESTIMACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BACKLOG!$A$15:$O$141</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BACKLOG!$A$1:$O$141</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">DISTRIBUCION!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">DISTRIBUCION!$A$1:$G$25</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="389">
   <si>
     <t>Nombre del Proyecto</t>
   </si>
@@ -1023,12 +1024,6 @@
   </si>
   <si>
     <t xml:space="preserve">RESUMEN DE ESTIMACIONES POR SPRINT DEL SISTEMA DE INFORMACIÓN WEB RESPONSIVO PARA LA GESTIÓN DE DATOS DE AJUPTEL, REGIÓN CARABOBO	</t>
-  </si>
-  <si>
-    <t>Configuración de entorno. Arquitectura NestJS + Angular. 
-Base de datos MySQL. Docker. GitHub. 
-Estructura monolítica modular. 
-Estándares de desarrollo. Configuración CI/CD inicial.</t>
   </si>
   <si>
     <t>HU001 – Inicio de sesión. HU002 – Roles y permisos. HU003 – Recuperación de contraseña. 
@@ -1072,9 +1067,6 @@
 Soporte inicial.</t>
   </si>
   <si>
-    <t>BACKLOG DEL PRODUCTO SISTEMA DE INFORMACIÓN WEB RESPONSIVO PARA LA GESTIÓN DE DATOS DE AJUPTEL, REGIÓN CARABOBO</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1211,16 +1203,734 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Deseo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>gestionar la información de los asociados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Para man</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tener un registro centralizado, confiable y actualizado</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como usuario </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>operacional</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>registrar un nuevo asociado con todos sus datos personales</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>incorporarlo a la base de datos de la asociación</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consultar y visualizar la información de los asociados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>atender rápidamente las solicitudes de los agremiados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>modificar los datos de un asociado existente</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mantener la información actualizada</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Como </t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>supervisor</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quiero</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> desactivar un registro de asociado </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>gestionar casos de egreso o fallecimiento preservando el historial de información</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deseo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>gestionar la información de familiares, voceros y proveedores asociados a AJUPTEL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mantener un registro organizado y actualizado de la información relacionada con los asociados.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Como</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> usuario operacional</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>registrar un familiar asociado a un asociado principal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tener los datos de contacto y parentesco</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consultar, modificar y eliminar familiares</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mantener actualizados los datos del núcleo familiar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>registrar y administrar voceros asociados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mantener actualizada la información de representación y contacto de los asociados.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>registrar y gestionar proveedores de servicios</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mantener un directorio actualizado de aliados y servicios asociados a AJUPTEL.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deseo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>importar y exportar datos de forma masiva</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>facilitar la migración de información histórica y la generación de archivos administrativos</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como usuario </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>operacional/supervisor</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>importar datos de asociados desde archivos compatibles</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>migrar la información histórica de la Asociación</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como usuario </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>operacional/supervisor/ejecutivo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>exportar consultas y reportes en diferentes formatos</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>compartir información administrativa cuando sea requerido.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Deseo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> acceder a indicadores y reportes administrativos</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>apoyar la gestión y consulta de información de la Asociación.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ejecutivo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Quiero visualizar un dashboard con indicadores administrativos</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consultar información resumida de la Asociación.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>generar reportes administrativos sobre los asociados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consultar y compartir información administrativa de la asociación.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Deseo a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cceder a una plataforma web institucional y a un portal privado de asociados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Para c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>onsultar información institucional, acceder a servicios digitales y mantenerme informado sobre actividades y contenido relacionado con AJUPTEL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>asociado (usuario final)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>iniciar sesión en el portal de asociados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Para a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cceder de forma segura a mi información personal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>asociado</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quiero c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>onsultar mi información personal desde el portal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Para v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>erificar y mantener actualizados mis datos registrados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deseo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>administrador (Supervisor/Operacional)</t>
+      <t>escanear documentos desde el móvil y enviarlos por email</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>digitalizar trámites y evitar desplazamientos innecesarios</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>asociado o personal administrativo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>escanear o capturar documentos desde mi dispositivo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>digitalizar y registrar documentos en la plataforma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Como</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> asociado o personal administrativo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consultar los documentos almacenados en la plataforma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>acceder rápidamente al historial documental asociado a los trámites realizados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ver el historial de los documentos que he escaneado y enviado</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tener un registro digital de mis trámites y documentos</t>
     </r>
   </si>
   <si>
@@ -1234,33 +1944,21 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>gestionar la información de los asociados</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Para man</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tener un registro centralizado, confiable y actualizado</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como usuario </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>operacional</t>
+      <t>recibir asistencia inteligente y validaciones automáticas dentro de la plataforma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Para</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> facilitar el uso del sistema y mejorar la calidad de la información registrada</t>
     </r>
   </si>
   <si>
@@ -1273,7 +1971,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>registrar un nuevo asociado con todos sus datos personales</t>
+      <t>que el sistema me ayude a detectar asociados duplicados antes de crearlos</t>
     </r>
   </si>
   <si>
@@ -1286,7 +1984,21 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>incorporarlo a la base de datos de la asociación</t>
+      <t>mantener la calidad y unicidad de los datos de la asociación</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cualquier usuario (especialmente adultos mayores)</t>
     </r>
   </si>
   <si>
@@ -1296,10 +2008,11 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultar y visualizar la información de los asociados</t>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>disponer de un asistente virtual que me ayude a resolver dudas frecuentes dentro de la plataforma</t>
     </r>
   </si>
   <si>
@@ -1309,10 +2022,24 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>atender rápidamente las solicitudes de los agremiados</t>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>utilizar el sistema de forma más sencilla sin depender de manuales o asistencia externa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Como usuario</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> operacional</t>
     </r>
   </si>
   <si>
@@ -1325,7 +2052,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>modificar los datos de un asociado existente</t>
+      <t>recibir sugerencias automáticas mientras realizo búsquedas en el sistema</t>
     </r>
   </si>
   <si>
@@ -1338,8 +2065,21 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>mantener la información actualizada</t>
-    </r>
+      <t>encontrar asociados e información relacionada de forma más rápida y eficiente</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya existe suficiente información para reportes reales. </t>
+  </si>
+  <si>
+    <t>¡</t>
+  </si>
+  <si>
+    <t>Configuración de entorno. Arquitectura Laravel + Vue.js. Base de datos MySQL. Docker. GitHub. 
+Estructura monolítica modular. Estándares de desarrollo. Configuración CI/CD inicial.</t>
+  </si>
+  <si>
+    <t>Finalizada</t>
   </si>
   <si>
     <r>
@@ -1348,62 +2088,11 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>supervisor</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Quiero</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> desactivar un registro de asociado </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>gestionar casos de egreso o fallecimiento preservando el historial de información</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Deseo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>gestionar la información de familiares, voceros y proveedores asociados a AJUPTEL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mantener un registro organizado y actualizado de la información relacionada con los asociados.</t>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>usuario cualquier rol</t>
     </r>
   </si>
   <si>
@@ -1416,85 +2105,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> usuario operacional</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>registrar un familiar asociado a un asociado principal</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tener los datos de contacto y parentesco</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultar, modificar y eliminar familiares</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mantener actualizados los datos del núcleo familiar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>registrar y administrar voceros asociados</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mantener actualizada la información de representación y contacto de los asociados.</t>
+      <t xml:space="preserve"> Asociado registrado</t>
     </r>
   </si>
   <si>
@@ -1507,33 +2118,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>supervisor/usuario operacional</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>registrar y gestionar proveedores de servicios</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mantener un directorio actualizado de aliados y servicios asociados a AJUPTEL.</t>
+      <t xml:space="preserve">Ejecutivo </t>
     </r>
   </si>
   <si>
@@ -1543,114 +2128,12 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>administrador (Supervisor/Operacional)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Deseo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>importar y exportar datos de forma masiva</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>facilitar la migración de información histórica y la generación de archivos administrativos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como usuario </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>operacional/supervisor</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>importar datos de asociados desde archivos compatibles</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>migrar la información histórica de la Asociación</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como usuario </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>operacional/supervisor/ejecutivo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>exportar consultas y reportes en diferentes formatos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>compartir información administrativa cuando sea requerido.</t>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>administrador (Supervisor/
+Operacional)</t>
     </r>
   </si>
   <si>
@@ -1663,33 +2146,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>ejecutivo (Junta Directiva)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Deseo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> acceder a indicadores y reportes administrativos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>apoyar la gestión y consulta de información de la Asociación.</t>
+      <t>administrador (Supervisor/
+Operacional</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
     </r>
   </si>
   <si>
@@ -1699,101 +2166,11 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ejecutivo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Quiero visualizar un dashboard con indicadores administrativos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultar información resumida de la Asociación.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>generar reportes administrativos sobre los asociados</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultar y compartir información administrativa de la asociación.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Como público general o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> asociado registrado</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Deseo a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cceder a una plataforma web institucional y a un portal privado de asociados</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Para c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>onsultar información institucional, acceder a servicios digitales y mantenerme informado sobre actividades y contenido relacionado con AJUPTEL</t>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>asociado o usuario operacional</t>
     </r>
   </si>
   <si>
@@ -1806,91 +2183,19 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>asociado (usuario final)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>iniciar sesión en el portal de asociados</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Para a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cceder de forma segura a mi información personal</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>asociado</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Quiero c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>onsultar mi información personal desde el portal</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Para v</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>erificar y mantener actualizados mis datos registrados</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como </t>
-    </r>
-    <r>
-      <rPr>
+      <t>supervisor/ usuario operacional</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>asociado o personal administrativo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Deseo </t>
+      <t>Como</t>
     </r>
     <r>
       <rPr>
@@ -1899,279 +2204,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>escanear documentos desde el móvil y enviarlos por email</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>digitalizar trámites y evitar desplazamientos innecesarios</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>asociado o personal administrativo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>escanear o capturar documentos desde mi dispositivo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>digitalizar y registrar documentos en la plataforma</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Como</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> asociado o personal administrativo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultar los documentos almacenados en la plataforma</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>acceder rápidamente al historial documental asociado a los trámites realizados</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ver el historial de los documentos que he escaneado y enviado</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tener un registro digital de mis trámites y documentos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>usuario del sistema</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Deseo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>recibir asistencia inteligente y validaciones automáticas dentro de la plataforma</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Para</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> facilitar el uso del sistema y mejorar la calidad de la información registrada</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>que el sistema me ayude a detectar asociados duplicados antes de crearlos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mantener la calidad y unicidad de los datos de la asociación</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Como </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cualquier usuario (especialmente adultos mayores)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>disponer de un asistente virtual que me ayude a resolver dudas frecuentes dentro de la plataforma</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>utilizar el sistema de forma más sencilla sin depender de manuales o asistencia externa</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Como usuario</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> operacional</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quiero </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>recibir sugerencias automáticas mientras realizo búsquedas en el sistema</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Para </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>encontrar asociados e información relacionada de forma más rápida y eficiente</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Ya existe suficiente información para reportes reales. </t>
+      <t xml:space="preserve"> usuario cualquier rol</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2240,7 +2274,7 @@
       <b/>
       <sz val="16.5"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2269,7 +2303,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2573,7 +2607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -2660,105 +2694,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2773,6 +2708,111 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2985,15 +3025,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>60476</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2226234</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>997234</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1784047</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>90091</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3015,8 +3055,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="11652250" cy="997234"/>
+          <a:off x="60476" y="0"/>
+          <a:ext cx="13970000" cy="997234"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3267,7 +3307,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="99.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="16" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="46" customWidth="1"/>
     <col min="3" max="3" width="32.5703125" style="16" customWidth="1"/>
     <col min="4" max="4" width="18.140625" style="16" customWidth="1"/>
     <col min="5" max="5" width="19.140625" style="16" customWidth="1"/>
@@ -3285,3293 +3325,3560 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15 16384:16384" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44"/>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-    </row>
-    <row r="2" spans="1:15 16384:16384" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>302</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
+      <c r="A1" s="66"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+    </row>
+    <row r="2" spans="1:15 16384:16384" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="64" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
     </row>
     <row r="3" spans="1:15 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:15 16384:16384" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41" t="s">
+      <c r="B4" s="68"/>
+      <c r="C4" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:15 16384:16384" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:15 16384:16384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:15 16384:16384" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="41" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:15 16384:16384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:15 16384:16384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="41" t="s">
+      <c r="B9" s="68"/>
+      <c r="C9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
       <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:15 16384:16384" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="41" t="s">
+      <c r="B10" s="68"/>
+      <c r="C10" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
       <c r="I10" s="16"/>
     </row>
     <row r="11" spans="1:15 16384:16384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41" t="s">
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
       <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:15 16384:16384" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41" t="s">
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
       <c r="I12" s="16"/>
     </row>
     <row r="13" spans="1:15 16384:16384" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="67"/>
     </row>
     <row r="14" spans="1:15 16384:16384" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="71" t="s">
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="72" t="s">
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
     </row>
     <row r="15" spans="1:15 16384:16384" s="17" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="75" t="s">
+      <c r="G15" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="75" t="s">
+      <c r="H15" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="76" t="s">
+      <c r="I15" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="76" t="s">
+      <c r="J15" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="76" t="s">
+      <c r="K15" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="L15" s="76" t="s">
+      <c r="L15" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="77" t="s">
+      <c r="M15" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="N15" s="76" t="s">
+      <c r="N15" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="O15" s="77" t="s">
+      <c r="O15" s="44" t="s">
         <v>33</v>
       </c>
       <c r="XFD15" s="16"/>
     </row>
     <row r="16" spans="1:15 16384:16384" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>302</v>
+      </c>
+      <c r="D16" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="E16" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="52" t="s">
         <v>304</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="G16" s="52" t="s">
         <v>305</v>
       </c>
-      <c r="E16" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="48" t="s">
+      <c r="H16" s="53" t="s">
         <v>306</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>307</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>308</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="45" t="s">
+      <c r="J16" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="54">
         <v>5</v>
       </c>
-      <c r="L16" s="42" t="s">
+      <c r="L16" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="42">
+      <c r="M16" s="55">
         <v>1</v>
       </c>
-      <c r="N16" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O16" s="42" t="s">
-        <v>40</v>
-      </c>
+      <c r="N16" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O16" s="55"/>
     </row>
     <row r="17" spans="1:20 16384:16384" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="58"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="49"/>
+      <c r="A17" s="50"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="53"/>
       <c r="I17" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="55"/>
     </row>
     <row r="18" spans="1:20 16384:16384" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="58"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="49"/>
+      <c r="A18" s="50"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="53"/>
       <c r="I18" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="55"/>
     </row>
     <row r="19" spans="1:20 16384:16384" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="58"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="49"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="53"/>
       <c r="I19" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="55"/>
     </row>
     <row r="20" spans="1:20 16384:16384" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="58"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46" t="s">
+      <c r="A20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="H20" s="46" t="s">
-        <v>310</v>
+      <c r="F20" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>307</v>
+      </c>
+      <c r="H20" s="51" t="s">
+        <v>308</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="42" t="s">
+      <c r="J20" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="55">
         <v>8</v>
       </c>
-      <c r="L20" s="42" t="s">
+      <c r="L20" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="55">
         <v>1</v>
       </c>
-      <c r="N20" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O20" s="42" t="s">
-        <v>40</v>
-      </c>
+      <c r="N20" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O20" s="55"/>
     </row>
     <row r="21" spans="1:20 16384:16384" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="58"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
+      <c r="A21" s="50"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
       <c r="I21" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="55"/>
     </row>
     <row r="22" spans="1:20 16384:16384" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="58"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
+      <c r="A22" s="50"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
       <c r="I22" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="55"/>
     </row>
     <row r="23" spans="1:20 16384:16384" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="58"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46" t="s">
+      <c r="A23" s="50"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="48" t="s">
-        <v>306</v>
-      </c>
-      <c r="G23" s="48" t="s">
-        <v>311</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>312</v>
+      <c r="F23" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="G23" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>310</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J23" s="42" t="s">
+      <c r="J23" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="55">
         <v>2</v>
       </c>
-      <c r="L23" s="42" t="s">
+      <c r="L23" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="M23" s="42">
+      <c r="M23" s="55">
         <v>1</v>
       </c>
-      <c r="N23" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O23" s="42" t="s">
-        <v>40</v>
-      </c>
+      <c r="N23" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O23" s="55"/>
     </row>
     <row r="24" spans="1:20 16384:16384" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="58"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
+      <c r="A24" s="50"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
       <c r="I24" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="55"/>
       <c r="T24" s="17"/>
     </row>
     <row r="25" spans="1:20 16384:16384" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="58"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
       <c r="I25" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="42"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="55"/>
       <c r="XFD25" s="19"/>
     </row>
     <row r="26" spans="1:20 16384:16384" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="57" t="s">
+      <c r="A26" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="51" t="s">
+        <v>384</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>311</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>312</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="G26" s="52" t="s">
         <v>314</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="H26" s="52" t="s">
         <v>315</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G26" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="H26" s="48" t="s">
-        <v>318</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="42" t="s">
+      <c r="J26" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="42">
+      <c r="K26" s="55">
         <v>8</v>
       </c>
-      <c r="L26" s="42" t="s">
+      <c r="L26" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="M26" s="42">
+      <c r="M26" s="55">
         <v>2</v>
       </c>
-      <c r="N26" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O26" s="42" t="s">
-        <v>56</v>
-      </c>
+      <c r="N26" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O26" s="55"/>
       <c r="XFD26" s="19"/>
     </row>
     <row r="27" spans="1:20 16384:16384" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="57"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
+      <c r="A27" s="56"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
       <c r="I27" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="55"/>
       <c r="XFD27" s="19"/>
     </row>
     <row r="28" spans="1:20 16384:16384" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="57"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
+      <c r="A28" s="56"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
       <c r="I28" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="55"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="55"/>
       <c r="XFD28" s="20"/>
     </row>
     <row r="29" spans="1:20 16384:16384" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="57"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
+      <c r="A29" s="56"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
       <c r="I29" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
     </row>
     <row r="30" spans="1:20 16384:16384" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="57"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
+      <c r="A30" s="56"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
       <c r="I30" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="55"/>
     </row>
     <row r="31" spans="1:20 16384:16384" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="57"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="52" t="s">
+      <c r="A31" s="56"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="G31" s="52" t="s">
         <v>316</v>
       </c>
-      <c r="G31" s="48" t="s">
-        <v>319</v>
-      </c>
-      <c r="H31" s="48" t="s">
-        <v>320</v>
+      <c r="H31" s="52" t="s">
+        <v>317</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="J31" s="42" t="s">
+      <c r="J31" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="K31" s="42">
+      <c r="K31" s="55">
         <v>5</v>
       </c>
-      <c r="L31" s="45" t="s">
+      <c r="L31" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="M31" s="42">
+      <c r="M31" s="55">
         <v>2</v>
       </c>
-      <c r="N31" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O31" s="42" t="s">
-        <v>56</v>
-      </c>
+      <c r="N31" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O31" s="55"/>
     </row>
     <row r="32" spans="1:20 16384:16384" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="57"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
+      <c r="A32" s="56"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
       <c r="I32" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="55"/>
     </row>
     <row r="33" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="57"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
+      <c r="A33" s="56"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
       <c r="I33" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="55"/>
     </row>
     <row r="34" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="57"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="52" t="s">
+      <c r="A34" s="56"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G34" s="48" t="s">
-        <v>321</v>
-      </c>
-      <c r="H34" s="48" t="s">
-        <v>322</v>
+      <c r="F34" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="G34" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="H34" s="52" t="s">
+        <v>319</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="J34" s="45" t="s">
+      <c r="J34" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="K34" s="42">
+      <c r="K34" s="55">
         <v>3</v>
       </c>
-      <c r="L34" s="45" t="s">
+      <c r="L34" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="M34" s="42">
+      <c r="M34" s="55">
         <v>2</v>
       </c>
-      <c r="N34" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O34" s="42" t="s">
-        <v>56</v>
-      </c>
+      <c r="N34" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O34" s="55"/>
     </row>
     <row r="35" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="57"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
       <c r="I35" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J35" s="45"/>
-      <c r="K35" s="42"/>
-      <c r="L35" s="45"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="55"/>
     </row>
     <row r="36" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="57"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
+      <c r="A36" s="56"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
       <c r="I36" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="J36" s="45"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
     </row>
     <row r="37" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="57"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="52" t="s">
+      <c r="A37" s="56"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="52" t="s">
-        <v>323</v>
-      </c>
-      <c r="G37" s="48" t="s">
-        <v>324</v>
-      </c>
-      <c r="H37" s="48" t="s">
-        <v>325</v>
+      <c r="F37" s="57" t="s">
+        <v>320</v>
+      </c>
+      <c r="G37" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="H37" s="52" t="s">
+        <v>322</v>
       </c>
       <c r="I37" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="J37" s="45" t="s">
+      <c r="J37" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="K37" s="42">
+      <c r="K37" s="55">
         <v>3</v>
       </c>
-      <c r="L37" s="45" t="s">
+      <c r="L37" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="M37" s="42">
+      <c r="M37" s="55">
         <v>2</v>
       </c>
-      <c r="N37" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O37" s="42" t="s">
-        <v>71</v>
-      </c>
+      <c r="N37" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O37" s="55"/>
     </row>
     <row r="38" spans="1:15" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="57"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
+      <c r="A38" s="56"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
       <c r="I38" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="J38" s="45"/>
-      <c r="K38" s="42"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="42"/>
-      <c r="N38" s="42"/>
-      <c r="O38" s="42"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="55"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="55"/>
     </row>
     <row r="39" spans="1:15" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="57"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
+      <c r="A39" s="56"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
       <c r="I39" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="J39" s="45"/>
-      <c r="K39" s="42"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="42"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
     </row>
     <row r="40" spans="1:15" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="58" t="s">
         <v>74</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>316</v>
-      </c>
-      <c r="C40" s="48" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>323</v>
+      </c>
+      <c r="D40" s="52" t="s">
+        <v>324</v>
+      </c>
+      <c r="E40" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="G40" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="D40" s="48" t="s">
+      <c r="H40" s="52" t="s">
         <v>327</v>
-      </c>
-      <c r="E40" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="48" t="s">
-        <v>328</v>
-      </c>
-      <c r="G40" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="H40" s="48" t="s">
-        <v>330</v>
       </c>
       <c r="I40" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="J40" s="42" t="s">
+      <c r="J40" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="K40" s="42">
+      <c r="K40" s="55">
         <v>6</v>
       </c>
-      <c r="L40" s="42" t="s">
+      <c r="L40" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="M40" s="42">
+      <c r="M40" s="55">
         <v>3</v>
       </c>
-      <c r="N40" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O40" s="42" t="s">
-        <v>71</v>
-      </c>
+      <c r="N40" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O40" s="55"/>
     </row>
     <row r="41" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="56"/>
+      <c r="A41" s="58"/>
       <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
       <c r="I41" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="J41" s="42"/>
-      <c r="K41" s="42"/>
-      <c r="L41" s="42"/>
-      <c r="M41" s="42"/>
-      <c r="N41" s="42"/>
-      <c r="O41" s="42"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
     </row>
     <row r="42" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="56"/>
+      <c r="A42" s="58"/>
       <c r="B42" s="52"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
       <c r="I42" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="55"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="55"/>
     </row>
     <row r="43" spans="1:15" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="56"/>
+      <c r="A43" s="58"/>
       <c r="B43" s="52"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="52" t="s">
+      <c r="C43" s="57"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="F43" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G43" s="48" t="s">
-        <v>331</v>
-      </c>
-      <c r="H43" s="48" t="s">
-        <v>332</v>
+      <c r="F43" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="G43" s="52" t="s">
+        <v>328</v>
+      </c>
+      <c r="H43" s="52" t="s">
+        <v>329</v>
       </c>
       <c r="I43" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="J43" s="42" t="s">
+      <c r="J43" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="K43" s="42">
+      <c r="K43" s="55">
         <v>4</v>
       </c>
-      <c r="L43" s="42" t="s">
+      <c r="L43" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="M43" s="42">
+      <c r="M43" s="55">
         <v>3</v>
       </c>
-      <c r="N43" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O43" s="42" t="s">
-        <v>71</v>
-      </c>
+      <c r="N43" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O43" s="55"/>
     </row>
     <row r="44" spans="1:15" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="56"/>
+      <c r="A44" s="58"/>
       <c r="B44" s="52"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
       <c r="I44" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="J44" s="42"/>
-      <c r="K44" s="42"/>
-      <c r="L44" s="42"/>
-      <c r="M44" s="42"/>
-      <c r="N44" s="42"/>
-      <c r="O44" s="42"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="55"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="55"/>
     </row>
     <row r="45" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="56"/>
+      <c r="A45" s="58"/>
       <c r="B45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
       <c r="I45" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="42"/>
-      <c r="N45" s="42"/>
-      <c r="O45" s="42"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="55"/>
     </row>
     <row r="46" spans="1:15" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="56"/>
+      <c r="A46" s="58"/>
       <c r="B46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="52" t="s">
+      <c r="C46" s="57"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="F46" s="48" t="s">
-        <v>323</v>
-      </c>
-      <c r="G46" s="48" t="s">
-        <v>333</v>
-      </c>
-      <c r="H46" s="48" t="s">
-        <v>334</v>
+      <c r="F46" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="G46" s="52" t="s">
+        <v>330</v>
+      </c>
+      <c r="H46" s="52" t="s">
+        <v>331</v>
       </c>
       <c r="I46" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="J46" s="45" t="s">
+      <c r="J46" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="K46" s="42">
+      <c r="K46" s="55">
         <v>5</v>
       </c>
-      <c r="L46" s="42" t="s">
+      <c r="L46" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="M46" s="42">
+      <c r="M46" s="55">
         <v>3</v>
       </c>
-      <c r="N46" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O46" s="42" t="s">
-        <v>71</v>
-      </c>
+      <c r="N46" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O46" s="55"/>
     </row>
     <row r="47" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="56"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="52"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
       <c r="I47" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="J47" s="45"/>
-      <c r="K47" s="42"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="42"/>
-      <c r="N47" s="42"/>
-      <c r="O47" s="42"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="55"/>
+      <c r="M47" s="55"/>
+      <c r="N47" s="55"/>
+      <c r="O47" s="55"/>
     </row>
     <row r="48" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="56"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
       <c r="I48" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
-      <c r="M48" s="42"/>
-      <c r="N48" s="42"/>
-      <c r="O48" s="42"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="55"/>
     </row>
     <row r="49" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="56"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="52"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
       <c r="I49" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="45"/>
-      <c r="M49" s="42"/>
-      <c r="N49" s="42"/>
-      <c r="O49" s="42"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="55"/>
+      <c r="N49" s="55"/>
+      <c r="O49" s="55"/>
     </row>
     <row r="50" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="56"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
       <c r="I50" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
-      <c r="M50" s="42"/>
-      <c r="N50" s="42"/>
-      <c r="O50" s="42"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="55"/>
+      <c r="N50" s="55"/>
+      <c r="O50" s="55"/>
     </row>
     <row r="51" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="56"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="52"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
       <c r="I51" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="45"/>
-      <c r="M51" s="42"/>
-      <c r="N51" s="42"/>
-      <c r="O51" s="42"/>
+      <c r="J51" s="54"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="54"/>
+      <c r="M51" s="55"/>
+      <c r="N51" s="55"/>
+      <c r="O51" s="55"/>
     </row>
     <row r="52" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="56"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="52" t="s">
+      <c r="C52" s="57"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="F52" s="48" t="s">
-        <v>335</v>
-      </c>
-      <c r="G52" s="48" t="s">
-        <v>336</v>
-      </c>
-      <c r="H52" s="48" t="s">
-        <v>337</v>
+      <c r="F52" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="G52" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="H52" s="52" t="s">
+        <v>333</v>
       </c>
       <c r="I52" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="J52" s="42" t="s">
+      <c r="J52" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="K52" s="42">
+      <c r="K52" s="55">
         <v>4</v>
       </c>
-      <c r="L52" s="42" t="s">
+      <c r="L52" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="M52" s="42">
+      <c r="M52" s="55">
         <v>3</v>
       </c>
-      <c r="N52" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O52" s="42" t="s">
-        <v>93</v>
-      </c>
+      <c r="N52" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O52" s="55"/>
     </row>
     <row r="53" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="56"/>
+      <c r="A53" s="58"/>
       <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="52"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
       <c r="I53" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="J53" s="42"/>
-      <c r="K53" s="42"/>
-      <c r="L53" s="42"/>
-      <c r="M53" s="42"/>
-      <c r="N53" s="42"/>
-      <c r="O53" s="42"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="55"/>
+      <c r="N53" s="55"/>
+      <c r="O53" s="55"/>
     </row>
     <row r="54" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="56"/>
+      <c r="A54" s="58"/>
       <c r="B54" s="52"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
-      <c r="H54" s="52"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
       <c r="I54" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="J54" s="42"/>
-      <c r="K54" s="42"/>
-      <c r="L54" s="42"/>
-      <c r="M54" s="42"/>
-      <c r="N54" s="42"/>
-      <c r="O54" s="42"/>
+      <c r="J54" s="55"/>
+      <c r="K54" s="55"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="55"/>
+      <c r="N54" s="55"/>
+      <c r="O54" s="55"/>
     </row>
     <row r="55" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="56"/>
+      <c r="A55" s="58"/>
       <c r="B55" s="52"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
-      <c r="H55" s="52"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
       <c r="I55" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="J55" s="42"/>
-      <c r="K55" s="42"/>
-      <c r="L55" s="42"/>
-      <c r="M55" s="42"/>
-      <c r="N55" s="42"/>
-      <c r="O55" s="42"/>
+      <c r="J55" s="55"/>
+      <c r="K55" s="55"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="55"/>
+      <c r="N55" s="55"/>
+      <c r="O55" s="55"/>
     </row>
     <row r="56" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="56"/>
+      <c r="A56" s="58"/>
       <c r="B56" s="52"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="52"/>
-      <c r="H56" s="52"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
       <c r="I56" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="42"/>
-      <c r="N56" s="42"/>
-      <c r="O56" s="42"/>
+      <c r="J56" s="55"/>
+      <c r="K56" s="55"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="55"/>
+      <c r="N56" s="55"/>
+      <c r="O56" s="55"/>
     </row>
     <row r="57" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="55" t="s">
+      <c r="A57" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="48" t="s">
+      <c r="B57" s="52" t="s">
+        <v>385</v>
+      </c>
+      <c r="C57" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="D57" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="E57" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="F57" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="G57" s="52" t="s">
+        <v>337</v>
+      </c>
+      <c r="H57" s="52" t="s">
         <v>338</v>
-      </c>
-      <c r="C57" s="48" t="s">
-        <v>339</v>
-      </c>
-      <c r="D57" s="48" t="s">
-        <v>340</v>
-      </c>
-      <c r="E57" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="F57" s="48" t="s">
-        <v>341</v>
-      </c>
-      <c r="G57" s="48" t="s">
-        <v>342</v>
-      </c>
-      <c r="H57" s="48" t="s">
-        <v>343</v>
       </c>
       <c r="I57" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="J57" s="45" t="s">
+      <c r="J57" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K57" s="42">
+      <c r="K57" s="55">
         <v>10</v>
       </c>
-      <c r="L57" s="45" t="s">
+      <c r="L57" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="M57" s="42">
+      <c r="M57" s="55">
         <v>4</v>
       </c>
-      <c r="N57" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O57" s="42" t="s">
-        <v>93</v>
-      </c>
+      <c r="N57" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O57" s="55"/>
     </row>
     <row r="58" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="55"/>
-      <c r="B58" s="48"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
+      <c r="A58" s="59"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
       <c r="I58" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="J58" s="45"/>
-      <c r="K58" s="42"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="42"/>
-      <c r="N58" s="42"/>
-      <c r="O58" s="42"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="55"/>
+      <c r="L58" s="54"/>
+      <c r="M58" s="55"/>
+      <c r="N58" s="55"/>
+      <c r="O58" s="55"/>
     </row>
     <row r="59" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="55"/>
-      <c r="B59" s="48"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
+      <c r="A59" s="59"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
       <c r="I59" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J59" s="45"/>
-      <c r="K59" s="42"/>
-      <c r="L59" s="45"/>
-      <c r="M59" s="42"/>
-      <c r="N59" s="42"/>
-      <c r="O59" s="42"/>
+      <c r="J59" s="54"/>
+      <c r="K59" s="55"/>
+      <c r="L59" s="54"/>
+      <c r="M59" s="55"/>
+      <c r="N59" s="55"/>
+      <c r="O59" s="55"/>
     </row>
     <row r="60" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="55"/>
-      <c r="B60" s="48"/>
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="52"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
+      <c r="A60" s="59"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
       <c r="I60" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="J60" s="45"/>
-      <c r="K60" s="42"/>
-      <c r="L60" s="45"/>
-      <c r="M60" s="42"/>
-      <c r="N60" s="42"/>
-      <c r="O60" s="42"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="55"/>
+      <c r="L60" s="54"/>
+      <c r="M60" s="55"/>
+      <c r="N60" s="55"/>
+      <c r="O60" s="55"/>
     </row>
     <row r="61" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="55"/>
-      <c r="B61" s="48"/>
-      <c r="C61" s="48"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="52" t="s">
+      <c r="A61" s="59"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="52"/>
+      <c r="E61" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="F61" s="48" t="s">
-        <v>344</v>
-      </c>
-      <c r="G61" s="48" t="s">
-        <v>345</v>
-      </c>
-      <c r="H61" s="48" t="s">
-        <v>346</v>
+      <c r="F61" s="52" t="s">
+        <v>339</v>
+      </c>
+      <c r="G61" s="52" t="s">
+        <v>340</v>
+      </c>
+      <c r="H61" s="52" t="s">
+        <v>341</v>
       </c>
       <c r="I61" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="J61" s="45" t="s">
+      <c r="J61" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K61" s="42">
+      <c r="K61" s="55">
         <v>6</v>
       </c>
-      <c r="L61" s="45" t="s">
+      <c r="L61" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="M61" s="42">
+      <c r="M61" s="55">
         <v>4</v>
       </c>
-      <c r="N61" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O61" s="42" t="s">
-        <v>93</v>
-      </c>
+      <c r="N61" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O61" s="55"/>
     </row>
     <row r="62" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="55"/>
-      <c r="B62" s="48"/>
-      <c r="C62" s="48"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
+      <c r="A62" s="59"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="52"/>
+      <c r="G62" s="52"/>
+      <c r="H62" s="52"/>
       <c r="I62" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="J62" s="45"/>
-      <c r="K62" s="42"/>
-      <c r="L62" s="45"/>
-      <c r="M62" s="42"/>
-      <c r="N62" s="42"/>
-      <c r="O62" s="42"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="55"/>
+      <c r="L62" s="54"/>
+      <c r="M62" s="55"/>
+      <c r="N62" s="55"/>
+      <c r="O62" s="55"/>
     </row>
     <row r="63" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="55"/>
-      <c r="B63" s="48"/>
-      <c r="C63" s="48"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
+      <c r="A63" s="59"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="52"/>
+      <c r="G63" s="52"/>
+      <c r="H63" s="52"/>
       <c r="I63" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="J63" s="45"/>
-      <c r="K63" s="42"/>
-      <c r="L63" s="45"/>
-      <c r="M63" s="42"/>
-      <c r="N63" s="42"/>
-      <c r="O63" s="42"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="55"/>
+      <c r="L63" s="54"/>
+      <c r="M63" s="55"/>
+      <c r="N63" s="55"/>
+      <c r="O63" s="55"/>
     </row>
     <row r="64" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="54" t="s">
+      <c r="A64" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="B64" s="48" t="s">
-        <v>347</v>
-      </c>
-      <c r="C64" s="48" t="s">
-        <v>348</v>
-      </c>
-      <c r="D64" s="48" t="s">
-        <v>349</v>
-      </c>
-      <c r="E64" s="52" t="s">
+      <c r="B64" s="52" t="s">
+        <v>383</v>
+      </c>
+      <c r="C64" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="D64" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="E64" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="F64" s="48" t="s">
-        <v>350</v>
-      </c>
-      <c r="G64" s="48" t="s">
-        <v>351</v>
-      </c>
-      <c r="H64" s="48" t="s">
-        <v>352</v>
+      <c r="F64" s="52" t="s">
+        <v>344</v>
+      </c>
+      <c r="G64" s="52" t="s">
+        <v>345</v>
+      </c>
+      <c r="H64" s="52" t="s">
+        <v>346</v>
       </c>
       <c r="I64" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="J64" s="45" t="s">
+      <c r="J64" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K64" s="42">
+      <c r="K64" s="55">
         <v>8</v>
       </c>
-      <c r="L64" s="42" t="s">
+      <c r="L64" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="M64" s="42">
+      <c r="M64" s="55">
         <v>4</v>
       </c>
-      <c r="N64" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O64" s="42" t="s">
-        <v>113</v>
-      </c>
+      <c r="N64" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O64" s="55"/>
     </row>
     <row r="65" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="54"/>
-      <c r="B65" s="48"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
+      <c r="A65" s="60"/>
+      <c r="B65" s="52"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
+      <c r="H65" s="52"/>
       <c r="I65" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="J65" s="45"/>
-      <c r="K65" s="42"/>
-      <c r="L65" s="42"/>
-      <c r="M65" s="42"/>
-      <c r="N65" s="42"/>
-      <c r="O65" s="42"/>
+      <c r="J65" s="54"/>
+      <c r="K65" s="55"/>
+      <c r="L65" s="55"/>
+      <c r="M65" s="55"/>
+      <c r="N65" s="55"/>
+      <c r="O65" s="55"/>
     </row>
     <row r="66" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="54"/>
-      <c r="B66" s="48"/>
-      <c r="C66" s="48"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
+      <c r="A66" s="60"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="52"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="52"/>
+      <c r="G66" s="52"/>
+      <c r="H66" s="52"/>
       <c r="I66" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="J66" s="45"/>
-      <c r="K66" s="42"/>
-      <c r="L66" s="42"/>
-      <c r="M66" s="42"/>
-      <c r="N66" s="42"/>
-      <c r="O66" s="42"/>
+      <c r="J66" s="54"/>
+      <c r="K66" s="55"/>
+      <c r="L66" s="55"/>
+      <c r="M66" s="55"/>
+      <c r="N66" s="55"/>
+      <c r="O66" s="55"/>
     </row>
     <row r="67" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="54"/>
-      <c r="B67" s="48"/>
-      <c r="C67" s="48"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="52" t="s">
+      <c r="A67" s="60"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="52"/>
+      <c r="D67" s="52"/>
+      <c r="E67" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="F67" s="52" t="s">
-        <v>350</v>
-      </c>
-      <c r="G67" s="48" t="s">
-        <v>353</v>
-      </c>
-      <c r="H67" s="48" t="s">
-        <v>354</v>
+      <c r="F67" s="57" t="s">
+        <v>344</v>
+      </c>
+      <c r="G67" s="52" t="s">
+        <v>347</v>
+      </c>
+      <c r="H67" s="52" t="s">
+        <v>348</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="J67" s="45" t="s">
+      <c r="J67" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="K67" s="42">
+      <c r="K67" s="55">
         <v>7</v>
       </c>
-      <c r="L67" s="45" t="s">
+      <c r="L67" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="M67" s="42">
+      <c r="M67" s="55">
         <v>4</v>
       </c>
-      <c r="N67" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O67" s="42" t="s">
-        <v>113</v>
-      </c>
+      <c r="N67" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O67" s="55"/>
     </row>
     <row r="68" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="54"/>
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
+      <c r="A68" s="60"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="52"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="52"/>
+      <c r="H68" s="52"/>
       <c r="I68" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="J68" s="45"/>
-      <c r="K68" s="42"/>
-      <c r="L68" s="45"/>
-      <c r="M68" s="42"/>
-      <c r="N68" s="42"/>
-      <c r="O68" s="42"/>
+      <c r="J68" s="54"/>
+      <c r="K68" s="55"/>
+      <c r="L68" s="54"/>
+      <c r="M68" s="55"/>
+      <c r="N68" s="55"/>
+      <c r="O68" s="55"/>
     </row>
     <row r="69" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="54"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
+      <c r="A69" s="60"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="52"/>
+      <c r="H69" s="52"/>
       <c r="I69" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="J69" s="45"/>
-      <c r="K69" s="42"/>
-      <c r="L69" s="45"/>
-      <c r="M69" s="42"/>
-      <c r="N69" s="42"/>
-      <c r="O69" s="42"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="55"/>
+      <c r="L69" s="54"/>
+      <c r="M69" s="55"/>
+      <c r="N69" s="55"/>
+      <c r="O69" s="55"/>
     </row>
     <row r="70" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="53" t="s">
+      <c r="A70" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="B70" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="C70" s="48" t="s">
-        <v>356</v>
-      </c>
-      <c r="D70" s="48" t="s">
-        <v>357</v>
-      </c>
-      <c r="E70" s="52" t="s">
+      <c r="B70" s="52" t="s">
+        <v>382</v>
+      </c>
+      <c r="C70" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="D70" s="52" t="s">
+        <v>350</v>
+      </c>
+      <c r="E70" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="F70" s="48" t="s">
-        <v>358</v>
-      </c>
-      <c r="G70" s="48" t="s">
-        <v>359</v>
-      </c>
-      <c r="H70" s="48" t="s">
-        <v>360</v>
+      <c r="F70" s="52" t="s">
+        <v>351</v>
+      </c>
+      <c r="G70" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="H70" s="52" t="s">
+        <v>353</v>
       </c>
       <c r="I70" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="J70" s="45" t="s">
+      <c r="J70" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K70" s="42">
+      <c r="K70" s="55">
         <v>5</v>
       </c>
-      <c r="L70" s="42" t="s">
+      <c r="L70" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="M70" s="42">
+      <c r="M70" s="55">
         <v>5</v>
       </c>
-      <c r="N70" s="42" t="s">
+      <c r="N70" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="42" t="s">
-        <v>123</v>
-      </c>
+      <c r="O70" s="55"/>
     </row>
     <row r="71" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="53"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
+      <c r="A71" s="61"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
       <c r="I71" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="J71" s="45"/>
-      <c r="K71" s="42"/>
-      <c r="L71" s="42"/>
-      <c r="M71" s="42"/>
-      <c r="N71" s="42"/>
-      <c r="O71" s="42"/>
+      <c r="J71" s="54"/>
+      <c r="K71" s="55"/>
+      <c r="L71" s="55"/>
+      <c r="M71" s="55"/>
+      <c r="N71" s="55"/>
+      <c r="O71" s="55"/>
     </row>
     <row r="72" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="53"/>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
+      <c r="A72" s="61"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="52"/>
+      <c r="H72" s="52"/>
       <c r="I72" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="J72" s="45"/>
-      <c r="K72" s="42"/>
-      <c r="L72" s="42"/>
-      <c r="M72" s="42"/>
-      <c r="N72" s="42"/>
-      <c r="O72" s="42"/>
+      <c r="J72" s="54"/>
+      <c r="K72" s="55"/>
+      <c r="L72" s="55"/>
+      <c r="M72" s="55"/>
+      <c r="N72" s="55"/>
+      <c r="O72" s="55"/>
     </row>
     <row r="73" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="53"/>
-      <c r="B73" s="48"/>
-      <c r="C73" s="48"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
+      <c r="A73" s="61"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="52"/>
+      <c r="D73" s="52"/>
+      <c r="E73" s="57"/>
+      <c r="F73" s="52"/>
+      <c r="G73" s="52"/>
+      <c r="H73" s="52"/>
       <c r="I73" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="J73" s="45"/>
-      <c r="K73" s="42"/>
-      <c r="L73" s="42"/>
-      <c r="M73" s="42"/>
-      <c r="N73" s="42"/>
-      <c r="O73" s="42"/>
+      <c r="J73" s="54"/>
+      <c r="K73" s="55"/>
+      <c r="L73" s="55"/>
+      <c r="M73" s="55"/>
+      <c r="N73" s="55"/>
+      <c r="O73" s="55"/>
     </row>
     <row r="74" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="53"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
+      <c r="A74" s="61"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
       <c r="I74" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="J74" s="45"/>
-      <c r="K74" s="42"/>
-      <c r="L74" s="42"/>
-      <c r="M74" s="42"/>
-      <c r="N74" s="42"/>
-      <c r="O74" s="42"/>
+      <c r="J74" s="54"/>
+      <c r="K74" s="55"/>
+      <c r="L74" s="55"/>
+      <c r="M74" s="55"/>
+      <c r="N74" s="55"/>
+      <c r="O74" s="55"/>
     </row>
     <row r="75" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="53"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="52" t="s">
+      <c r="A75" s="61"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="F75" s="52" t="s">
-        <v>361</v>
-      </c>
-      <c r="G75" s="48" t="s">
-        <v>362</v>
-      </c>
-      <c r="H75" s="48" t="s">
-        <v>363</v>
+      <c r="F75" s="57" t="s">
+        <v>354</v>
+      </c>
+      <c r="G75" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="H75" s="52" t="s">
+        <v>356</v>
       </c>
       <c r="I75" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="J75" s="45" t="s">
+      <c r="J75" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K75" s="42">
+      <c r="K75" s="55">
         <v>4</v>
       </c>
-      <c r="L75" s="45" t="s">
+      <c r="L75" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="M75" s="42">
+      <c r="M75" s="55">
         <v>5</v>
       </c>
-      <c r="N75" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O75" s="42" t="s">
-        <v>123</v>
-      </c>
+      <c r="N75" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O75" s="55"/>
     </row>
     <row r="76" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="53"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
+      <c r="A76" s="61"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="57"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
       <c r="I76" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="J76" s="45"/>
-      <c r="K76" s="42"/>
-      <c r="L76" s="45"/>
-      <c r="M76" s="42"/>
-      <c r="N76" s="42"/>
-      <c r="O76" s="42"/>
+      <c r="J76" s="54"/>
+      <c r="K76" s="55"/>
+      <c r="L76" s="54"/>
+      <c r="M76" s="55"/>
+      <c r="N76" s="55"/>
+      <c r="O76" s="55"/>
     </row>
     <row r="77" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="53"/>
-      <c r="B77" s="48"/>
-      <c r="C77" s="48"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
+      <c r="A77" s="61"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="57"/>
+      <c r="F77" s="57"/>
+      <c r="G77" s="52"/>
+      <c r="H77" s="52"/>
       <c r="I77" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="J77" s="45"/>
-      <c r="K77" s="42"/>
-      <c r="L77" s="45"/>
-      <c r="M77" s="42"/>
-      <c r="N77" s="42"/>
-      <c r="O77" s="42"/>
+      <c r="J77" s="54"/>
+      <c r="K77" s="55"/>
+      <c r="L77" s="54"/>
+      <c r="M77" s="55"/>
+      <c r="N77" s="55"/>
+      <c r="O77" s="55"/>
     </row>
     <row r="78" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="53"/>
-      <c r="B78" s="48"/>
-      <c r="C78" s="48"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
+      <c r="A78" s="61"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="52"/>
+      <c r="H78" s="52"/>
       <c r="I78" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="J78" s="45"/>
-      <c r="K78" s="42"/>
-      <c r="L78" s="45"/>
-      <c r="M78" s="42"/>
-      <c r="N78" s="42"/>
-      <c r="O78" s="42"/>
+      <c r="J78" s="54"/>
+      <c r="K78" s="55"/>
+      <c r="L78" s="54"/>
+      <c r="M78" s="55"/>
+      <c r="N78" s="55"/>
+      <c r="O78" s="55"/>
     </row>
     <row r="79" spans="1:15 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
+      <c r="A79" s="61"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
       <c r="I79" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="J79" s="45"/>
-      <c r="K79" s="42"/>
-      <c r="L79" s="45"/>
-      <c r="M79" s="42"/>
-      <c r="N79" s="42"/>
-      <c r="O79" s="42"/>
+      <c r="J79" s="54"/>
+      <c r="K79" s="55"/>
+      <c r="L79" s="54"/>
+      <c r="M79" s="55"/>
+      <c r="N79" s="55"/>
+      <c r="O79" s="55"/>
     </row>
     <row r="80" spans="1:15 16384:16384" s="24" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="52" t="s">
+      <c r="A80" s="61"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="F80" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="G80" s="50" t="s">
+      <c r="F80" s="62" t="s">
+        <v>388</v>
+      </c>
+      <c r="G80" s="62" t="s">
         <v>136</v>
       </c>
-      <c r="H80" s="50" t="s">
+      <c r="H80" s="62" t="s">
         <v>137</v>
       </c>
       <c r="I80" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="J80" s="45" t="s">
+      <c r="J80" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="K80" s="42">
+      <c r="K80" s="55">
         <v>3</v>
       </c>
-      <c r="L80" s="45" t="s">
+      <c r="L80" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="M80" s="42">
+      <c r="M80" s="55">
         <v>5</v>
       </c>
-      <c r="N80" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O80" s="42"/>
+      <c r="N80" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O80" s="55"/>
       <c r="XFD80" s="16"/>
     </row>
     <row r="81" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="53"/>
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="50"/>
+      <c r="A81" s="61"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="52"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="62"/>
+      <c r="G81" s="62"/>
+      <c r="H81" s="62"/>
       <c r="I81" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="J81" s="45"/>
-      <c r="K81" s="42"/>
-      <c r="L81" s="45"/>
-      <c r="M81" s="42"/>
-      <c r="N81" s="42"/>
-      <c r="O81" s="42"/>
+      <c r="J81" s="54"/>
+      <c r="K81" s="55"/>
+      <c r="L81" s="54"/>
+      <c r="M81" s="55"/>
+      <c r="N81" s="55"/>
+      <c r="O81" s="55"/>
     </row>
     <row r="82" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="53"/>
-      <c r="B82" s="48"/>
-      <c r="C82" s="48"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="50"/>
+      <c r="A82" s="61"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="52"/>
+      <c r="D82" s="52"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="62"/>
+      <c r="G82" s="62"/>
+      <c r="H82" s="62"/>
       <c r="I82" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="J82" s="45"/>
-      <c r="K82" s="42"/>
-      <c r="L82" s="45"/>
-      <c r="M82" s="42"/>
-      <c r="N82" s="42"/>
-      <c r="O82" s="42"/>
+      <c r="J82" s="54"/>
+      <c r="K82" s="55"/>
+      <c r="L82" s="54"/>
+      <c r="M82" s="55"/>
+      <c r="N82" s="55"/>
+      <c r="O82" s="55"/>
     </row>
     <row r="83" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="53"/>
-      <c r="B83" s="48"/>
-      <c r="C83" s="48"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="50"/>
+      <c r="A83" s="61"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="52"/>
+      <c r="D83" s="52"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="62"/>
+      <c r="G83" s="62"/>
+      <c r="H83" s="62"/>
       <c r="I83" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="J83" s="45"/>
-      <c r="K83" s="42"/>
-      <c r="L83" s="45"/>
-      <c r="M83" s="42"/>
-      <c r="N83" s="42"/>
-      <c r="O83" s="42"/>
+      <c r="J83" s="54"/>
+      <c r="K83" s="55"/>
+      <c r="L83" s="54"/>
+      <c r="M83" s="55"/>
+      <c r="N83" s="55"/>
+      <c r="O83" s="55"/>
     </row>
     <row r="84" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="53"/>
-      <c r="B84" s="48"/>
-      <c r="C84" s="48"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
-      <c r="H84" s="50"/>
+      <c r="A84" s="61"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="62"/>
       <c r="I84" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="J84" s="45"/>
-      <c r="K84" s="42"/>
-      <c r="L84" s="45"/>
-      <c r="M84" s="42"/>
-      <c r="N84" s="42"/>
-      <c r="O84" s="42"/>
+      <c r="J84" s="54"/>
+      <c r="K84" s="55"/>
+      <c r="L84" s="54"/>
+      <c r="M84" s="55"/>
+      <c r="N84" s="55"/>
+      <c r="O84" s="55"/>
     </row>
     <row r="85" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="53"/>
-      <c r="B85" s="48"/>
-      <c r="C85" s="48"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="52" t="s">
+      <c r="A85" s="61"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="F85" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="G85" s="50" t="s">
+      <c r="F85" s="62" t="s">
+        <v>388</v>
+      </c>
+      <c r="G85" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="H85" s="50" t="s">
+      <c r="H85" s="62" t="s">
         <v>146</v>
       </c>
       <c r="I85" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="J85" s="45" t="s">
+      <c r="J85" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="K85" s="42">
+      <c r="K85" s="55">
         <v>2</v>
       </c>
-      <c r="L85" s="45" t="s">
+      <c r="L85" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="M85" s="42">
+      <c r="M85" s="55">
         <v>5</v>
       </c>
-      <c r="N85" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O85" s="42"/>
+      <c r="N85" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O85" s="55"/>
     </row>
     <row r="86" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="53"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="50"/>
+      <c r="A86" s="61"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="62"/>
+      <c r="H86" s="62"/>
       <c r="I86" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="J86" s="45"/>
-      <c r="K86" s="42"/>
-      <c r="L86" s="45"/>
-      <c r="M86" s="42"/>
-      <c r="N86" s="42"/>
-      <c r="O86" s="42"/>
+      <c r="J86" s="54"/>
+      <c r="K86" s="55"/>
+      <c r="L86" s="54"/>
+      <c r="M86" s="55"/>
+      <c r="N86" s="55"/>
+      <c r="O86" s="55"/>
     </row>
     <row r="87" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="53"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
-      <c r="H87" s="50"/>
+      <c r="A87" s="61"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="62"/>
+      <c r="G87" s="62"/>
+      <c r="H87" s="62"/>
       <c r="I87" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="J87" s="45"/>
-      <c r="K87" s="42"/>
-      <c r="L87" s="45"/>
-      <c r="M87" s="42"/>
-      <c r="N87" s="42"/>
-      <c r="O87" s="42"/>
+      <c r="J87" s="54"/>
+      <c r="K87" s="55"/>
+      <c r="L87" s="54"/>
+      <c r="M87" s="55"/>
+      <c r="N87" s="55"/>
+      <c r="O87" s="55"/>
     </row>
     <row r="88" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="53"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
-      <c r="H88" s="50"/>
+      <c r="A88" s="61"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="62"/>
+      <c r="G88" s="62"/>
+      <c r="H88" s="62"/>
       <c r="I88" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="J88" s="45"/>
-      <c r="K88" s="42"/>
-      <c r="L88" s="45"/>
-      <c r="M88" s="42"/>
-      <c r="N88" s="42"/>
-      <c r="O88" s="42"/>
+      <c r="J88" s="54"/>
+      <c r="K88" s="55"/>
+      <c r="L88" s="54"/>
+      <c r="M88" s="55"/>
+      <c r="N88" s="55"/>
+      <c r="O88" s="55"/>
     </row>
     <row r="89" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="53"/>
-      <c r="B89" s="48"/>
-      <c r="C89" s="48"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="52"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
-      <c r="H89" s="50"/>
+      <c r="A89" s="61"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="52"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="62"/>
+      <c r="G89" s="62"/>
+      <c r="H89" s="62"/>
       <c r="I89" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="J89" s="45"/>
-      <c r="K89" s="42"/>
-      <c r="L89" s="45"/>
-      <c r="M89" s="42"/>
-      <c r="N89" s="42"/>
-      <c r="O89" s="42"/>
+      <c r="J89" s="54"/>
+      <c r="K89" s="55"/>
+      <c r="L89" s="54"/>
+      <c r="M89" s="55"/>
+      <c r="N89" s="55"/>
+      <c r="O89" s="55"/>
     </row>
     <row r="90" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="53"/>
-      <c r="B90" s="48"/>
-      <c r="C90" s="48"/>
-      <c r="D90" s="48"/>
-      <c r="E90" s="52" t="s">
+      <c r="A90" s="61"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="52"/>
+      <c r="D90" s="52"/>
+      <c r="E90" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="F90" s="50" t="s">
+      <c r="F90" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="G90" s="50" t="s">
+      <c r="G90" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="H90" s="50" t="s">
+      <c r="H90" s="62" t="s">
         <v>153</v>
       </c>
       <c r="I90" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="J90" s="45" t="s">
+      <c r="J90" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K90" s="42">
+      <c r="K90" s="55">
         <v>8</v>
       </c>
-      <c r="L90" s="45" t="s">
+      <c r="L90" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="M90" s="42">
+      <c r="M90" s="55">
         <v>1</v>
       </c>
-      <c r="N90" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O90" s="42"/>
+      <c r="N90" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O90" s="55"/>
     </row>
     <row r="91" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="53"/>
-      <c r="B91" s="48"/>
-      <c r="C91" s="48"/>
-      <c r="D91" s="48"/>
-      <c r="E91" s="52"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50"/>
-      <c r="H91" s="50"/>
+      <c r="A91" s="61"/>
+      <c r="B91" s="52"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="52"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="62"/>
+      <c r="G91" s="62"/>
+      <c r="H91" s="62"/>
       <c r="I91" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="J91" s="45"/>
-      <c r="K91" s="42"/>
-      <c r="L91" s="45"/>
-      <c r="M91" s="42"/>
-      <c r="N91" s="42"/>
-      <c r="O91" s="42"/>
+      <c r="J91" s="54"/>
+      <c r="K91" s="55"/>
+      <c r="L91" s="54"/>
+      <c r="M91" s="55"/>
+      <c r="N91" s="55"/>
+      <c r="O91" s="55"/>
     </row>
     <row r="92" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="53"/>
-      <c r="B92" s="48"/>
-      <c r="C92" s="48"/>
-      <c r="D92" s="48"/>
-      <c r="E92" s="52"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="50"/>
-      <c r="H92" s="50"/>
+      <c r="A92" s="61"/>
+      <c r="B92" s="52"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="52"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="62"/>
+      <c r="G92" s="62"/>
+      <c r="H92" s="62"/>
       <c r="I92" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="J92" s="45"/>
-      <c r="K92" s="42"/>
-      <c r="L92" s="45"/>
-      <c r="M92" s="42"/>
-      <c r="N92" s="42"/>
-      <c r="O92" s="42"/>
+      <c r="J92" s="54"/>
+      <c r="K92" s="55"/>
+      <c r="L92" s="54"/>
+      <c r="M92" s="55"/>
+      <c r="N92" s="55"/>
+      <c r="O92" s="55"/>
     </row>
     <row r="93" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="53"/>
-      <c r="B93" s="48"/>
-      <c r="C93" s="48"/>
-      <c r="D93" s="48"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
-      <c r="H93" s="50"/>
+      <c r="A93" s="61"/>
+      <c r="B93" s="52"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="62"/>
+      <c r="G93" s="62"/>
+      <c r="H93" s="62"/>
       <c r="I93" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="J93" s="45"/>
-      <c r="K93" s="42"/>
-      <c r="L93" s="45"/>
-      <c r="M93" s="42"/>
-      <c r="N93" s="42"/>
-      <c r="O93" s="42"/>
+      <c r="J93" s="54"/>
+      <c r="K93" s="55"/>
+      <c r="L93" s="54"/>
+      <c r="M93" s="55"/>
+      <c r="N93" s="55"/>
+      <c r="O93" s="55"/>
     </row>
     <row r="94" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="53"/>
-      <c r="B94" s="48"/>
-      <c r="C94" s="48"/>
-      <c r="D94" s="48"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="50"/>
-      <c r="G94" s="50"/>
-      <c r="H94" s="50"/>
+      <c r="A94" s="61"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="52"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="62"/>
+      <c r="G94" s="62"/>
+      <c r="H94" s="62"/>
       <c r="I94" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="J94" s="45"/>
-      <c r="K94" s="42"/>
-      <c r="L94" s="45"/>
-      <c r="M94" s="42"/>
-      <c r="N94" s="42"/>
-      <c r="O94" s="42"/>
+      <c r="J94" s="54"/>
+      <c r="K94" s="55"/>
+      <c r="L94" s="54"/>
+      <c r="M94" s="55"/>
+      <c r="N94" s="55"/>
+      <c r="O94" s="55"/>
     </row>
     <row r="95" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="53"/>
-      <c r="B95" s="48"/>
-      <c r="C95" s="48"/>
-      <c r="D95" s="48"/>
-      <c r="E95" s="52" t="s">
+      <c r="A95" s="61"/>
+      <c r="B95" s="52"/>
+      <c r="C95" s="52"/>
+      <c r="D95" s="52"/>
+      <c r="E95" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="F95" s="50" t="s">
+      <c r="F95" s="62" t="s">
         <v>135</v>
       </c>
-      <c r="G95" s="50" t="s">
+      <c r="G95" s="62" t="s">
         <v>160</v>
       </c>
-      <c r="H95" s="50" t="s">
+      <c r="H95" s="62" t="s">
         <v>161</v>
       </c>
       <c r="I95" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J95" s="45" t="s">
+      <c r="J95" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K95" s="42">
+      <c r="K95" s="55">
         <v>5</v>
       </c>
-      <c r="L95" s="45" t="s">
+      <c r="L95" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="M95" s="42">
+      <c r="M95" s="55">
         <v>1</v>
       </c>
-      <c r="N95" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O95" s="42"/>
+      <c r="N95" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O95" s="55"/>
     </row>
     <row r="96" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="53"/>
-      <c r="B96" s="48"/>
-      <c r="C96" s="48"/>
-      <c r="D96" s="48"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50"/>
-      <c r="H96" s="50"/>
+      <c r="A96" s="61"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="52"/>
+      <c r="D96" s="52"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="62"/>
+      <c r="G96" s="62"/>
+      <c r="H96" s="62"/>
       <c r="I96" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="J96" s="45"/>
-      <c r="K96" s="42"/>
-      <c r="L96" s="45"/>
-      <c r="M96" s="42"/>
-      <c r="N96" s="42"/>
-      <c r="O96" s="42"/>
+      <c r="J96" s="54"/>
+      <c r="K96" s="55"/>
+      <c r="L96" s="54"/>
+      <c r="M96" s="55"/>
+      <c r="N96" s="55"/>
+      <c r="O96" s="55"/>
     </row>
     <row r="97" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="53"/>
-      <c r="B97" s="48"/>
-      <c r="C97" s="48"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
-      <c r="H97" s="50"/>
+      <c r="A97" s="61"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="52"/>
+      <c r="D97" s="52"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="62"/>
+      <c r="G97" s="62"/>
+      <c r="H97" s="62"/>
       <c r="I97" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J97" s="45"/>
-      <c r="K97" s="42"/>
-      <c r="L97" s="45"/>
-      <c r="M97" s="42"/>
-      <c r="N97" s="42"/>
-      <c r="O97" s="42"/>
+      <c r="J97" s="54"/>
+      <c r="K97" s="55"/>
+      <c r="L97" s="54"/>
+      <c r="M97" s="55"/>
+      <c r="N97" s="55"/>
+      <c r="O97" s="55"/>
     </row>
     <row r="98" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="53"/>
-      <c r="B98" s="48"/>
-      <c r="C98" s="48"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="50"/>
-      <c r="H98" s="50"/>
+      <c r="A98" s="61"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="52"/>
+      <c r="D98" s="52"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="62"/>
+      <c r="H98" s="62"/>
       <c r="I98" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="J98" s="45"/>
-      <c r="K98" s="42"/>
-      <c r="L98" s="45"/>
-      <c r="M98" s="42"/>
-      <c r="N98" s="42"/>
-      <c r="O98" s="42"/>
+      <c r="J98" s="54"/>
+      <c r="K98" s="55"/>
+      <c r="L98" s="54"/>
+      <c r="M98" s="55"/>
+      <c r="N98" s="55"/>
+      <c r="O98" s="55"/>
     </row>
     <row r="99" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="53"/>
-      <c r="B99" s="48"/>
-      <c r="C99" s="48"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
-      <c r="H99" s="50"/>
+      <c r="A99" s="61"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="62"/>
+      <c r="G99" s="62"/>
+      <c r="H99" s="62"/>
       <c r="I99" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="J99" s="45"/>
-      <c r="K99" s="42"/>
-      <c r="L99" s="45"/>
-      <c r="M99" s="42"/>
-      <c r="N99" s="42"/>
-      <c r="O99" s="42"/>
+      <c r="J99" s="54"/>
+      <c r="K99" s="55"/>
+      <c r="L99" s="54"/>
+      <c r="M99" s="55"/>
+      <c r="N99" s="55"/>
+      <c r="O99" s="55"/>
     </row>
     <row r="100" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="51" t="s">
+      <c r="A100" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="B100" s="46" t="s">
-        <v>364</v>
-      </c>
-      <c r="C100" s="46" t="s">
-        <v>365</v>
-      </c>
-      <c r="D100" s="46" t="s">
-        <v>366</v>
-      </c>
-      <c r="E100" s="46" t="s">
+      <c r="B100" s="51" t="s">
+        <v>386</v>
+      </c>
+      <c r="C100" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="D100" s="51" t="s">
+        <v>358</v>
+      </c>
+      <c r="E100" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="F100" s="48" t="s">
-        <v>367</v>
-      </c>
-      <c r="G100" s="48" t="s">
-        <v>368</v>
-      </c>
-      <c r="H100" s="49" t="s">
-        <v>369</v>
+      <c r="F100" s="52" t="s">
+        <v>359</v>
+      </c>
+      <c r="G100" s="52" t="s">
+        <v>360</v>
+      </c>
+      <c r="H100" s="53" t="s">
+        <v>361</v>
       </c>
       <c r="I100" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="J100" s="45" t="s">
+      <c r="J100" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K100" s="45">
+      <c r="K100" s="54">
         <v>10</v>
       </c>
-      <c r="L100" s="42" t="s">
+      <c r="L100" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="M100" s="42">
+      <c r="M100" s="55">
         <v>6</v>
       </c>
-      <c r="N100" s="42" t="s">
+      <c r="N100" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O100" s="42" t="s">
-        <v>123</v>
-      </c>
+      <c r="O100" s="55"/>
     </row>
     <row r="101" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="46"/>
-      <c r="C101" s="46"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="49"/>
+      <c r="A101" s="70"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="53"/>
       <c r="I101" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="J101" s="45"/>
-      <c r="K101" s="45"/>
-      <c r="L101" s="42"/>
-      <c r="M101" s="42"/>
-      <c r="N101" s="42"/>
-      <c r="O101" s="42"/>
+      <c r="J101" s="54"/>
+      <c r="K101" s="54"/>
+      <c r="L101" s="55"/>
+      <c r="M101" s="55"/>
+      <c r="N101" s="55"/>
+      <c r="O101" s="55"/>
     </row>
     <row r="102" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="51"/>
-      <c r="B102" s="46"/>
-      <c r="C102" s="46"/>
-      <c r="D102" s="46"/>
-      <c r="E102" s="46"/>
-      <c r="F102" s="48"/>
-      <c r="G102" s="48"/>
-      <c r="H102" s="49"/>
+      <c r="A102" s="70"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="51"/>
+      <c r="D102" s="51"/>
+      <c r="E102" s="51"/>
+      <c r="F102" s="52"/>
+      <c r="G102" s="52"/>
+      <c r="H102" s="53"/>
       <c r="I102" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="J102" s="45"/>
-      <c r="K102" s="45"/>
-      <c r="L102" s="42"/>
-      <c r="M102" s="42"/>
-      <c r="N102" s="42"/>
-      <c r="O102" s="42"/>
+      <c r="J102" s="54"/>
+      <c r="K102" s="54"/>
+      <c r="L102" s="55"/>
+      <c r="M102" s="55"/>
+      <c r="N102" s="55"/>
+      <c r="O102" s="55"/>
     </row>
     <row r="103" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="51"/>
-      <c r="B103" s="46"/>
-      <c r="C103" s="46"/>
-      <c r="D103" s="46"/>
-      <c r="E103" s="46"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="48"/>
-      <c r="H103" s="49"/>
+      <c r="A103" s="70"/>
+      <c r="B103" s="51"/>
+      <c r="C103" s="51"/>
+      <c r="D103" s="51"/>
+      <c r="E103" s="51"/>
+      <c r="F103" s="52"/>
+      <c r="G103" s="52"/>
+      <c r="H103" s="53"/>
       <c r="I103" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="J103" s="45"/>
-      <c r="K103" s="45"/>
-      <c r="L103" s="42"/>
-      <c r="M103" s="42"/>
-      <c r="N103" s="42"/>
-      <c r="O103" s="42"/>
+      <c r="J103" s="54"/>
+      <c r="K103" s="54"/>
+      <c r="L103" s="55"/>
+      <c r="M103" s="55"/>
+      <c r="N103" s="55"/>
+      <c r="O103" s="55"/>
     </row>
     <row r="104" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="51"/>
-      <c r="B104" s="46"/>
-      <c r="C104" s="46"/>
-      <c r="D104" s="46"/>
-      <c r="E104" s="46"/>
-      <c r="F104" s="48"/>
-      <c r="G104" s="48"/>
-      <c r="H104" s="49"/>
+      <c r="A104" s="70"/>
+      <c r="B104" s="51"/>
+      <c r="C104" s="51"/>
+      <c r="D104" s="51"/>
+      <c r="E104" s="51"/>
+      <c r="F104" s="52"/>
+      <c r="G104" s="52"/>
+      <c r="H104" s="53"/>
       <c r="I104" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="J104" s="45"/>
-      <c r="K104" s="45"/>
-      <c r="L104" s="42"/>
-      <c r="M104" s="42"/>
-      <c r="N104" s="42"/>
-      <c r="O104" s="42"/>
+      <c r="J104" s="54"/>
+      <c r="K104" s="54"/>
+      <c r="L104" s="55"/>
+      <c r="M104" s="55"/>
+      <c r="N104" s="55"/>
+      <c r="O104" s="55"/>
     </row>
     <row r="105" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="51"/>
-      <c r="B105" s="46"/>
-      <c r="C105" s="46"/>
-      <c r="D105" s="46"/>
-      <c r="E105" s="46"/>
-      <c r="F105" s="48"/>
-      <c r="G105" s="48"/>
-      <c r="H105" s="49"/>
+      <c r="A105" s="70"/>
+      <c r="B105" s="51"/>
+      <c r="C105" s="51"/>
+      <c r="D105" s="51"/>
+      <c r="E105" s="51"/>
+      <c r="F105" s="52"/>
+      <c r="G105" s="52"/>
+      <c r="H105" s="53"/>
       <c r="I105" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="J105" s="45"/>
-      <c r="K105" s="45"/>
-      <c r="L105" s="42"/>
-      <c r="M105" s="42"/>
-      <c r="N105" s="42"/>
-      <c r="O105" s="42"/>
+      <c r="J105" s="54"/>
+      <c r="K105" s="54"/>
+      <c r="L105" s="55"/>
+      <c r="M105" s="55"/>
+      <c r="N105" s="55"/>
+      <c r="O105" s="55"/>
     </row>
     <row r="106" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="51"/>
-      <c r="B106" s="46"/>
-      <c r="C106" s="46"/>
-      <c r="D106" s="46"/>
-      <c r="E106" s="46"/>
-      <c r="F106" s="48"/>
-      <c r="G106" s="48"/>
-      <c r="H106" s="49"/>
+      <c r="A106" s="70"/>
+      <c r="B106" s="51"/>
+      <c r="C106" s="51"/>
+      <c r="D106" s="51"/>
+      <c r="E106" s="51"/>
+      <c r="F106" s="52"/>
+      <c r="G106" s="52"/>
+      <c r="H106" s="53"/>
       <c r="I106" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="J106" s="45"/>
-      <c r="K106" s="45"/>
-      <c r="L106" s="42"/>
-      <c r="M106" s="42"/>
-      <c r="N106" s="42"/>
-      <c r="O106" s="42"/>
+      <c r="J106" s="54"/>
+      <c r="K106" s="54"/>
+      <c r="L106" s="55"/>
+      <c r="M106" s="55"/>
+      <c r="N106" s="55"/>
+      <c r="O106" s="55"/>
     </row>
     <row r="107" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="51"/>
-      <c r="B107" s="46"/>
-      <c r="C107" s="46"/>
-      <c r="D107" s="46"/>
-      <c r="E107" s="46" t="s">
+      <c r="A107" s="70"/>
+      <c r="B107" s="51"/>
+      <c r="C107" s="51"/>
+      <c r="D107" s="51"/>
+      <c r="E107" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="F107" s="46" t="s">
-        <v>370</v>
-      </c>
-      <c r="G107" s="50" t="s">
+      <c r="F107" s="51" t="s">
+        <v>362</v>
+      </c>
+      <c r="G107" s="62" t="s">
         <v>177</v>
       </c>
-      <c r="H107" s="50" t="s">
+      <c r="H107" s="62" t="s">
         <v>178</v>
       </c>
       <c r="I107" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="J107" s="42" t="s">
+      <c r="J107" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="K107" s="42">
+      <c r="K107" s="55">
         <v>5</v>
       </c>
-      <c r="L107" s="42" t="s">
+      <c r="L107" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="M107" s="42">
+      <c r="M107" s="55">
         <v>6</v>
       </c>
-      <c r="N107" s="42" t="s">
+      <c r="N107" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O107" s="42" t="s">
-        <v>123</v>
-      </c>
+      <c r="O107" s="55"/>
     </row>
     <row r="108" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="51"/>
-      <c r="B108" s="46"/>
-      <c r="C108" s="46"/>
-      <c r="D108" s="46"/>
-      <c r="E108" s="46"/>
-      <c r="F108" s="46"/>
-      <c r="G108" s="46"/>
-      <c r="H108" s="46"/>
+      <c r="A108" s="70"/>
+      <c r="B108" s="51"/>
+      <c r="C108" s="51"/>
+      <c r="D108" s="51"/>
+      <c r="E108" s="51"/>
+      <c r="F108" s="51"/>
+      <c r="G108" s="51"/>
+      <c r="H108" s="51"/>
       <c r="I108" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="J108" s="42"/>
-      <c r="K108" s="42"/>
-      <c r="L108" s="42"/>
-      <c r="M108" s="42"/>
-      <c r="N108" s="42"/>
-      <c r="O108" s="42"/>
+      <c r="J108" s="55"/>
+      <c r="K108" s="55"/>
+      <c r="L108" s="55"/>
+      <c r="M108" s="55"/>
+      <c r="N108" s="55"/>
+      <c r="O108" s="55"/>
     </row>
     <row r="109" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="51"/>
-      <c r="B109" s="46"/>
-      <c r="C109" s="46"/>
-      <c r="D109" s="46"/>
-      <c r="E109" s="46"/>
-      <c r="F109" s="46"/>
-      <c r="G109" s="46"/>
-      <c r="H109" s="46"/>
+      <c r="A109" s="70"/>
+      <c r="B109" s="51"/>
+      <c r="C109" s="51"/>
+      <c r="D109" s="51"/>
+      <c r="E109" s="51"/>
+      <c r="F109" s="51"/>
+      <c r="G109" s="51"/>
+      <c r="H109" s="51"/>
       <c r="I109" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="J109" s="42"/>
-      <c r="K109" s="42"/>
-      <c r="L109" s="42"/>
-      <c r="M109" s="42"/>
-      <c r="N109" s="42"/>
-      <c r="O109" s="42"/>
+      <c r="J109" s="55"/>
+      <c r="K109" s="55"/>
+      <c r="L109" s="55"/>
+      <c r="M109" s="55"/>
+      <c r="N109" s="55"/>
+      <c r="O109" s="55"/>
     </row>
     <row r="110" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="51"/>
-      <c r="B110" s="46"/>
-      <c r="C110" s="46"/>
-      <c r="D110" s="46"/>
-      <c r="E110" s="46"/>
-      <c r="F110" s="46"/>
-      <c r="G110" s="46"/>
-      <c r="H110" s="46"/>
+      <c r="A110" s="70"/>
+      <c r="B110" s="51"/>
+      <c r="C110" s="51"/>
+      <c r="D110" s="51"/>
+      <c r="E110" s="51"/>
+      <c r="F110" s="51"/>
+      <c r="G110" s="51"/>
+      <c r="H110" s="51"/>
       <c r="I110" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="J110" s="42"/>
-      <c r="K110" s="42"/>
-      <c r="L110" s="42"/>
-      <c r="M110" s="42"/>
-      <c r="N110" s="42"/>
-      <c r="O110" s="42"/>
+      <c r="J110" s="55"/>
+      <c r="K110" s="55"/>
+      <c r="L110" s="55"/>
+      <c r="M110" s="55"/>
+      <c r="N110" s="55"/>
+      <c r="O110" s="55"/>
     </row>
     <row r="111" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="51"/>
-      <c r="B111" s="46"/>
-      <c r="C111" s="46"/>
-      <c r="D111" s="46"/>
-      <c r="E111" s="46"/>
-      <c r="F111" s="46"/>
-      <c r="G111" s="46"/>
-      <c r="H111" s="46"/>
+      <c r="A111" s="70"/>
+      <c r="B111" s="51"/>
+      <c r="C111" s="51"/>
+      <c r="D111" s="51"/>
+      <c r="E111" s="51"/>
+      <c r="F111" s="51"/>
+      <c r="G111" s="51"/>
+      <c r="H111" s="51"/>
       <c r="I111" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="J111" s="42"/>
-      <c r="K111" s="42"/>
-      <c r="L111" s="42"/>
-      <c r="M111" s="42"/>
-      <c r="N111" s="42"/>
-      <c r="O111" s="42"/>
+      <c r="J111" s="55"/>
+      <c r="K111" s="55"/>
+      <c r="L111" s="55"/>
+      <c r="M111" s="55"/>
+      <c r="N111" s="55"/>
+      <c r="O111" s="55"/>
     </row>
     <row r="112" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="51"/>
-      <c r="B112" s="46"/>
-      <c r="C112" s="46"/>
-      <c r="D112" s="46"/>
-      <c r="E112" s="46"/>
-      <c r="F112" s="46"/>
-      <c r="G112" s="46"/>
-      <c r="H112" s="46"/>
+      <c r="A112" s="70"/>
+      <c r="B112" s="51"/>
+      <c r="C112" s="51"/>
+      <c r="D112" s="51"/>
+      <c r="E112" s="51"/>
+      <c r="F112" s="51"/>
+      <c r="G112" s="51"/>
+      <c r="H112" s="51"/>
       <c r="I112" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="J112" s="42"/>
-      <c r="K112" s="42"/>
-      <c r="L112" s="42"/>
-      <c r="M112" s="42"/>
-      <c r="N112" s="42"/>
-      <c r="O112" s="42"/>
+      <c r="J112" s="55"/>
+      <c r="K112" s="55"/>
+      <c r="L112" s="55"/>
+      <c r="M112" s="55"/>
+      <c r="N112" s="55"/>
+      <c r="O112" s="55"/>
     </row>
     <row r="113" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="51"/>
-      <c r="B113" s="46"/>
-      <c r="C113" s="46"/>
-      <c r="D113" s="46"/>
-      <c r="E113" s="46"/>
-      <c r="F113" s="46"/>
-      <c r="G113" s="46"/>
-      <c r="H113" s="46"/>
+      <c r="A113" s="70"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="51"/>
+      <c r="D113" s="51"/>
+      <c r="E113" s="51"/>
+      <c r="F113" s="51"/>
+      <c r="G113" s="51"/>
+      <c r="H113" s="51"/>
       <c r="I113" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="J113" s="42"/>
-      <c r="K113" s="42"/>
-      <c r="L113" s="42"/>
-      <c r="M113" s="42"/>
-      <c r="N113" s="42"/>
-      <c r="O113" s="42"/>
+      <c r="J113" s="55"/>
+      <c r="K113" s="55"/>
+      <c r="L113" s="55"/>
+      <c r="M113" s="55"/>
+      <c r="N113" s="55"/>
+      <c r="O113" s="55"/>
     </row>
     <row r="114" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="51"/>
-      <c r="B114" s="46"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="46"/>
-      <c r="E114" s="46" t="s">
+      <c r="A114" s="70"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="51"/>
+      <c r="D114" s="51"/>
+      <c r="E114" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="F114" s="48" t="s">
-        <v>367</v>
-      </c>
-      <c r="G114" s="48" t="s">
-        <v>371</v>
-      </c>
-      <c r="H114" s="48" t="s">
-        <v>372</v>
+      <c r="F114" s="52" t="s">
+        <v>359</v>
+      </c>
+      <c r="G114" s="52" t="s">
+        <v>363</v>
+      </c>
+      <c r="H114" s="52" t="s">
+        <v>364</v>
       </c>
       <c r="I114" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="J114" s="42" t="s">
+      <c r="J114" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="K114" s="42">
+      <c r="K114" s="55">
         <v>5</v>
       </c>
-      <c r="L114" s="42" t="s">
+      <c r="L114" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="M114" s="42">
+      <c r="M114" s="55">
         <v>6</v>
       </c>
-      <c r="N114" s="42" t="s">
+      <c r="N114" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O114" s="42"/>
+      <c r="O114" s="55"/>
     </row>
     <row r="115" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="51"/>
-      <c r="B115" s="46"/>
-      <c r="C115" s="46"/>
-      <c r="D115" s="46"/>
-      <c r="E115" s="46"/>
-      <c r="F115" s="48"/>
-      <c r="G115" s="48"/>
-      <c r="H115" s="48"/>
+      <c r="A115" s="70"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="51"/>
+      <c r="D115" s="51"/>
+      <c r="E115" s="51"/>
+      <c r="F115" s="52"/>
+      <c r="G115" s="52"/>
+      <c r="H115" s="52"/>
       <c r="I115" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="J115" s="42"/>
-      <c r="K115" s="42"/>
-      <c r="L115" s="42"/>
-      <c r="M115" s="42"/>
-      <c r="N115" s="42"/>
-      <c r="O115" s="42"/>
+      <c r="J115" s="55"/>
+      <c r="K115" s="55"/>
+      <c r="L115" s="55"/>
+      <c r="M115" s="55"/>
+      <c r="N115" s="55"/>
+      <c r="O115" s="55"/>
     </row>
     <row r="116" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="51"/>
-      <c r="B116" s="46"/>
-      <c r="C116" s="46"/>
-      <c r="D116" s="46"/>
-      <c r="E116" s="46"/>
-      <c r="F116" s="48"/>
-      <c r="G116" s="48"/>
-      <c r="H116" s="48"/>
+      <c r="A116" s="70"/>
+      <c r="B116" s="51"/>
+      <c r="C116" s="51"/>
+      <c r="D116" s="51"/>
+      <c r="E116" s="51"/>
+      <c r="F116" s="52"/>
+      <c r="G116" s="52"/>
+      <c r="H116" s="52"/>
       <c r="I116" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="J116" s="42"/>
-      <c r="K116" s="42"/>
-      <c r="L116" s="42"/>
-      <c r="M116" s="42"/>
-      <c r="N116" s="42"/>
-      <c r="O116" s="42"/>
+      <c r="J116" s="55"/>
+      <c r="K116" s="55"/>
+      <c r="L116" s="55"/>
+      <c r="M116" s="55"/>
+      <c r="N116" s="55"/>
+      <c r="O116" s="55"/>
     </row>
     <row r="117" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="51"/>
-      <c r="B117" s="46"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="46"/>
-      <c r="E117" s="46"/>
-      <c r="F117" s="48"/>
-      <c r="G117" s="48"/>
-      <c r="H117" s="48"/>
+      <c r="A117" s="70"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="51"/>
+      <c r="D117" s="51"/>
+      <c r="E117" s="51"/>
+      <c r="F117" s="52"/>
+      <c r="G117" s="52"/>
+      <c r="H117" s="52"/>
       <c r="I117" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="J117" s="42"/>
-      <c r="K117" s="42"/>
-      <c r="L117" s="42"/>
-      <c r="M117" s="42"/>
-      <c r="N117" s="42"/>
-      <c r="O117" s="42"/>
+      <c r="J117" s="55"/>
+      <c r="K117" s="55"/>
+      <c r="L117" s="55"/>
+      <c r="M117" s="55"/>
+      <c r="N117" s="55"/>
+      <c r="O117" s="55"/>
     </row>
     <row r="118" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="51"/>
-      <c r="B118" s="46"/>
-      <c r="C118" s="46"/>
-      <c r="D118" s="46"/>
-      <c r="E118" s="46"/>
-      <c r="F118" s="48"/>
-      <c r="G118" s="48"/>
-      <c r="H118" s="48"/>
+      <c r="A118" s="70"/>
+      <c r="B118" s="51"/>
+      <c r="C118" s="51"/>
+      <c r="D118" s="51"/>
+      <c r="E118" s="51"/>
+      <c r="F118" s="52"/>
+      <c r="G118" s="52"/>
+      <c r="H118" s="52"/>
       <c r="I118" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="J118" s="42"/>
-      <c r="K118" s="42"/>
-      <c r="L118" s="42"/>
-      <c r="M118" s="42"/>
-      <c r="N118" s="42"/>
-      <c r="O118" s="42"/>
+      <c r="J118" s="55"/>
+      <c r="K118" s="55"/>
+      <c r="L118" s="55"/>
+      <c r="M118" s="55"/>
+      <c r="N118" s="55"/>
+      <c r="O118" s="55"/>
     </row>
     <row r="119" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="51"/>
-      <c r="B119" s="46"/>
-      <c r="C119" s="46"/>
-      <c r="D119" s="46"/>
-      <c r="E119" s="46"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="48"/>
-      <c r="H119" s="48"/>
+      <c r="A119" s="70"/>
+      <c r="B119" s="51"/>
+      <c r="C119" s="51"/>
+      <c r="D119" s="51"/>
+      <c r="E119" s="51"/>
+      <c r="F119" s="52"/>
+      <c r="G119" s="52"/>
+      <c r="H119" s="52"/>
       <c r="I119" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="J119" s="42"/>
-      <c r="K119" s="42"/>
-      <c r="L119" s="42"/>
-      <c r="M119" s="42"/>
-      <c r="N119" s="42"/>
-      <c r="O119" s="42"/>
+      <c r="J119" s="55"/>
+      <c r="K119" s="55"/>
+      <c r="L119" s="55"/>
+      <c r="M119" s="55"/>
+      <c r="N119" s="55"/>
+      <c r="O119" s="55"/>
     </row>
     <row r="120" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="51"/>
-      <c r="B120" s="46"/>
-      <c r="C120" s="46"/>
-      <c r="D120" s="46"/>
-      <c r="E120" s="46" t="s">
+      <c r="A120" s="70"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="51"/>
+      <c r="D120" s="51"/>
+      <c r="E120" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="F120" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="G120" s="48" t="s">
-        <v>373</v>
-      </c>
-      <c r="H120" s="48" t="s">
-        <v>374</v>
+      <c r="F120" s="52" t="s">
+        <v>354</v>
+      </c>
+      <c r="G120" s="52" t="s">
+        <v>365</v>
+      </c>
+      <c r="H120" s="52" t="s">
+        <v>366</v>
       </c>
       <c r="I120" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="J120" s="42" t="s">
+      <c r="J120" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="K120" s="42">
+      <c r="K120" s="55">
         <v>5</v>
       </c>
-      <c r="L120" s="42" t="s">
+      <c r="L120" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="M120" s="42">
+      <c r="M120" s="55">
         <v>6</v>
       </c>
-      <c r="N120" s="42" t="s">
+      <c r="N120" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O120" s="42" t="s">
-        <v>123</v>
-      </c>
+      <c r="O120" s="55"/>
     </row>
     <row r="121" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="51"/>
-      <c r="B121" s="46"/>
-      <c r="C121" s="46"/>
-      <c r="D121" s="46"/>
-      <c r="E121" s="46"/>
-      <c r="F121" s="48"/>
-      <c r="G121" s="48"/>
-      <c r="H121" s="48"/>
+      <c r="A121" s="70"/>
+      <c r="B121" s="51"/>
+      <c r="C121" s="51"/>
+      <c r="D121" s="51"/>
+      <c r="E121" s="51"/>
+      <c r="F121" s="52"/>
+      <c r="G121" s="52"/>
+      <c r="H121" s="52"/>
       <c r="I121" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="J121" s="42"/>
-      <c r="K121" s="42"/>
-      <c r="L121" s="42"/>
-      <c r="M121" s="42"/>
-      <c r="N121" s="42"/>
-      <c r="O121" s="42"/>
+      <c r="J121" s="55"/>
+      <c r="K121" s="55"/>
+      <c r="L121" s="55"/>
+      <c r="M121" s="55"/>
+      <c r="N121" s="55"/>
+      <c r="O121" s="55"/>
     </row>
     <row r="122" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="51"/>
-      <c r="B122" s="46"/>
-      <c r="C122" s="46"/>
-      <c r="D122" s="46"/>
-      <c r="E122" s="46"/>
-      <c r="F122" s="48"/>
-      <c r="G122" s="48"/>
-      <c r="H122" s="48"/>
+      <c r="A122" s="70"/>
+      <c r="B122" s="51"/>
+      <c r="C122" s="51"/>
+      <c r="D122" s="51"/>
+      <c r="E122" s="51"/>
+      <c r="F122" s="52"/>
+      <c r="G122" s="52"/>
+      <c r="H122" s="52"/>
       <c r="I122" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="J122" s="42"/>
-      <c r="K122" s="42"/>
-      <c r="L122" s="42"/>
-      <c r="M122" s="42"/>
-      <c r="N122" s="42"/>
-      <c r="O122" s="42"/>
+      <c r="J122" s="55"/>
+      <c r="K122" s="55"/>
+      <c r="L122" s="55"/>
+      <c r="M122" s="55"/>
+      <c r="N122" s="55"/>
+      <c r="O122" s="55"/>
     </row>
     <row r="123" spans="1:16 16384:16384" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="51"/>
-      <c r="B123" s="46"/>
-      <c r="C123" s="46"/>
-      <c r="D123" s="46"/>
-      <c r="E123" s="46"/>
-      <c r="F123" s="48"/>
-      <c r="G123" s="48"/>
-      <c r="H123" s="48"/>
+      <c r="A123" s="70"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="51"/>
+      <c r="D123" s="51"/>
+      <c r="E123" s="51"/>
+      <c r="F123" s="52"/>
+      <c r="G123" s="52"/>
+      <c r="H123" s="52"/>
       <c r="I123" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="J123" s="42"/>
-      <c r="K123" s="42"/>
-      <c r="L123" s="42"/>
-      <c r="M123" s="42"/>
-      <c r="N123" s="42"/>
-      <c r="O123" s="42"/>
+      <c r="J123" s="55"/>
+      <c r="K123" s="55"/>
+      <c r="L123" s="55"/>
+      <c r="M123" s="55"/>
+      <c r="N123" s="55"/>
+      <c r="O123" s="55"/>
     </row>
     <row r="124" spans="1:16 16384:16384" s="26" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="47" t="s">
+      <c r="A124" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="B124" s="46" t="s">
-        <v>375</v>
-      </c>
-      <c r="C124" s="46" t="s">
-        <v>376</v>
-      </c>
-      <c r="D124" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="E124" s="46" t="s">
+      <c r="B124" s="51" t="s">
+        <v>381</v>
+      </c>
+      <c r="C124" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="D124" s="51" t="s">
+        <v>368</v>
+      </c>
+      <c r="E124" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="F124" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G124" s="48" t="s">
-        <v>378</v>
-      </c>
-      <c r="H124" s="49" t="s">
-        <v>379</v>
+      <c r="F124" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="G124" s="52" t="s">
+        <v>369</v>
+      </c>
+      <c r="H124" s="53" t="s">
+        <v>370</v>
       </c>
       <c r="I124" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="J124" s="45" t="s">
+      <c r="J124" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K124" s="45">
+      <c r="K124" s="54">
         <v>8</v>
       </c>
-      <c r="L124" s="42" t="s">
+      <c r="L124" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="M124" s="42">
+      <c r="M124" s="55">
         <v>3</v>
       </c>
-      <c r="N124" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O124" s="42" t="s">
-        <v>93</v>
-      </c>
+      <c r="N124" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O124" s="55"/>
       <c r="P124" s="25"/>
       <c r="XFD124" s="16"/>
     </row>
     <row r="125" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="47"/>
-      <c r="B125" s="46"/>
-      <c r="C125" s="46"/>
-      <c r="D125" s="46"/>
-      <c r="E125" s="46"/>
-      <c r="F125" s="48"/>
-      <c r="G125" s="48"/>
-      <c r="H125" s="49"/>
+      <c r="A125" s="63"/>
+      <c r="B125" s="51"/>
+      <c r="C125" s="51"/>
+      <c r="D125" s="51"/>
+      <c r="E125" s="51"/>
+      <c r="F125" s="52"/>
+      <c r="G125" s="52"/>
+      <c r="H125" s="53"/>
       <c r="I125" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="J125" s="45"/>
-      <c r="K125" s="45"/>
-      <c r="L125" s="42"/>
-      <c r="M125" s="42"/>
-      <c r="N125" s="42"/>
-      <c r="O125" s="42"/>
+      <c r="J125" s="54"/>
+      <c r="K125" s="54"/>
+      <c r="L125" s="55"/>
+      <c r="M125" s="55"/>
+      <c r="N125" s="55"/>
+      <c r="O125" s="55"/>
       <c r="P125" s="27"/>
       <c r="XFD125" s="16"/>
     </row>
     <row r="126" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="47"/>
-      <c r="B126" s="46"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="46"/>
-      <c r="E126" s="46"/>
-      <c r="F126" s="48"/>
-      <c r="G126" s="48"/>
-      <c r="H126" s="49"/>
+      <c r="A126" s="63"/>
+      <c r="B126" s="51"/>
+      <c r="C126" s="51"/>
+      <c r="D126" s="51"/>
+      <c r="E126" s="51"/>
+      <c r="F126" s="52"/>
+      <c r="G126" s="52"/>
+      <c r="H126" s="53"/>
       <c r="I126" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="J126" s="45"/>
-      <c r="K126" s="45"/>
-      <c r="L126" s="42"/>
-      <c r="M126" s="42"/>
-      <c r="N126" s="42"/>
-      <c r="O126" s="42"/>
+      <c r="J126" s="54"/>
+      <c r="K126" s="54"/>
+      <c r="L126" s="55"/>
+      <c r="M126" s="55"/>
+      <c r="N126" s="55"/>
+      <c r="O126" s="55"/>
       <c r="P126" s="27"/>
       <c r="XFD126" s="16"/>
     </row>
     <row r="127" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="47"/>
-      <c r="B127" s="46"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="46"/>
-      <c r="E127" s="46"/>
-      <c r="F127" s="48"/>
-      <c r="G127" s="48"/>
-      <c r="H127" s="49"/>
+      <c r="A127" s="63"/>
+      <c r="B127" s="51"/>
+      <c r="C127" s="51"/>
+      <c r="D127" s="51"/>
+      <c r="E127" s="51"/>
+      <c r="F127" s="52"/>
+      <c r="G127" s="52"/>
+      <c r="H127" s="53"/>
       <c r="I127" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="J127" s="45"/>
-      <c r="K127" s="45"/>
-      <c r="L127" s="42"/>
-      <c r="M127" s="42"/>
-      <c r="N127" s="42"/>
-      <c r="O127" s="42"/>
+      <c r="J127" s="54"/>
+      <c r="K127" s="54"/>
+      <c r="L127" s="55"/>
+      <c r="M127" s="55"/>
+      <c r="N127" s="55"/>
+      <c r="O127" s="55"/>
       <c r="P127" s="27"/>
       <c r="XFD127" s="16"/>
     </row>
     <row r="128" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="47"/>
-      <c r="B128" s="46"/>
-      <c r="C128" s="46"/>
-      <c r="D128" s="46"/>
-      <c r="E128" s="46"/>
-      <c r="F128" s="48"/>
-      <c r="G128" s="48"/>
-      <c r="H128" s="49"/>
+      <c r="A128" s="63"/>
+      <c r="B128" s="51"/>
+      <c r="C128" s="51"/>
+      <c r="D128" s="51"/>
+      <c r="E128" s="51"/>
+      <c r="F128" s="52"/>
+      <c r="G128" s="52"/>
+      <c r="H128" s="53"/>
       <c r="I128" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="J128" s="45"/>
-      <c r="K128" s="45"/>
-      <c r="L128" s="42"/>
-      <c r="M128" s="42"/>
-      <c r="N128" s="42"/>
-      <c r="O128" s="42"/>
+      <c r="J128" s="54"/>
+      <c r="K128" s="54"/>
+      <c r="L128" s="55"/>
+      <c r="M128" s="55"/>
+      <c r="N128" s="55"/>
+      <c r="O128" s="55"/>
       <c r="P128" s="27"/>
       <c r="XFD128" s="16"/>
     </row>
     <row r="129" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="47"/>
-      <c r="B129" s="46"/>
-      <c r="C129" s="46"/>
-      <c r="D129" s="46"/>
-      <c r="E129" s="46"/>
-      <c r="F129" s="48"/>
-      <c r="G129" s="48"/>
-      <c r="H129" s="49"/>
+      <c r="A129" s="63"/>
+      <c r="B129" s="51"/>
+      <c r="C129" s="51"/>
+      <c r="D129" s="51"/>
+      <c r="E129" s="51"/>
+      <c r="F129" s="52"/>
+      <c r="G129" s="52"/>
+      <c r="H129" s="53"/>
       <c r="I129" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="J129" s="45"/>
-      <c r="K129" s="45"/>
-      <c r="L129" s="42"/>
-      <c r="M129" s="42"/>
-      <c r="N129" s="42"/>
-      <c r="O129" s="42"/>
+      <c r="J129" s="54"/>
+      <c r="K129" s="54"/>
+      <c r="L129" s="55"/>
+      <c r="M129" s="55"/>
+      <c r="N129" s="55"/>
+      <c r="O129" s="55"/>
       <c r="P129" s="27"/>
       <c r="XFD129" s="16"/>
     </row>
     <row r="130" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="47"/>
-      <c r="B130" s="46"/>
-      <c r="C130" s="46"/>
-      <c r="D130" s="46"/>
-      <c r="E130" s="46" t="s">
+      <c r="A130" s="63"/>
+      <c r="B130" s="51"/>
+      <c r="C130" s="51"/>
+      <c r="D130" s="51"/>
+      <c r="E130" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="F130" s="46" t="s">
-        <v>380</v>
-      </c>
-      <c r="G130" s="46" t="s">
-        <v>381</v>
-      </c>
-      <c r="H130" s="46" t="s">
-        <v>382</v>
+      <c r="F130" s="51" t="s">
+        <v>371</v>
+      </c>
+      <c r="G130" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="H130" s="51" t="s">
+        <v>373</v>
       </c>
       <c r="I130" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="J130" s="42" t="s">
+      <c r="J130" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="K130" s="42">
+      <c r="K130" s="55">
         <v>10</v>
       </c>
-      <c r="L130" s="42" t="s">
+      <c r="L130" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="M130" s="42">
+      <c r="M130" s="55">
         <v>7</v>
       </c>
-      <c r="N130" s="42" t="s">
+      <c r="N130" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O130" s="42" t="s">
-        <v>208</v>
-      </c>
+      <c r="O130" s="55"/>
       <c r="P130" s="27"/>
       <c r="XFD130" s="16"/>
     </row>
     <row r="131" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="47"/>
-      <c r="B131" s="46"/>
-      <c r="C131" s="46"/>
-      <c r="D131" s="46"/>
-      <c r="E131" s="46"/>
-      <c r="F131" s="46"/>
-      <c r="G131" s="46"/>
-      <c r="H131" s="46"/>
+      <c r="A131" s="63"/>
+      <c r="B131" s="51"/>
+      <c r="C131" s="51"/>
+      <c r="D131" s="51"/>
+      <c r="E131" s="51"/>
+      <c r="F131" s="51"/>
+      <c r="G131" s="51"/>
+      <c r="H131" s="51"/>
       <c r="I131" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="J131" s="42"/>
-      <c r="K131" s="42"/>
-      <c r="L131" s="42"/>
-      <c r="M131" s="42"/>
-      <c r="N131" s="42"/>
-      <c r="O131" s="42"/>
+      <c r="J131" s="55"/>
+      <c r="K131" s="55"/>
+      <c r="L131" s="55"/>
+      <c r="M131" s="55"/>
+      <c r="N131" s="55"/>
+      <c r="O131" s="55"/>
       <c r="P131" s="27"/>
       <c r="XFD131" s="16"/>
     </row>
     <row r="132" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="47"/>
-      <c r="B132" s="46"/>
-      <c r="C132" s="46"/>
-      <c r="D132" s="46"/>
-      <c r="E132" s="46"/>
-      <c r="F132" s="46"/>
-      <c r="G132" s="46"/>
-      <c r="H132" s="46"/>
+      <c r="A132" s="63"/>
+      <c r="B132" s="51"/>
+      <c r="C132" s="51"/>
+      <c r="D132" s="51"/>
+      <c r="E132" s="51"/>
+      <c r="F132" s="51"/>
+      <c r="G132" s="51"/>
+      <c r="H132" s="51"/>
       <c r="I132" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="J132" s="42"/>
-      <c r="K132" s="42"/>
-      <c r="L132" s="42"/>
-      <c r="M132" s="42"/>
-      <c r="N132" s="42"/>
-      <c r="O132" s="42"/>
+      <c r="J132" s="55"/>
+      <c r="K132" s="55"/>
+      <c r="L132" s="55"/>
+      <c r="M132" s="55"/>
+      <c r="N132" s="55"/>
+      <c r="O132" s="55"/>
       <c r="P132" s="27"/>
       <c r="XFD132" s="16"/>
     </row>
     <row r="133" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="47"/>
-      <c r="B133" s="46"/>
-      <c r="C133" s="46"/>
-      <c r="D133" s="46"/>
-      <c r="E133" s="46"/>
-      <c r="F133" s="46"/>
-      <c r="G133" s="46"/>
-      <c r="H133" s="46"/>
+      <c r="A133" s="63"/>
+      <c r="B133" s="51"/>
+      <c r="C133" s="51"/>
+      <c r="D133" s="51"/>
+      <c r="E133" s="51"/>
+      <c r="F133" s="51"/>
+      <c r="G133" s="51"/>
+      <c r="H133" s="51"/>
       <c r="I133" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="J133" s="42"/>
-      <c r="K133" s="42"/>
-      <c r="L133" s="42"/>
-      <c r="M133" s="42"/>
-      <c r="N133" s="42"/>
-      <c r="O133" s="42"/>
+      <c r="J133" s="55"/>
+      <c r="K133" s="55"/>
+      <c r="L133" s="55"/>
+      <c r="M133" s="55"/>
+      <c r="N133" s="55"/>
+      <c r="O133" s="55"/>
       <c r="P133" s="27"/>
       <c r="XFD133" s="16"/>
     </row>
     <row r="134" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="47"/>
-      <c r="B134" s="46"/>
-      <c r="C134" s="46"/>
-      <c r="D134" s="46"/>
-      <c r="E134" s="46"/>
-      <c r="F134" s="46"/>
-      <c r="G134" s="46"/>
-      <c r="H134" s="46"/>
+      <c r="A134" s="63"/>
+      <c r="B134" s="51"/>
+      <c r="C134" s="51"/>
+      <c r="D134" s="51"/>
+      <c r="E134" s="51"/>
+      <c r="F134" s="51"/>
+      <c r="G134" s="51"/>
+      <c r="H134" s="51"/>
       <c r="I134" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="J134" s="42"/>
-      <c r="K134" s="42"/>
-      <c r="L134" s="42"/>
-      <c r="M134" s="42"/>
-      <c r="N134" s="42"/>
-      <c r="O134" s="42"/>
+      <c r="J134" s="55"/>
+      <c r="K134" s="55"/>
+      <c r="L134" s="55"/>
+      <c r="M134" s="55"/>
+      <c r="N134" s="55"/>
+      <c r="O134" s="55"/>
       <c r="P134" s="27"/>
       <c r="XFD134" s="16"/>
     </row>
     <row r="135" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="47"/>
-      <c r="B135" s="46"/>
-      <c r="C135" s="46"/>
-      <c r="D135" s="46"/>
-      <c r="E135" s="46"/>
-      <c r="F135" s="46"/>
-      <c r="G135" s="46"/>
-      <c r="H135" s="46"/>
+      <c r="A135" s="63"/>
+      <c r="B135" s="51"/>
+      <c r="C135" s="51"/>
+      <c r="D135" s="51"/>
+      <c r="E135" s="51"/>
+      <c r="F135" s="51"/>
+      <c r="G135" s="51"/>
+      <c r="H135" s="51"/>
       <c r="I135" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="J135" s="42"/>
-      <c r="K135" s="42"/>
-      <c r="L135" s="42"/>
-      <c r="M135" s="42"/>
-      <c r="N135" s="42"/>
-      <c r="O135" s="42"/>
+      <c r="J135" s="55"/>
+      <c r="K135" s="55"/>
+      <c r="L135" s="55"/>
+      <c r="M135" s="55"/>
+      <c r="N135" s="55"/>
+      <c r="O135" s="55"/>
       <c r="P135" s="27"/>
       <c r="XFD135" s="16"/>
     </row>
     <row r="136" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="47"/>
-      <c r="B136" s="46"/>
-      <c r="C136" s="46"/>
-      <c r="D136" s="46"/>
-      <c r="E136" s="46" t="s">
+      <c r="A136" s="63"/>
+      <c r="B136" s="51"/>
+      <c r="C136" s="51"/>
+      <c r="D136" s="51"/>
+      <c r="E136" s="51" t="s">
         <v>214</v>
       </c>
-      <c r="F136" s="48" t="s">
-        <v>383</v>
-      </c>
-      <c r="G136" s="48" t="s">
-        <v>384</v>
-      </c>
-      <c r="H136" s="48" t="s">
-        <v>385</v>
+      <c r="F136" s="52" t="s">
+        <v>374</v>
+      </c>
+      <c r="G136" s="52" t="s">
+        <v>375</v>
+      </c>
+      <c r="H136" s="52" t="s">
+        <v>376</v>
       </c>
       <c r="I136" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="J136" s="42" t="s">
+      <c r="J136" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="K136" s="42">
+      <c r="K136" s="55">
         <v>5</v>
       </c>
-      <c r="L136" s="42" t="s">
+      <c r="L136" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="M136" s="42">
+      <c r="M136" s="55">
         <v>2</v>
       </c>
-      <c r="N136" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="O136" s="42" t="s">
-        <v>208</v>
-      </c>
+      <c r="N136" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="O136" s="55"/>
       <c r="P136" s="27"/>
       <c r="XFD136" s="16"/>
     </row>
     <row r="137" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="47"/>
-      <c r="B137" s="46"/>
-      <c r="C137" s="46"/>
-      <c r="D137" s="46"/>
-      <c r="E137" s="46"/>
-      <c r="F137" s="48"/>
-      <c r="G137" s="48"/>
-      <c r="H137" s="48"/>
+      <c r="A137" s="63"/>
+      <c r="B137" s="51"/>
+      <c r="C137" s="51"/>
+      <c r="D137" s="51"/>
+      <c r="E137" s="51"/>
+      <c r="F137" s="52"/>
+      <c r="G137" s="52"/>
+      <c r="H137" s="52"/>
       <c r="I137" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="J137" s="42"/>
-      <c r="K137" s="42"/>
-      <c r="L137" s="42"/>
-      <c r="M137" s="42"/>
-      <c r="N137" s="42"/>
-      <c r="O137" s="42"/>
+      <c r="J137" s="55"/>
+      <c r="K137" s="55"/>
+      <c r="L137" s="55"/>
+      <c r="M137" s="55"/>
+      <c r="N137" s="55"/>
+      <c r="O137" s="55"/>
       <c r="P137" s="27"/>
       <c r="XFD137" s="16"/>
     </row>
     <row r="138" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="47"/>
-      <c r="B138" s="46"/>
-      <c r="C138" s="46"/>
-      <c r="D138" s="46"/>
-      <c r="E138" s="46"/>
-      <c r="F138" s="48"/>
-      <c r="G138" s="48"/>
-      <c r="H138" s="48"/>
+      <c r="A138" s="63"/>
+      <c r="B138" s="51"/>
+      <c r="C138" s="51"/>
+      <c r="D138" s="51"/>
+      <c r="E138" s="51"/>
+      <c r="F138" s="52"/>
+      <c r="G138" s="52"/>
+      <c r="H138" s="52"/>
       <c r="I138" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="J138" s="42"/>
-      <c r="K138" s="42"/>
-      <c r="L138" s="42"/>
-      <c r="M138" s="42"/>
-      <c r="N138" s="42"/>
-      <c r="O138" s="42"/>
+      <c r="J138" s="55"/>
+      <c r="K138" s="55"/>
+      <c r="L138" s="55"/>
+      <c r="M138" s="55"/>
+      <c r="N138" s="55"/>
+      <c r="O138" s="55"/>
       <c r="P138" s="27"/>
       <c r="XFD138" s="16"/>
     </row>
     <row r="139" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="47"/>
-      <c r="B139" s="46"/>
-      <c r="C139" s="46"/>
-      <c r="D139" s="46"/>
-      <c r="E139" s="46"/>
-      <c r="F139" s="48"/>
-      <c r="G139" s="48"/>
-      <c r="H139" s="48"/>
+      <c r="A139" s="63"/>
+      <c r="B139" s="51"/>
+      <c r="C139" s="51"/>
+      <c r="D139" s="51"/>
+      <c r="E139" s="51"/>
+      <c r="F139" s="52"/>
+      <c r="G139" s="52"/>
+      <c r="H139" s="52"/>
       <c r="I139" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="J139" s="42"/>
-      <c r="K139" s="42"/>
-      <c r="L139" s="42"/>
-      <c r="M139" s="42"/>
-      <c r="N139" s="42"/>
-      <c r="O139" s="42"/>
+      <c r="J139" s="55"/>
+      <c r="K139" s="55"/>
+      <c r="L139" s="55"/>
+      <c r="M139" s="55"/>
+      <c r="N139" s="55"/>
+      <c r="O139" s="55"/>
       <c r="P139" s="27"/>
       <c r="XFD139" s="16"/>
     </row>
     <row r="140" spans="1:16 16384:16384" s="28" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="47"/>
-      <c r="B140" s="46"/>
-      <c r="C140" s="46"/>
-      <c r="D140" s="46"/>
-      <c r="E140" s="46"/>
-      <c r="F140" s="48"/>
-      <c r="G140" s="48"/>
-      <c r="H140" s="48"/>
+      <c r="A140" s="63"/>
+      <c r="B140" s="51"/>
+      <c r="C140" s="51"/>
+      <c r="D140" s="51"/>
+      <c r="E140" s="51"/>
+      <c r="F140" s="52"/>
+      <c r="G140" s="52"/>
+      <c r="H140" s="52"/>
       <c r="I140" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="J140" s="42"/>
-      <c r="K140" s="42"/>
-      <c r="L140" s="42"/>
-      <c r="M140" s="42"/>
-      <c r="N140" s="42"/>
-      <c r="O140" s="42"/>
+      <c r="J140" s="55"/>
+      <c r="K140" s="55"/>
+      <c r="L140" s="55"/>
+      <c r="M140" s="55"/>
+      <c r="N140" s="55"/>
+      <c r="O140" s="55"/>
       <c r="P140" s="27"/>
       <c r="XFD140" s="16"/>
     </row>
     <row r="141" spans="1:16 16384:16384" s="30" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="47"/>
-      <c r="B141" s="46"/>
-      <c r="C141" s="46"/>
-      <c r="D141" s="46"/>
-      <c r="E141" s="46"/>
-      <c r="F141" s="48"/>
-      <c r="G141" s="48"/>
-      <c r="H141" s="48"/>
+      <c r="A141" s="63"/>
+      <c r="B141" s="51"/>
+      <c r="C141" s="51"/>
+      <c r="D141" s="51"/>
+      <c r="E141" s="51"/>
+      <c r="F141" s="52"/>
+      <c r="G141" s="52"/>
+      <c r="H141" s="52"/>
       <c r="I141" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="J141" s="42"/>
-      <c r="K141" s="42"/>
-      <c r="L141" s="42"/>
-      <c r="M141" s="42"/>
-      <c r="N141" s="42"/>
-      <c r="O141" s="42"/>
+      <c r="J141" s="55"/>
+      <c r="K141" s="55"/>
+      <c r="L141" s="55"/>
+      <c r="M141" s="55"/>
+      <c r="N141" s="55"/>
+      <c r="O141" s="55"/>
       <c r="P141" s="29"/>
       <c r="XFD141" s="16"/>
     </row>
   </sheetData>
+  <autoFilter ref="A15:O141" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="336">
+    <mergeCell ref="F130:F135"/>
+    <mergeCell ref="G130:G135"/>
+    <mergeCell ref="H130:H135"/>
+    <mergeCell ref="J130:J135"/>
+    <mergeCell ref="K130:K135"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F120:F123"/>
+    <mergeCell ref="G120:G123"/>
+    <mergeCell ref="H120:H123"/>
+    <mergeCell ref="J120:J123"/>
+    <mergeCell ref="K120:K123"/>
+    <mergeCell ref="E107:E113"/>
+    <mergeCell ref="F107:F113"/>
+    <mergeCell ref="G107:G113"/>
+    <mergeCell ref="H107:H113"/>
+    <mergeCell ref="J107:J113"/>
+    <mergeCell ref="A100:A123"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="K124:K129"/>
+    <mergeCell ref="L124:L129"/>
+    <mergeCell ref="M124:M129"/>
+    <mergeCell ref="N124:N129"/>
+    <mergeCell ref="O124:O129"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="K114:K119"/>
+    <mergeCell ref="L114:L119"/>
+    <mergeCell ref="M114:M119"/>
+    <mergeCell ref="N114:N119"/>
+    <mergeCell ref="O114:O119"/>
+    <mergeCell ref="E120:E123"/>
+    <mergeCell ref="L130:L135"/>
+    <mergeCell ref="M130:M135"/>
+    <mergeCell ref="N130:N135"/>
+    <mergeCell ref="O130:O135"/>
+    <mergeCell ref="A124:A141"/>
+    <mergeCell ref="B124:B141"/>
+    <mergeCell ref="C124:C141"/>
+    <mergeCell ref="D124:D141"/>
+    <mergeCell ref="E124:E129"/>
+    <mergeCell ref="F124:F129"/>
+    <mergeCell ref="G124:G129"/>
+    <mergeCell ref="H124:H129"/>
+    <mergeCell ref="J124:J129"/>
+    <mergeCell ref="E136:E141"/>
+    <mergeCell ref="F136:F141"/>
+    <mergeCell ref="G136:G141"/>
+    <mergeCell ref="H136:H141"/>
+    <mergeCell ref="J136:J141"/>
+    <mergeCell ref="K136:K141"/>
+    <mergeCell ref="L136:L141"/>
+    <mergeCell ref="M136:M141"/>
+    <mergeCell ref="N136:N141"/>
+    <mergeCell ref="O136:O141"/>
+    <mergeCell ref="E130:E135"/>
+    <mergeCell ref="L120:L123"/>
+    <mergeCell ref="M120:M123"/>
+    <mergeCell ref="N120:N123"/>
+    <mergeCell ref="O120:O123"/>
+    <mergeCell ref="K100:K106"/>
+    <mergeCell ref="L100:L106"/>
+    <mergeCell ref="M100:M106"/>
+    <mergeCell ref="N100:N106"/>
+    <mergeCell ref="O100:O106"/>
+    <mergeCell ref="K107:K113"/>
+    <mergeCell ref="L107:L113"/>
+    <mergeCell ref="M107:M113"/>
+    <mergeCell ref="N107:N113"/>
+    <mergeCell ref="O107:O113"/>
+    <mergeCell ref="B100:B123"/>
+    <mergeCell ref="C100:C123"/>
+    <mergeCell ref="D100:D123"/>
+    <mergeCell ref="E100:E106"/>
+    <mergeCell ref="F100:F106"/>
+    <mergeCell ref="G100:G106"/>
+    <mergeCell ref="H100:H106"/>
+    <mergeCell ref="J100:J106"/>
+    <mergeCell ref="E114:E119"/>
+    <mergeCell ref="F114:F119"/>
+    <mergeCell ref="G114:G119"/>
+    <mergeCell ref="H114:H119"/>
+    <mergeCell ref="J114:J119"/>
+    <mergeCell ref="K90:K94"/>
+    <mergeCell ref="L90:L94"/>
+    <mergeCell ref="M90:M94"/>
+    <mergeCell ref="N90:N94"/>
+    <mergeCell ref="O90:O94"/>
+    <mergeCell ref="E95:E99"/>
+    <mergeCell ref="F95:F99"/>
+    <mergeCell ref="G95:G99"/>
+    <mergeCell ref="H95:H99"/>
+    <mergeCell ref="J95:J99"/>
+    <mergeCell ref="K95:K99"/>
+    <mergeCell ref="L95:L99"/>
+    <mergeCell ref="M95:M99"/>
+    <mergeCell ref="N95:N99"/>
+    <mergeCell ref="O95:O99"/>
+    <mergeCell ref="K80:K84"/>
+    <mergeCell ref="L80:L84"/>
+    <mergeCell ref="M80:M84"/>
+    <mergeCell ref="N80:N84"/>
+    <mergeCell ref="O80:O84"/>
+    <mergeCell ref="E85:E89"/>
+    <mergeCell ref="F85:F89"/>
+    <mergeCell ref="G85:G89"/>
+    <mergeCell ref="H85:H89"/>
+    <mergeCell ref="J85:J89"/>
+    <mergeCell ref="K85:K89"/>
+    <mergeCell ref="L85:L89"/>
+    <mergeCell ref="M85:M89"/>
+    <mergeCell ref="N85:N89"/>
+    <mergeCell ref="O85:O89"/>
+    <mergeCell ref="K70:K74"/>
+    <mergeCell ref="L70:L74"/>
+    <mergeCell ref="M70:M74"/>
+    <mergeCell ref="N70:N74"/>
+    <mergeCell ref="O70:O74"/>
+    <mergeCell ref="E75:E79"/>
+    <mergeCell ref="F75:F79"/>
+    <mergeCell ref="G75:G79"/>
+    <mergeCell ref="H75:H79"/>
+    <mergeCell ref="J75:J79"/>
+    <mergeCell ref="K75:K79"/>
+    <mergeCell ref="L75:L79"/>
+    <mergeCell ref="M75:M79"/>
+    <mergeCell ref="N75:N79"/>
+    <mergeCell ref="O75:O79"/>
+    <mergeCell ref="A70:A99"/>
+    <mergeCell ref="B70:B99"/>
+    <mergeCell ref="C70:C99"/>
+    <mergeCell ref="D70:D99"/>
+    <mergeCell ref="E70:E74"/>
+    <mergeCell ref="F70:F74"/>
+    <mergeCell ref="G70:G74"/>
+    <mergeCell ref="H70:H74"/>
+    <mergeCell ref="J70:J74"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="E90:E94"/>
+    <mergeCell ref="F90:F94"/>
+    <mergeCell ref="G90:G94"/>
+    <mergeCell ref="H90:H94"/>
+    <mergeCell ref="J90:J94"/>
+    <mergeCell ref="K64:K66"/>
+    <mergeCell ref="L64:L66"/>
+    <mergeCell ref="M64:M66"/>
+    <mergeCell ref="N64:N66"/>
+    <mergeCell ref="O64:O66"/>
+    <mergeCell ref="E67:E69"/>
+    <mergeCell ref="F67:F69"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="H67:H69"/>
+    <mergeCell ref="J67:J69"/>
+    <mergeCell ref="K67:K69"/>
+    <mergeCell ref="L67:L69"/>
+    <mergeCell ref="M67:M69"/>
+    <mergeCell ref="N67:N69"/>
+    <mergeCell ref="O67:O69"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="C64:C69"/>
+    <mergeCell ref="D64:D69"/>
+    <mergeCell ref="E64:E66"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="H64:H66"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="K57:K60"/>
+    <mergeCell ref="L57:L60"/>
+    <mergeCell ref="M57:M60"/>
+    <mergeCell ref="N57:N60"/>
+    <mergeCell ref="O57:O60"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="H61:H63"/>
+    <mergeCell ref="J61:J63"/>
+    <mergeCell ref="K61:K63"/>
+    <mergeCell ref="L61:L63"/>
+    <mergeCell ref="M61:M63"/>
+    <mergeCell ref="N61:N63"/>
+    <mergeCell ref="O61:O63"/>
+    <mergeCell ref="A57:A63"/>
+    <mergeCell ref="B57:B63"/>
+    <mergeCell ref="C57:C63"/>
+    <mergeCell ref="D57:D63"/>
+    <mergeCell ref="E57:E60"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="H57:H60"/>
+    <mergeCell ref="J57:J60"/>
+    <mergeCell ref="K46:K51"/>
+    <mergeCell ref="L46:L51"/>
+    <mergeCell ref="M46:M51"/>
+    <mergeCell ref="N46:N51"/>
+    <mergeCell ref="O46:O51"/>
+    <mergeCell ref="E52:E56"/>
+    <mergeCell ref="F52:F56"/>
+    <mergeCell ref="G52:G56"/>
+    <mergeCell ref="H52:H56"/>
+    <mergeCell ref="J52:J56"/>
+    <mergeCell ref="K52:K56"/>
+    <mergeCell ref="L52:L56"/>
+    <mergeCell ref="M52:M56"/>
+    <mergeCell ref="N52:N56"/>
+    <mergeCell ref="O52:O56"/>
+    <mergeCell ref="K40:K42"/>
+    <mergeCell ref="L40:L42"/>
+    <mergeCell ref="M40:M42"/>
+    <mergeCell ref="N40:N42"/>
+    <mergeCell ref="O40:O42"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="H43:H45"/>
+    <mergeCell ref="J43:J45"/>
+    <mergeCell ref="K43:K45"/>
+    <mergeCell ref="L43:L45"/>
+    <mergeCell ref="M43:M45"/>
+    <mergeCell ref="N43:N45"/>
+    <mergeCell ref="O43:O45"/>
+    <mergeCell ref="A40:A56"/>
+    <mergeCell ref="B40:B56"/>
+    <mergeCell ref="C40:C56"/>
+    <mergeCell ref="D40:D56"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="G46:G51"/>
+    <mergeCell ref="H46:H51"/>
+    <mergeCell ref="J46:J51"/>
+    <mergeCell ref="K34:K36"/>
+    <mergeCell ref="L34:L36"/>
+    <mergeCell ref="M34:M36"/>
+    <mergeCell ref="N34:N36"/>
+    <mergeCell ref="O34:O36"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="K37:K39"/>
+    <mergeCell ref="L37:L39"/>
+    <mergeCell ref="M37:M39"/>
+    <mergeCell ref="N37:N39"/>
+    <mergeCell ref="O37:O39"/>
+    <mergeCell ref="K26:K30"/>
+    <mergeCell ref="L26:L30"/>
+    <mergeCell ref="M26:M30"/>
+    <mergeCell ref="N26:N30"/>
+    <mergeCell ref="O26:O30"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="K31:K33"/>
+    <mergeCell ref="L31:L33"/>
+    <mergeCell ref="M31:M33"/>
+    <mergeCell ref="N31:N33"/>
+    <mergeCell ref="O31:O33"/>
+    <mergeCell ref="A26:A39"/>
+    <mergeCell ref="B26:B39"/>
+    <mergeCell ref="C26:C39"/>
+    <mergeCell ref="D26:D39"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="F26:F30"/>
+    <mergeCell ref="G26:G30"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="J26:J30"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="H34:H36"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="M20:M22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="O20:O22"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="J23:J25"/>
+    <mergeCell ref="K23:K25"/>
+    <mergeCell ref="L23:L25"/>
+    <mergeCell ref="M23:M25"/>
+    <mergeCell ref="N23:N25"/>
+    <mergeCell ref="O23:O25"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="E14:H14"/>
     <mergeCell ref="I14:O14"/>
@@ -6596,326 +6903,14 @@
     <mergeCell ref="J20:J22"/>
     <mergeCell ref="K20:K22"/>
     <mergeCell ref="L20:L22"/>
-    <mergeCell ref="M20:M22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="O20:O22"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="J23:J25"/>
-    <mergeCell ref="K23:K25"/>
-    <mergeCell ref="L23:L25"/>
-    <mergeCell ref="M23:M25"/>
-    <mergeCell ref="N23:N25"/>
-    <mergeCell ref="O23:O25"/>
-    <mergeCell ref="A26:A39"/>
-    <mergeCell ref="B26:B39"/>
-    <mergeCell ref="C26:C39"/>
-    <mergeCell ref="D26:D39"/>
-    <mergeCell ref="E26:E30"/>
-    <mergeCell ref="F26:F30"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="J26:J30"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="H34:H36"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="K26:K30"/>
-    <mergeCell ref="L26:L30"/>
-    <mergeCell ref="M26:M30"/>
-    <mergeCell ref="N26:N30"/>
-    <mergeCell ref="O26:O30"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="K31:K33"/>
-    <mergeCell ref="L31:L33"/>
-    <mergeCell ref="M31:M33"/>
-    <mergeCell ref="N31:N33"/>
-    <mergeCell ref="O31:O33"/>
-    <mergeCell ref="K34:K36"/>
-    <mergeCell ref="L34:L36"/>
-    <mergeCell ref="M34:M36"/>
-    <mergeCell ref="N34:N36"/>
-    <mergeCell ref="O34:O36"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="H37:H39"/>
-    <mergeCell ref="J37:J39"/>
-    <mergeCell ref="K37:K39"/>
-    <mergeCell ref="L37:L39"/>
-    <mergeCell ref="M37:M39"/>
-    <mergeCell ref="N37:N39"/>
-    <mergeCell ref="O37:O39"/>
-    <mergeCell ref="A40:A56"/>
-    <mergeCell ref="B40:B56"/>
-    <mergeCell ref="C40:C56"/>
-    <mergeCell ref="D40:D56"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="G46:G51"/>
-    <mergeCell ref="H46:H51"/>
-    <mergeCell ref="J46:J51"/>
-    <mergeCell ref="K40:K42"/>
-    <mergeCell ref="L40:L42"/>
-    <mergeCell ref="M40:M42"/>
-    <mergeCell ref="N40:N42"/>
-    <mergeCell ref="O40:O42"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="H43:H45"/>
-    <mergeCell ref="J43:J45"/>
-    <mergeCell ref="K43:K45"/>
-    <mergeCell ref="L43:L45"/>
-    <mergeCell ref="M43:M45"/>
-    <mergeCell ref="N43:N45"/>
-    <mergeCell ref="O43:O45"/>
-    <mergeCell ref="K46:K51"/>
-    <mergeCell ref="L46:L51"/>
-    <mergeCell ref="M46:M51"/>
-    <mergeCell ref="N46:N51"/>
-    <mergeCell ref="O46:O51"/>
-    <mergeCell ref="E52:E56"/>
-    <mergeCell ref="F52:F56"/>
-    <mergeCell ref="G52:G56"/>
-    <mergeCell ref="H52:H56"/>
-    <mergeCell ref="J52:J56"/>
-    <mergeCell ref="K52:K56"/>
-    <mergeCell ref="L52:L56"/>
-    <mergeCell ref="M52:M56"/>
-    <mergeCell ref="N52:N56"/>
-    <mergeCell ref="O52:O56"/>
-    <mergeCell ref="A57:A63"/>
-    <mergeCell ref="B57:B63"/>
-    <mergeCell ref="C57:C63"/>
-    <mergeCell ref="D57:D63"/>
-    <mergeCell ref="E57:E60"/>
-    <mergeCell ref="F57:F60"/>
-    <mergeCell ref="G57:G60"/>
-    <mergeCell ref="H57:H60"/>
-    <mergeCell ref="J57:J60"/>
-    <mergeCell ref="K57:K60"/>
-    <mergeCell ref="L57:L60"/>
-    <mergeCell ref="M57:M60"/>
-    <mergeCell ref="N57:N60"/>
-    <mergeCell ref="O57:O60"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="F61:F63"/>
-    <mergeCell ref="G61:G63"/>
-    <mergeCell ref="H61:H63"/>
-    <mergeCell ref="J61:J63"/>
-    <mergeCell ref="K61:K63"/>
-    <mergeCell ref="L61:L63"/>
-    <mergeCell ref="M61:M63"/>
-    <mergeCell ref="N61:N63"/>
-    <mergeCell ref="O61:O63"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="B64:B69"/>
-    <mergeCell ref="C64:C69"/>
-    <mergeCell ref="D64:D69"/>
-    <mergeCell ref="E64:E66"/>
-    <mergeCell ref="F64:F66"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="H64:H66"/>
-    <mergeCell ref="J64:J66"/>
-    <mergeCell ref="K64:K66"/>
-    <mergeCell ref="L64:L66"/>
-    <mergeCell ref="M64:M66"/>
-    <mergeCell ref="N64:N66"/>
-    <mergeCell ref="O64:O66"/>
-    <mergeCell ref="E67:E69"/>
-    <mergeCell ref="F67:F69"/>
-    <mergeCell ref="G67:G69"/>
-    <mergeCell ref="H67:H69"/>
-    <mergeCell ref="J67:J69"/>
-    <mergeCell ref="K67:K69"/>
-    <mergeCell ref="L67:L69"/>
-    <mergeCell ref="M67:M69"/>
-    <mergeCell ref="N67:N69"/>
-    <mergeCell ref="O67:O69"/>
-    <mergeCell ref="A70:A99"/>
-    <mergeCell ref="B70:B99"/>
-    <mergeCell ref="C70:C99"/>
-    <mergeCell ref="D70:D99"/>
-    <mergeCell ref="E70:E74"/>
-    <mergeCell ref="F70:F74"/>
-    <mergeCell ref="G70:G74"/>
-    <mergeCell ref="H70:H74"/>
-    <mergeCell ref="J70:J74"/>
-    <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="E90:E94"/>
-    <mergeCell ref="F90:F94"/>
-    <mergeCell ref="G90:G94"/>
-    <mergeCell ref="H90:H94"/>
-    <mergeCell ref="J90:J94"/>
-    <mergeCell ref="K70:K74"/>
-    <mergeCell ref="L70:L74"/>
-    <mergeCell ref="M70:M74"/>
-    <mergeCell ref="N70:N74"/>
-    <mergeCell ref="O70:O74"/>
-    <mergeCell ref="E75:E79"/>
-    <mergeCell ref="F75:F79"/>
-    <mergeCell ref="G75:G79"/>
-    <mergeCell ref="H75:H79"/>
-    <mergeCell ref="J75:J79"/>
-    <mergeCell ref="K75:K79"/>
-    <mergeCell ref="L75:L79"/>
-    <mergeCell ref="M75:M79"/>
-    <mergeCell ref="N75:N79"/>
-    <mergeCell ref="O75:O79"/>
-    <mergeCell ref="K80:K84"/>
-    <mergeCell ref="L80:L84"/>
-    <mergeCell ref="M80:M84"/>
-    <mergeCell ref="N80:N84"/>
-    <mergeCell ref="O80:O84"/>
-    <mergeCell ref="E85:E89"/>
-    <mergeCell ref="F85:F89"/>
-    <mergeCell ref="G85:G89"/>
-    <mergeCell ref="H85:H89"/>
-    <mergeCell ref="J85:J89"/>
-    <mergeCell ref="K85:K89"/>
-    <mergeCell ref="L85:L89"/>
-    <mergeCell ref="M85:M89"/>
-    <mergeCell ref="N85:N89"/>
-    <mergeCell ref="O85:O89"/>
-    <mergeCell ref="K90:K94"/>
-    <mergeCell ref="L90:L94"/>
-    <mergeCell ref="M90:M94"/>
-    <mergeCell ref="N90:N94"/>
-    <mergeCell ref="O90:O94"/>
-    <mergeCell ref="E95:E99"/>
-    <mergeCell ref="F95:F99"/>
-    <mergeCell ref="G95:G99"/>
-    <mergeCell ref="H95:H99"/>
-    <mergeCell ref="J95:J99"/>
-    <mergeCell ref="K95:K99"/>
-    <mergeCell ref="L95:L99"/>
-    <mergeCell ref="M95:M99"/>
-    <mergeCell ref="N95:N99"/>
-    <mergeCell ref="O95:O99"/>
-    <mergeCell ref="A100:A123"/>
-    <mergeCell ref="B100:B123"/>
-    <mergeCell ref="C100:C123"/>
-    <mergeCell ref="D100:D123"/>
-    <mergeCell ref="E100:E106"/>
-    <mergeCell ref="F100:F106"/>
-    <mergeCell ref="G100:G106"/>
-    <mergeCell ref="H100:H106"/>
-    <mergeCell ref="J100:J106"/>
-    <mergeCell ref="E114:E119"/>
-    <mergeCell ref="F114:F119"/>
-    <mergeCell ref="G114:G119"/>
-    <mergeCell ref="H114:H119"/>
-    <mergeCell ref="J114:J119"/>
-    <mergeCell ref="K100:K106"/>
-    <mergeCell ref="L100:L106"/>
-    <mergeCell ref="M100:M106"/>
-    <mergeCell ref="N100:N106"/>
-    <mergeCell ref="O100:O106"/>
-    <mergeCell ref="E107:E113"/>
-    <mergeCell ref="F107:F113"/>
-    <mergeCell ref="G107:G113"/>
-    <mergeCell ref="H107:H113"/>
-    <mergeCell ref="J107:J113"/>
-    <mergeCell ref="K107:K113"/>
-    <mergeCell ref="L107:L113"/>
-    <mergeCell ref="M107:M113"/>
-    <mergeCell ref="N107:N113"/>
-    <mergeCell ref="O107:O113"/>
-    <mergeCell ref="K114:K119"/>
-    <mergeCell ref="L114:L119"/>
-    <mergeCell ref="M114:M119"/>
-    <mergeCell ref="N114:N119"/>
-    <mergeCell ref="O114:O119"/>
-    <mergeCell ref="E120:E123"/>
-    <mergeCell ref="F120:F123"/>
-    <mergeCell ref="G120:G123"/>
-    <mergeCell ref="H120:H123"/>
-    <mergeCell ref="J120:J123"/>
-    <mergeCell ref="K120:K123"/>
-    <mergeCell ref="L120:L123"/>
-    <mergeCell ref="M120:M123"/>
-    <mergeCell ref="N120:N123"/>
-    <mergeCell ref="O120:O123"/>
-    <mergeCell ref="L130:L135"/>
-    <mergeCell ref="M130:M135"/>
-    <mergeCell ref="N130:N135"/>
-    <mergeCell ref="O130:O135"/>
-    <mergeCell ref="A124:A141"/>
-    <mergeCell ref="B124:B141"/>
-    <mergeCell ref="C124:C141"/>
-    <mergeCell ref="D124:D141"/>
-    <mergeCell ref="E124:E129"/>
-    <mergeCell ref="F124:F129"/>
-    <mergeCell ref="G124:G129"/>
-    <mergeCell ref="H124:H129"/>
-    <mergeCell ref="J124:J129"/>
-    <mergeCell ref="E136:E141"/>
-    <mergeCell ref="F136:F141"/>
-    <mergeCell ref="G136:G141"/>
-    <mergeCell ref="H136:H141"/>
-    <mergeCell ref="J136:J141"/>
-    <mergeCell ref="K136:K141"/>
-    <mergeCell ref="L136:L141"/>
-    <mergeCell ref="M136:M141"/>
-    <mergeCell ref="N136:N141"/>
-    <mergeCell ref="O136:O141"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="K124:K129"/>
-    <mergeCell ref="L124:L129"/>
-    <mergeCell ref="M124:M129"/>
-    <mergeCell ref="N124:N129"/>
-    <mergeCell ref="O124:O129"/>
-    <mergeCell ref="E130:E135"/>
-    <mergeCell ref="F130:F135"/>
-    <mergeCell ref="G130:G135"/>
-    <mergeCell ref="H130:H135"/>
-    <mergeCell ref="J130:J135"/>
-    <mergeCell ref="K130:K135"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup scale="23" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="6" manualBreakCount="6">
-    <brk id="39" max="16383" man="1"/>
+    <brk id="14" max="14" man="1"/>
     <brk id="56" max="16383" man="1"/>
     <brk id="63" max="16383" man="1"/>
-    <brk id="79" max="16383" man="1"/>
+    <brk id="78" max="14" man="1"/>
     <brk id="99" max="16383" man="1"/>
     <brk id="119" max="16383" man="1"/>
   </rowBreaks>
@@ -6928,7 +6923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.42578125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="35" customWidth="1"/>
@@ -6941,372 +6936,373 @@
     <col min="8" max="16384" width="8.42578125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60"/>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-    </row>
-    <row r="2" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+    <row r="1" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+    </row>
+    <row r="3" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="73" t="s">
         <v>289</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-    </row>
-    <row r="3" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" s="33" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+    </row>
+    <row r="4" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B5" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-    </row>
-    <row r="5" spans="1:7" s="33" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="61" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="61" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
+        <v>2</v>
+      </c>
+      <c r="B6" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
     </row>
     <row r="7" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+    </row>
+    <row r="8" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B8" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-    </row>
-    <row r="8" spans="1:7" s="33" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
     </row>
     <row r="9" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
     </row>
     <row r="10" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+    </row>
+    <row r="11" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B11" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-    </row>
-    <row r="11" spans="1:7" s="33" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
     </row>
     <row r="12" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+    </row>
+    <row r="13" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="61" t="s">
+      <c r="B13" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-    </row>
-    <row r="14" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="62" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+      <c r="B15" s="71"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+    </row>
+    <row r="16" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B16" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C16" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D16" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E16" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F16" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G16" s="37" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
+    <row r="17" spans="1:7" ht="126" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B17" s="38" t="s">
         <v>229</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>235</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>295</v>
+        <v>379</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="144" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="126" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="162" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>386</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A22" s="38" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="144" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>230</v>
       </c>
       <c r="D24" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="252" x14ac:dyDescent="0.25">
+      <c r="A25" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="D25" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E25" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="F24" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="G24" s="39"/>
+      <c r="F25" s="39" t="s">
+        <v>300</v>
+      </c>
+      <c r="G25" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B13:D13"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup scale="40" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -7325,16 +7321,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67"/>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
+      <c r="A1" s="76"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="77" t="s">
         <v>293</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -7343,82 +7339,82 @@
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="63"/>
+      <c r="C4" s="75"/>
     </row>
     <row r="5" spans="1:3" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="63"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="63"/>
+      <c r="C6" s="75"/>
     </row>
     <row r="7" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="63"/>
+      <c r="C7" s="75"/>
     </row>
     <row r="8" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="63"/>
+      <c r="C8" s="75"/>
     </row>
     <row r="9" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="63"/>
+      <c r="C9" s="75"/>
     </row>
     <row r="10" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="66"/>
+      <c r="C10" s="79"/>
     </row>
     <row r="11" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="63"/>
+      <c r="C11" s="75"/>
     </row>
     <row r="12" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="63"/>
+      <c r="C12" s="75"/>
     </row>
     <row r="13" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11"/>
@@ -7565,18 +7561,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/docs/fase1/product_backlog_ajuptel.xlsx
+++ b/public/docs/fase1/product_backlog_ajuptel.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Nombre del Proyecto</t>
   </si>
   <si>
-    <t xml:space="preserve">Sistema de Información Web Responsivo para la Gestión de Datos de AJUPTEL Carabobo</t>
+    <t xml:space="preserve">Sistema de Información Web Responsivo con Integración de Portal Informativo y Chatbot Interactivo con Inteligencia Artificial orientado a la optimización de la gestión de datos de la Asociación Civil (AJUPTEL), Región Carabobo. </t>
   </si>
   <si>
     <t xml:space="preserve">Dueño del Producto</t>
@@ -143,6 +143,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -152,6 +153,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">administrador (Supervisor)</t>
     </r>
@@ -164,6 +166,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo </t>
     </r>
@@ -173,6 +176,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">gestionar la autenticación y control de acceso al sistema</t>
     </r>
@@ -185,6 +189,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -194,6 +199,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">garantizar la seguridad de los datos de los asociados</t>
     </r>
@@ -208,6 +214,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -216,6 +223,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">usuario (cualquier rol)</t>
     </r>
@@ -227,6 +235,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -235,6 +244,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">iniciar sesión con usuario y contraseña</t>
     </r>
@@ -246,6 +256,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -254,6 +265,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">acceder al sistema de forma segura</t>
     </r>
@@ -290,6 +302,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -299,6 +312,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">gestionar los roles y permisos de los usuarios</t>
     </r>
@@ -311,6 +325,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -320,6 +335,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">controlar el acceso a las funcionalidades del sistema</t>
     </r>
@@ -343,6 +359,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -351,6 +368,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">cerrar sesión de forma segura</t>
     </r>
@@ -362,6 +380,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -370,6 +389,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">proteger mi cuenta en equipos compartidos</t>
     </r>
@@ -397,6 +417,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -406,6 +427,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">administrador (Supervisor/
 Operacional)</t>
@@ -419,6 +441,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo </t>
     </r>
@@ -428,6 +451,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">gestionar la información de los asociados</t>
     </r>
@@ -439,6 +463,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para man</t>
     </r>
@@ -447,6 +472,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">tener un registro centralizado, confiable y actualizado</t>
     </r>
@@ -461,6 +487,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como usuario </t>
     </r>
@@ -469,6 +496,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">operacional</t>
     </r>
@@ -480,6 +508,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -488,6 +517,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">registrar un nuevo asociado con todos sus datos personales</t>
     </r>
@@ -499,6 +529,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -507,6 +538,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">incorporarlo a la base de datos de la asociación</t>
     </r>
@@ -536,6 +568,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -544,6 +577,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">consultar y visualizar la información de los asociados</t>
     </r>
@@ -555,6 +589,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -563,6 +598,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">atender rápidamente las solicitudes de los agremiados</t>
     </r>
@@ -586,6 +622,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -594,6 +631,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">modificar los datos de un asociado existente</t>
     </r>
@@ -605,6 +643,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -613,6 +652,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">mantener la información actualizada</t>
     </r>
@@ -636,6 +676,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -644,6 +685,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">supervisor</t>
     </r>
@@ -655,6 +697,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero</t>
     </r>
@@ -663,6 +706,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> desactivar un registro de asociado </t>
     </r>
@@ -674,6 +718,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -682,6 +727,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">gestionar casos de egreso o fallecimiento preservando el historial de información</t>
     </r>
@@ -705,6 +751,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo </t>
     </r>
@@ -713,6 +760,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">gestionar la información de familiares, voceros y proveedores asociados a AJUPTEL</t>
     </r>
@@ -724,6 +772,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -732,6 +781,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">mantener un registro organizado y actualizado de la información relacionada con los asociados.</t>
     </r>
@@ -746,6 +796,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como</t>
     </r>
@@ -754,6 +805,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> usuario operacional</t>
     </r>
@@ -765,6 +817,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -773,6 +826,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">registrar un familiar asociado a un asociado principal</t>
     </r>
@@ -784,6 +838,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -792,6 +847,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">tener los datos de contacto y parentesco</t>
     </r>
@@ -815,6 +871,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -823,6 +880,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">consultar, modificar y eliminar familiares</t>
     </r>
@@ -834,6 +892,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -842,6 +901,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">mantener actualizados los datos del núcleo familiar</t>
     </r>
@@ -865,6 +925,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -873,6 +934,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">registrar y administrar voceros asociados</t>
     </r>
@@ -884,6 +946,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -892,6 +955,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">mantener actualizada la información de representación y contacto de los asociados.</t>
     </r>
@@ -924,6 +988,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -932,6 +997,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">supervisor/ usuario operacional</t>
     </r>
@@ -943,6 +1009,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -951,6 +1018,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">registrar y gestionar proveedores de servicios</t>
     </r>
@@ -962,6 +1030,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -970,6 +1039,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">mantener un directorio actualizado de aliados y servicios asociados a AJUPTEL.</t>
     </r>
@@ -1002,6 +1072,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1010,6 +1081,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">administrador (Supervisor/
 Operacional</t>
@@ -1020,6 +1092,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
@@ -1031,6 +1104,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo </t>
     </r>
@@ -1039,6 +1113,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">importar y exportar datos de forma masiva</t>
     </r>
@@ -1050,6 +1125,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1058,6 +1134,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">facilitar la migración de información histórica y la generación de archivos administrativos</t>
     </r>
@@ -1072,6 +1149,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como usuario </t>
     </r>
@@ -1080,6 +1158,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">operacional/supervisor</t>
     </r>
@@ -1091,6 +1170,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -1099,6 +1179,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">importar datos de asociados desde archivos compatibles</t>
     </r>
@@ -1110,6 +1191,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1118,6 +1200,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">migrar la información histórica de la Asociación</t>
     </r>
@@ -1144,6 +1227,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como usuario </t>
     </r>
@@ -1152,6 +1236,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">operacional/supervisor/ejecutivo</t>
     </r>
@@ -1163,6 +1248,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -1171,6 +1257,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">exportar consultas y reportes en diferentes formatos</t>
     </r>
@@ -1182,6 +1269,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1190,6 +1278,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">compartir información administrativa cuando sea requerido.</t>
     </r>
@@ -1216,6 +1305,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1224,6 +1314,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ejecutivo </t>
     </r>
@@ -1235,6 +1326,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo</t>
     </r>
@@ -1243,6 +1335,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> acceder a indicadores y reportes administrativos</t>
     </r>
@@ -1254,6 +1347,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1262,6 +1356,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">apoyar la gestión y consulta de información de la Asociación.</t>
     </r>
@@ -1276,6 +1371,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1284,6 +1380,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ejecutivo</t>
     </r>
@@ -1295,6 +1392,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -1303,6 +1401,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero visualizar un dashboard con indicadores administrativos</t>
     </r>
@@ -1314,6 +1413,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1322,6 +1422,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">consultar información resumida de la Asociación.</t>
     </r>
@@ -1348,6 +1449,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -1356,6 +1458,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">generar reportes administrativos sobre los asociados</t>
     </r>
@@ -1367,6 +1470,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1375,6 +1479,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">consultar y compartir información administrativa de la asociación.</t>
     </r>
@@ -1398,6 +1503,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como</t>
     </r>
@@ -1406,6 +1512,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Asociado registrado</t>
     </r>
@@ -1417,6 +1524,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo a</t>
     </r>
@@ -1425,6 +1533,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">cceder a una plataforma web institucional y a un portal privado de asociados</t>
     </r>
@@ -1436,6 +1545,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para c</t>
     </r>
@@ -1444,6 +1554,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">onsultar información institucional, acceder a servicios digitales y mantenerme informado sobre actividades y contenido relacionado con AJUPTEL</t>
     </r>
@@ -1458,6 +1569,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1466,6 +1578,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">asociado (usuario final)</t>
     </r>
@@ -1477,6 +1590,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -1485,6 +1599,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">iniciar sesión en el portal de asociados</t>
     </r>
@@ -1496,6 +1611,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para a</t>
     </r>
@@ -1504,6 +1620,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">cceder de forma segura a mi información personal</t>
     </r>
@@ -1534,6 +1651,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1542,6 +1660,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">asociado</t>
     </r>
@@ -1553,6 +1672,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero c</t>
     </r>
@@ -1561,6 +1681,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">onsultar mi información personal desde el portal</t>
     </r>
@@ -1572,6 +1693,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para v</t>
     </r>
@@ -1580,6 +1702,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">erificar y mantener actualizados mis datos registrados</t>
     </r>
@@ -1613,6 +1736,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como</t>
     </r>
@@ -1622,6 +1746,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> usuario cualquier rol</t>
     </r>
@@ -1757,6 +1882,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1766,6 +1892,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">asociado o usuario operacional</t>
     </r>
@@ -1778,6 +1905,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo </t>
     </r>
@@ -1787,6 +1915,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">escanear documentos desde el móvil y enviarlos por email</t>
     </r>
@@ -1799,6 +1928,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1808,6 +1938,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">digitalizar trámites y evitar desplazamientos innecesarios</t>
     </r>
@@ -1822,6 +1953,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -1830,6 +1962,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">asociado o personal administrativo</t>
     </r>
@@ -1841,6 +1974,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -1849,6 +1983,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">escanear o capturar documentos desde mi dispositivo</t>
     </r>
@@ -1860,6 +1995,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1868,6 +2004,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">digitalizar y registrar documentos en la plataforma</t>
     </r>
@@ -1904,6 +2041,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como</t>
     </r>
@@ -1913,6 +2051,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> asociado o personal administrativo</t>
     </r>
@@ -1951,6 +2090,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -1959,6 +2099,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">consultar los documentos almacenados en la plataforma</t>
     </r>
@@ -1970,6 +2111,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -1978,6 +2120,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">acceder rápidamente al historial documental asociado a los trámites realizados</t>
     </r>
@@ -2010,6 +2153,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -2018,6 +2162,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ver el historial de los documentos que he escaneado y enviado</t>
     </r>
@@ -2029,6 +2174,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -2037,6 +2183,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">tener un registro digital de mis trámites y documentos</t>
     </r>
@@ -2064,6 +2211,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -2073,6 +2221,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">usuario cualquier rol</t>
     </r>
@@ -2085,6 +2234,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Deseo </t>
     </r>
@@ -2094,6 +2244,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">recibir asistencia inteligente y validaciones automáticas dentro de la plataforma</t>
     </r>
@@ -2106,6 +2257,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para</t>
     </r>
@@ -2115,6 +2267,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> facilitar el uso del sistema y mejorar la calidad de la información registrada</t>
     </r>
@@ -2129,6 +2282,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -2137,6 +2291,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">que el sistema me ayude a detectar asociados duplicados antes de crearlos</t>
     </r>
@@ -2148,6 +2303,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -2156,6 +2312,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">mantener la calidad y unicidad de los datos de la asociación</t>
     </r>
@@ -2189,6 +2346,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Como </t>
     </r>
@@ -2198,6 +2356,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">cualquier usuario (especialmente adultos mayores)</t>
     </r>
@@ -2210,6 +2369,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quiero </t>
     </r>
@@ -2219,6 +2379,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">disponer de un asistente virtual que me ayude a resolver dudas frecuentes dentro de la plataforma</t>
     </r>
@@ -2231,6 +2392,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Para </t>
     </r>
@@ -2240,6 +2402,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">utilizar el sistema de forma más sencilla sin depender de manuales o asistencia externa</t>
     </r>
@@ -2493,7 +2656,38 @@
 Entrega de Producto Final</t>
   </si>
   <si>
-    <t xml:space="preserve">RESUMEN DE ESTIMACIONES POR SPRINT DEL SISTEMA DE INFORMACIÓN WEB RESPONSIVO PARA LA GESTIÓN DE DATOS DE AJUPTEL, REGIÓN CARABOBO	</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RESUMEN DE ESTIMACIONES POR SPRINT DEL </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SISTEMA DE INFORMACIÓN WEB RESPONSIVO CON INTEGRACIÓN DE PORTAL INFORMATIVO Y CHATBOT INTERACTIVO CON INTELIGENCIA ARTIFICIAL ORIENTADO A LA OPTIMIZACIÓN DE LA GESTIÓN DE DATOS DE LA ASOCIACIÓN CIVIL (AJUPTEL), REGIÓN CARABOBO. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Duración Total Proyecto</t>
@@ -2522,6 +2716,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">5 (HU001) + 5 (HU002) + 3 (HU003) +  5 (HU020) + 5 (HU021) = </t>
     </r>
@@ -2531,6 +2726,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">23 puntos</t>
     </r>
@@ -2544,6 +2740,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">8 (HU004) + 5 (HU005) + 5 (HU006)  3 (HU007) + 5 (HU028)= </t>
     </r>
@@ -2553,6 +2750,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> 23 puntos</t>
     </r>
@@ -2566,6 +2764,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">5 (HU008) + 5 (HU009) + 3 (HU010) + 3 (HU0011) + 5 (HU026) = </t>
     </r>
@@ -2575,6 +2774,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">21</t>
     </r>
@@ -2583,6 +2783,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2592,6 +2793,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">puntos</t>
     </r>
@@ -2605,6 +2807,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">8 (HU012) + 5 (HU013) + 5 (HU014) + 5 (HU015)= 23</t>
     </r>
@@ -2614,6 +2817,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> puntos</t>
     </r>
@@ -2627,6 +2831,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">5 (HU016) + 5 (HU017) + 5 (HU018) + 5 (HU019) = 20</t>
     </r>
@@ -2636,6 +2841,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> puntos</t>
     </r>
@@ -2649,6 +2855,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">5 (HU022) + 5 (HU023) + 5 (HU024) + 3 (HU025) = 18</t>
     </r>
@@ -2658,6 +2865,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> puntos</t>
     </r>
@@ -2671,6 +2879,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">8 (HU027) = 8</t>
     </r>
@@ -2680,6 +2889,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> puntos</t>
     </r>
@@ -2699,12 +2909,13 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2738,15 +2949,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -2770,37 +2975,27 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2812,42 +3007,17 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -2998,7 +3168,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3011,7 +3181,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3027,11 +3197,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3039,27 +3209,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3067,7 +3237,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3075,56 +3245,40 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3135,15 +3289,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3163,59 +3313,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3223,75 +3337,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3515,9 +3609,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1426320</xdr:colOff>
+      <xdr:colOff>1425960</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>858600</xdr:rowOff>
+      <xdr:rowOff>858240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3532,7 +3626,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="10617840" cy="858600"/>
+          <a:ext cx="10617480" cy="858240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3561,7 +3655,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>2519640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>768960</xdr:rowOff>
+      <xdr:rowOff>768600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3576,7 +3670,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26640" y="195480"/>
-          <a:ext cx="7426800" cy="573480"/>
+          <a:ext cx="7426440" cy="573120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3603,9 +3697,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1043640</xdr:colOff>
+      <xdr:colOff>1043280</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>655200</xdr:rowOff>
+      <xdr:rowOff>654840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3620,7 +3714,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="95400"/>
-          <a:ext cx="6612120" cy="559800"/>
+          <a:ext cx="6611760" cy="559440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3797,11 +3891,11 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -4032,16 +4126,16 @@
       <c r="K15" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="22" t="s">
+      <c r="L15" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="22" t="n">
+      <c r="M15" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="22" t="s">
+      <c r="N15" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="22"/>
+      <c r="O15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16"/>
@@ -4057,10 +4151,10 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16"/>
@@ -4076,10 +4170,10 @@
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16"/>
@@ -4095,10 +4189,10 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16"/>
@@ -4120,22 +4214,22 @@
       <c r="I19" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K19" s="22" t="n">
+      <c r="K19" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="22" t="s">
+      <c r="L19" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="M19" s="22" t="n">
+      <c r="M19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="22" t="s">
+      <c r="N19" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O19" s="22"/>
+      <c r="O19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="80.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16"/>
@@ -4149,12 +4243,12 @@
       <c r="I20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16"/>
@@ -4168,12 +4262,12 @@
       <c r="I21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16"/>
@@ -4195,22 +4289,22 @@
       <c r="I22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K22" s="22" t="n">
+      <c r="K22" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="L22" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="M22" s="22" t="n">
+      <c r="M22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="22" t="s">
+      <c r="N22" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O22" s="22"/>
+      <c r="O22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16"/>
@@ -4224,14 +4318,13 @@
       <c r="I23" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
       <c r="S23" s="5"/>
-      <c r="XFD23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="16"/>
@@ -4245,16 +4338,15 @@
       <c r="I24" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="XFD24" s="23"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="22" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="17" t="s">
@@ -4281,26 +4373,25 @@
       <c r="I25" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="J25" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K25" s="22" t="n">
+      <c r="K25" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="22" t="s">
+      <c r="L25" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="M25" s="22" t="n">
+      <c r="M25" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="22" t="s">
+      <c r="N25" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O25" s="22"/>
-      <c r="XFD25" s="23"/>
+      <c r="O25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24"/>
+      <c r="A26" s="22"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="19"/>
@@ -4311,15 +4402,15 @@
       <c r="I26" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24"/>
+      <c r="A27" s="22"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="19"/>
@@ -4330,15 +4421,15 @@
       <c r="I27" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="19"/>
@@ -4349,15 +4440,15 @@
       <c r="I28" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="19"/>
@@ -4368,19 +4459,19 @@
       <c r="I29" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="19"/>
-      <c r="E30" s="25" t="s">
+      <c r="E30" s="18" t="s">
         <v>75</v>
       </c>
       <c r="F30" s="19" t="s">
@@ -4395,25 +4486,25 @@
       <c r="I30" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="J30" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K30" s="22" t="n">
+      <c r="K30" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L30" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M30" s="22" t="n">
+      <c r="M30" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="22" t="s">
+      <c r="N30" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O30" s="22"/>
+      <c r="O30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="19"/>
@@ -4424,15 +4515,15 @@
       <c r="I31" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
       <c r="L31" s="21"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="19"/>
@@ -4440,22 +4531,22 @@
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
-      <c r="I32" s="26" t="s">
+      <c r="I32" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
       <c r="L32" s="21"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="19"/>
-      <c r="E33" s="25" t="s">
+      <c r="E33" s="18" t="s">
         <v>81</v>
       </c>
       <c r="F33" s="19" t="s">
@@ -4473,22 +4564,22 @@
       <c r="J33" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K33" s="22" t="n">
+      <c r="K33" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L33" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M33" s="22" t="n">
+      <c r="M33" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N33" s="22" t="s">
+      <c r="N33" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O33" s="22"/>
+      <c r="O33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="19"/>
@@ -4496,18 +4587,18 @@
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
-      <c r="I34" s="26" t="s">
+      <c r="I34" s="23" t="s">
         <v>85</v>
       </c>
       <c r="J34" s="21"/>
-      <c r="K34" s="22"/>
+      <c r="K34" s="21"/>
       <c r="L34" s="21"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21"/>
+      <c r="O34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="19"/>
@@ -4515,22 +4606,22 @@
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
-      <c r="I35" s="26" t="s">
+      <c r="I35" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J35" s="21"/>
-      <c r="K35" s="22"/>
+      <c r="K35" s="21"/>
       <c r="L35" s="21"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="19"/>
-      <c r="E36" s="25" t="s">
+      <c r="E36" s="18" t="s">
         <v>87</v>
       </c>
       <c r="F36" s="19" t="s">
@@ -4542,28 +4633,28 @@
       <c r="H36" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I36" s="26" t="s">
+      <c r="I36" s="23" t="s">
         <v>91</v>
       </c>
       <c r="J36" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K36" s="22" t="n">
+      <c r="K36" s="21" t="n">
         <v>3</v>
       </c>
       <c r="L36" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M36" s="22" t="n">
+      <c r="M36" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="22" t="s">
+      <c r="N36" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O36" s="22"/>
+      <c r="O36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="19"/>
@@ -4571,18 +4662,18 @@
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
-      <c r="I37" s="26" t="s">
+      <c r="I37" s="23" t="s">
         <v>92</v>
       </c>
       <c r="J37" s="21"/>
-      <c r="K37" s="22"/>
+      <c r="K37" s="21"/>
       <c r="L37" s="21"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="19"/>
@@ -4590,18 +4681,18 @@
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
-      <c r="I38" s="26" t="s">
+      <c r="I38" s="23" t="s">
         <v>93</v>
       </c>
       <c r="J38" s="21"/>
-      <c r="K38" s="22"/>
+      <c r="K38" s="21"/>
       <c r="L38" s="21"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="24" t="s">
         <v>94</v>
       </c>
       <c r="B39" s="19" t="s">
@@ -4613,7 +4704,7 @@
       <c r="D39" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="18" t="s">
         <v>97</v>
       </c>
       <c r="F39" s="19" t="s">
@@ -4628,25 +4719,25 @@
       <c r="I39" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J39" s="22" t="s">
+      <c r="J39" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K39" s="22" t="n">
+      <c r="K39" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L39" s="22" t="s">
+      <c r="L39" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M39" s="22" t="n">
+      <c r="M39" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N39" s="22" t="s">
+      <c r="N39" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O39" s="22"/>
-    </row>
-    <row r="40" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="27"/>
+      <c r="O39" s="21"/>
+    </row>
+    <row r="40" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24"/>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
@@ -4654,18 +4745,18 @@
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
-      <c r="I40" s="26" t="s">
+      <c r="I40" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="22"/>
-    </row>
-    <row r="41" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="27"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="21"/>
+      <c r="O40" s="21"/>
+    </row>
+    <row r="41" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="24"/>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
       <c r="D41" s="19"/>
@@ -4673,22 +4764,22 @@
       <c r="F41" s="19"/>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
-      <c r="I41" s="26" t="s">
+      <c r="I41" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="22"/>
-      <c r="O41" s="22"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="21"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="27"/>
+      <c r="A42" s="24"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
-      <c r="E42" s="25" t="s">
+      <c r="E42" s="18" t="s">
         <v>104</v>
       </c>
       <c r="F42" s="19" t="s">
@@ -4703,25 +4794,25 @@
       <c r="I42" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="J42" s="22" t="s">
+      <c r="J42" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K42" s="22" t="n">
+      <c r="K42" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L42" s="22" t="s">
+      <c r="L42" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="M42" s="22" t="n">
+      <c r="M42" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N42" s="22" t="s">
+      <c r="N42" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O42" s="22"/>
-    </row>
-    <row r="43" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="27"/>
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="24"/>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
@@ -4729,18 +4820,18 @@
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
       <c r="H43" s="19"/>
-      <c r="I43" s="26" t="s">
+      <c r="I43" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
-    </row>
-    <row r="44" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="27"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="24"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
@@ -4748,22 +4839,22 @@
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
       <c r="H44" s="19"/>
-      <c r="I44" s="26" t="s">
+      <c r="I44" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="27"/>
+      <c r="A45" s="24"/>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="18" t="s">
         <v>110</v>
       </c>
       <c r="F45" s="19" t="s">
@@ -4781,22 +4872,22 @@
       <c r="J45" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K45" s="22" t="n">
+      <c r="K45" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="L45" s="22" t="s">
+      <c r="L45" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M45" s="22" t="n">
+      <c r="M45" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N45" s="22" t="s">
+      <c r="N45" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O45" s="22"/>
-    </row>
-    <row r="46" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="27"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="24"/>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
@@ -4808,14 +4899,14 @@
         <v>114</v>
       </c>
       <c r="J46" s="21"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-    </row>
-    <row r="47" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="27"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21"/>
+      <c r="O46" s="21"/>
+    </row>
+    <row r="47" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="24"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
@@ -4829,12 +4920,12 @@
       <c r="J47" s="21"/>
       <c r="K47" s="21"/>
       <c r="L47" s="21"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-    </row>
-    <row r="48" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="27"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="21"/>
+    </row>
+    <row r="48" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="24"/>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
@@ -4848,12 +4939,12 @@
       <c r="J48" s="21"/>
       <c r="K48" s="21"/>
       <c r="L48" s="21"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="22"/>
-      <c r="O48" s="22"/>
-    </row>
-    <row r="49" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="27"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="21"/>
+      <c r="O48" s="21"/>
+    </row>
+    <row r="49" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="24"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
@@ -4867,12 +4958,12 @@
       <c r="J49" s="21"/>
       <c r="K49" s="21"/>
       <c r="L49" s="21"/>
-      <c r="M49" s="22"/>
-      <c r="N49" s="22"/>
-      <c r="O49" s="22"/>
-    </row>
-    <row r="50" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="27"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="21"/>
+    </row>
+    <row r="50" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="24"/>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
       <c r="D50" s="19"/>
@@ -4886,16 +4977,16 @@
       <c r="J50" s="21"/>
       <c r="K50" s="21"/>
       <c r="L50" s="21"/>
-      <c r="M50" s="22"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="22"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
     </row>
     <row r="51" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="27"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="18" t="s">
         <v>119</v>
       </c>
       <c r="F51" s="19" t="s">
@@ -4907,28 +4998,28 @@
       <c r="H51" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="I51" s="26" t="s">
+      <c r="I51" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J51" s="22" t="s">
+      <c r="J51" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="K51" s="22" t="n">
+      <c r="K51" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="L51" s="22" t="s">
+      <c r="L51" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="M51" s="22" t="n">
+      <c r="M51" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N51" s="22" t="s">
+      <c r="N51" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O51" s="22"/>
-    </row>
-    <row r="52" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="27"/>
+      <c r="O51" s="21"/>
+    </row>
+    <row r="52" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="24"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
       <c r="D52" s="19"/>
@@ -4936,18 +5027,18 @@
       <c r="F52" s="19"/>
       <c r="G52" s="19"/>
       <c r="H52" s="19"/>
-      <c r="I52" s="26" t="s">
+      <c r="I52" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="22"/>
-      <c r="N52" s="22"/>
-      <c r="O52" s="22"/>
-    </row>
-    <row r="53" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="27"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="21"/>
+    </row>
+    <row r="53" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="24"/>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
@@ -4955,18 +5046,18 @@
       <c r="F53" s="19"/>
       <c r="G53" s="19"/>
       <c r="H53" s="19"/>
-      <c r="I53" s="26" t="s">
+      <c r="I53" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="J53" s="22"/>
-      <c r="K53" s="22"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="22"/>
-      <c r="O53" s="22"/>
-    </row>
-    <row r="54" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="27"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="21"/>
+    </row>
+    <row r="54" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="24"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
       <c r="D54" s="19"/>
@@ -4974,18 +5065,18 @@
       <c r="F54" s="19"/>
       <c r="G54" s="19"/>
       <c r="H54" s="19"/>
-      <c r="I54" s="26" t="s">
+      <c r="I54" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
-      <c r="O54" s="22"/>
-    </row>
-    <row r="55" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="27"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+    </row>
+    <row r="55" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="24"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
@@ -4993,18 +5084,18 @@
       <c r="F55" s="19"/>
       <c r="G55" s="19"/>
       <c r="H55" s="19"/>
-      <c r="I55" s="26" t="s">
+      <c r="I55" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="22"/>
-      <c r="N55" s="22"/>
-      <c r="O55" s="22"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="25" t="s">
         <v>129</v>
       </c>
       <c r="B56" s="19" t="s">
@@ -5016,7 +5107,7 @@
       <c r="D56" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E56" s="25" t="s">
+      <c r="E56" s="18" t="s">
         <v>133</v>
       </c>
       <c r="F56" s="19" t="s">
@@ -5034,22 +5125,22 @@
       <c r="J56" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K56" s="22" t="n">
+      <c r="K56" s="21" t="n">
         <v>8</v>
       </c>
       <c r="L56" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M56" s="22" t="n">
+      <c r="M56" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N56" s="22" t="s">
+      <c r="N56" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O56" s="22"/>
-    </row>
-    <row r="57" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="28"/>
+      <c r="O56" s="21"/>
+    </row>
+    <row r="57" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="25"/>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
@@ -5057,18 +5148,18 @@
       <c r="F57" s="19"/>
       <c r="G57" s="19"/>
       <c r="H57" s="19"/>
-      <c r="I57" s="26" t="s">
+      <c r="I57" s="23" t="s">
         <v>138</v>
       </c>
       <c r="J57" s="21"/>
-      <c r="K57" s="22"/>
+      <c r="K57" s="21"/>
       <c r="L57" s="21"/>
-      <c r="M57" s="22"/>
-      <c r="N57" s="22"/>
-      <c r="O57" s="22"/>
-    </row>
-    <row r="58" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="28"/>
+      <c r="M57" s="21"/>
+      <c r="N57" s="21"/>
+      <c r="O57" s="21"/>
+    </row>
+    <row r="58" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="25"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
@@ -5076,18 +5167,18 @@
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
-      <c r="I58" s="26" t="s">
+      <c r="I58" s="23" t="s">
         <v>139</v>
       </c>
       <c r="J58" s="21"/>
-      <c r="K58" s="22"/>
+      <c r="K58" s="21"/>
       <c r="L58" s="21"/>
-      <c r="M58" s="22"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="22"/>
-    </row>
-    <row r="59" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="28"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
+      <c r="O58" s="21"/>
+    </row>
+    <row r="59" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="25"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
@@ -5095,22 +5186,22 @@
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
-      <c r="I59" s="26" t="s">
+      <c r="I59" s="23" t="s">
         <v>140</v>
       </c>
       <c r="J59" s="21"/>
-      <c r="K59" s="22"/>
+      <c r="K59" s="21"/>
       <c r="L59" s="21"/>
-      <c r="M59" s="22"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="22"/>
+      <c r="M59" s="21"/>
+      <c r="N59" s="21"/>
+      <c r="O59" s="21"/>
     </row>
     <row r="60" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="28"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
-      <c r="E60" s="25" t="s">
+      <c r="E60" s="18" t="s">
         <v>141</v>
       </c>
       <c r="F60" s="19" t="s">
@@ -5128,22 +5219,22 @@
       <c r="J60" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K60" s="22" t="n">
+      <c r="K60" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L60" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="M60" s="22" t="n">
+      <c r="M60" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N60" s="22" t="s">
+      <c r="N60" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O60" s="22"/>
-    </row>
-    <row r="61" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="28"/>
+      <c r="O60" s="21"/>
+    </row>
+    <row r="61" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="25"/>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
@@ -5151,18 +5242,18 @@
       <c r="F61" s="19"/>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
-      <c r="I61" s="26" t="s">
+      <c r="I61" s="23" t="s">
         <v>147</v>
       </c>
       <c r="J61" s="21"/>
-      <c r="K61" s="22"/>
+      <c r="K61" s="21"/>
       <c r="L61" s="21"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-    </row>
-    <row r="62" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="28"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="21"/>
+    </row>
+    <row r="62" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="25"/>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
@@ -5170,18 +5261,18 @@
       <c r="F62" s="19"/>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
-      <c r="I62" s="26" t="s">
+      <c r="I62" s="23" t="s">
         <v>148</v>
       </c>
       <c r="J62" s="21"/>
-      <c r="K62" s="22"/>
+      <c r="K62" s="21"/>
       <c r="L62" s="21"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="22"/>
+      <c r="M62" s="21"/>
+      <c r="N62" s="21"/>
+      <c r="O62" s="21"/>
     </row>
     <row r="63" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="26" t="s">
         <v>149</v>
       </c>
       <c r="B63" s="19" t="s">
@@ -5193,7 +5284,7 @@
       <c r="D63" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="E63" s="25" t="s">
+      <c r="E63" s="18" t="s">
         <v>153</v>
       </c>
       <c r="F63" s="19" t="s">
@@ -5211,22 +5302,22 @@
       <c r="J63" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K63" s="22" t="n">
+      <c r="K63" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L63" s="22" t="s">
+      <c r="L63" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="M63" s="22" t="n">
+      <c r="M63" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N63" s="22" t="s">
+      <c r="N63" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O63" s="22"/>
-    </row>
-    <row r="64" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="29"/>
+      <c r="O63" s="21"/>
+    </row>
+    <row r="64" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="26"/>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
@@ -5234,18 +5325,18 @@
       <c r="F64" s="19"/>
       <c r="G64" s="19"/>
       <c r="H64" s="19"/>
-      <c r="I64" s="26" t="s">
+      <c r="I64" s="23" t="s">
         <v>159</v>
       </c>
       <c r="J64" s="21"/>
-      <c r="K64" s="22"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="22"/>
-      <c r="N64" s="22"/>
-      <c r="O64" s="22"/>
-    </row>
-    <row r="65" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="29"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21"/>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21"/>
+      <c r="O64" s="21"/>
+    </row>
+    <row r="65" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="26"/>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
@@ -5253,22 +5344,22 @@
       <c r="F65" s="19"/>
       <c r="G65" s="19"/>
       <c r="H65" s="19"/>
-      <c r="I65" s="26" t="s">
+      <c r="I65" s="23" t="s">
         <v>160</v>
       </c>
       <c r="J65" s="21"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="22"/>
-      <c r="N65" s="22"/>
-      <c r="O65" s="22"/>
+      <c r="K65" s="21"/>
+      <c r="L65" s="21"/>
+      <c r="M65" s="21"/>
+      <c r="N65" s="21"/>
+      <c r="O65" s="21"/>
     </row>
     <row r="66" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="29"/>
+      <c r="A66" s="26"/>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
-      <c r="E66" s="25" t="s">
+      <c r="E66" s="18" t="s">
         <v>161</v>
       </c>
       <c r="F66" s="19" t="s">
@@ -5286,22 +5377,22 @@
       <c r="J66" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K66" s="22" t="n">
+      <c r="K66" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L66" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="M66" s="22" t="n">
+      <c r="M66" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N66" s="22" t="s">
+      <c r="N66" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O66" s="22"/>
-    </row>
-    <row r="67" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="29"/>
+      <c r="O66" s="21"/>
+    </row>
+    <row r="67" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="26"/>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
@@ -5309,18 +5400,18 @@
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
-      <c r="I67" s="26" t="s">
+      <c r="I67" s="23" t="s">
         <v>165</v>
       </c>
       <c r="J67" s="21"/>
-      <c r="K67" s="22"/>
+      <c r="K67" s="21"/>
       <c r="L67" s="21"/>
-      <c r="M67" s="22"/>
-      <c r="N67" s="22"/>
-      <c r="O67" s="22"/>
-    </row>
-    <row r="68" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="29"/>
+      <c r="M67" s="21"/>
+      <c r="N67" s="21"/>
+      <c r="O67" s="21"/>
+    </row>
+    <row r="68" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="26"/>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
@@ -5328,18 +5419,18 @@
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
       <c r="H68" s="19"/>
-      <c r="I68" s="26" t="s">
+      <c r="I68" s="23" t="s">
         <v>166</v>
       </c>
       <c r="J68" s="21"/>
-      <c r="K68" s="22"/>
+      <c r="K68" s="21"/>
       <c r="L68" s="21"/>
-      <c r="M68" s="22"/>
-      <c r="N68" s="22"/>
-      <c r="O68" s="22"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
     </row>
     <row r="69" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="30" t="s">
+      <c r="A69" s="27" t="s">
         <v>167</v>
       </c>
       <c r="B69" s="19" t="s">
@@ -5351,7 +5442,7 @@
       <c r="D69" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E69" s="25" t="s">
+      <c r="E69" s="18" t="s">
         <v>171</v>
       </c>
       <c r="F69" s="19" t="s">
@@ -5369,102 +5460,102 @@
       <c r="J69" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K69" s="22" t="n">
+      <c r="K69" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L69" s="22" t="s">
+      <c r="L69" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="M69" s="22" t="n">
+      <c r="M69" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N69" s="22" t="s">
+      <c r="N69" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O69" s="22"/>
-    </row>
-    <row r="70" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="30"/>
+      <c r="O69" s="21"/>
+    </row>
+    <row r="70" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="27"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
       <c r="I70" s="7" t="s">
         <v>176</v>
       </c>
       <c r="J70" s="21"/>
-      <c r="K70" s="22"/>
-      <c r="L70" s="22"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-    </row>
-    <row r="71" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="30"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+    </row>
+    <row r="71" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="27"/>
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
       <c r="I71" s="7" t="s">
         <v>177</v>
       </c>
       <c r="J71" s="21"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-    </row>
-    <row r="72" customFormat="false" ht="74" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="30"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
+    </row>
+    <row r="72" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="27"/>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25"/>
-      <c r="I72" s="31" t="s">
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="23" t="s">
         <v>178</v>
       </c>
       <c r="J72" s="21"/>
-      <c r="K72" s="22"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-    </row>
-    <row r="73" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="30"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
+    </row>
+    <row r="73" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="27"/>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="26" t="s">
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="23" t="s">
         <v>179</v>
       </c>
       <c r="J73" s="21"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
     </row>
     <row r="74" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="30"/>
+      <c r="A74" s="27"/>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
-      <c r="E74" s="25" t="s">
+      <c r="E74" s="18" t="s">
         <v>180</v>
       </c>
       <c r="F74" s="19" t="s">
@@ -5482,665 +5573,665 @@
       <c r="J74" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K74" s="22" t="n">
+      <c r="K74" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L74" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="M74" s="22" t="n">
+      <c r="M74" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N74" s="22" t="s">
+      <c r="N74" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O74" s="22"/>
-    </row>
-    <row r="75" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="30"/>
+      <c r="O74" s="21"/>
+    </row>
+    <row r="75" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="27"/>
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
       <c r="I75" s="7" t="s">
         <v>186</v>
       </c>
       <c r="J75" s="21"/>
-      <c r="K75" s="22"/>
+      <c r="K75" s="21"/>
       <c r="L75" s="21"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-    </row>
-    <row r="76" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="30"/>
+      <c r="M75" s="21"/>
+      <c r="N75" s="21"/>
+      <c r="O75" s="21"/>
+    </row>
+    <row r="76" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="27"/>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18"/>
+      <c r="H76" s="18"/>
       <c r="I76" s="7" t="s">
         <v>187</v>
       </c>
       <c r="J76" s="21"/>
-      <c r="K76" s="22"/>
+      <c r="K76" s="21"/>
       <c r="L76" s="21"/>
-      <c r="M76" s="22"/>
-      <c r="N76" s="22"/>
-      <c r="O76" s="22"/>
-    </row>
-    <row r="77" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="30"/>
+      <c r="M76" s="21"/>
+      <c r="N76" s="21"/>
+      <c r="O76" s="21"/>
+    </row>
+    <row r="77" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="27"/>
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
       <c r="I77" s="7" t="s">
         <v>188</v>
       </c>
       <c r="J77" s="21"/>
-      <c r="K77" s="22"/>
+      <c r="K77" s="21"/>
       <c r="L77" s="21"/>
-      <c r="M77" s="22"/>
-      <c r="N77" s="22"/>
-      <c r="O77" s="22"/>
-    </row>
-    <row r="78" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="30"/>
+      <c r="M77" s="21"/>
+      <c r="N77" s="21"/>
+      <c r="O77" s="21"/>
+    </row>
+    <row r="78" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="27"/>
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="26" t="s">
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="23" t="s">
         <v>189</v>
       </c>
       <c r="J78" s="21"/>
-      <c r="K78" s="22"/>
+      <c r="K78" s="21"/>
       <c r="L78" s="21"/>
-      <c r="M78" s="22"/>
-      <c r="N78" s="22"/>
-      <c r="O78" s="22"/>
-    </row>
-    <row r="79" s="32" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="30"/>
+      <c r="M78" s="21"/>
+      <c r="N78" s="21"/>
+      <c r="O78" s="21"/>
+    </row>
+    <row r="79" s="28" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="27"/>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
-      <c r="E79" s="25" t="s">
+      <c r="E79" s="18" t="s">
         <v>190</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="G79" s="22" t="s">
+      <c r="G79" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="H79" s="22" t="s">
+      <c r="H79" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="I79" s="31" t="s">
+      <c r="I79" s="23" t="s">
         <v>194</v>
       </c>
       <c r="J79" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K79" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L79" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M79" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N79" s="22" t="s">
+      <c r="N79" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O79" s="22"/>
+      <c r="O79" s="21"/>
       <c r="XFC79" s="3"/>
       <c r="XFD79" s="1"/>
     </row>
-    <row r="80" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="30"/>
+    <row r="80" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="27"/>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
-      <c r="E80" s="25"/>
+      <c r="E80" s="18"/>
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
       <c r="H80" s="17"/>
-      <c r="I80" s="31" t="s">
+      <c r="I80" s="23" t="s">
         <v>196</v>
       </c>
       <c r="J80" s="21"/>
-      <c r="K80" s="22"/>
+      <c r="K80" s="21"/>
       <c r="L80" s="21"/>
-      <c r="M80" s="22"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="22"/>
-    </row>
-    <row r="81" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="30"/>
+      <c r="M80" s="21"/>
+      <c r="N80" s="21"/>
+      <c r="O80" s="21"/>
+    </row>
+    <row r="81" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="27"/>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
-      <c r="E81" s="25"/>
+      <c r="E81" s="18"/>
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
       <c r="H81" s="17"/>
-      <c r="I81" s="31" t="s">
+      <c r="I81" s="23" t="s">
         <v>197</v>
       </c>
       <c r="J81" s="21"/>
-      <c r="K81" s="22"/>
+      <c r="K81" s="21"/>
       <c r="L81" s="21"/>
-      <c r="M81" s="22"/>
-      <c r="N81" s="22"/>
-      <c r="O81" s="22"/>
-    </row>
-    <row r="82" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="30"/>
+      <c r="M81" s="21"/>
+      <c r="N81" s="21"/>
+      <c r="O81" s="21"/>
+    </row>
+    <row r="82" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="27"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
-      <c r="E82" s="25"/>
+      <c r="E82" s="18"/>
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
       <c r="H82" s="17"/>
-      <c r="I82" s="31" t="s">
+      <c r="I82" s="23" t="s">
         <v>198</v>
       </c>
       <c r="J82" s="21"/>
-      <c r="K82" s="22"/>
+      <c r="K82" s="21"/>
       <c r="L82" s="21"/>
-      <c r="M82" s="22"/>
-      <c r="N82" s="22"/>
-      <c r="O82" s="22"/>
-    </row>
-    <row r="83" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="30"/>
+      <c r="M82" s="21"/>
+      <c r="N82" s="21"/>
+      <c r="O82" s="21"/>
+    </row>
+    <row r="83" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="27"/>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
-      <c r="E83" s="25"/>
+      <c r="E83" s="18"/>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
       <c r="H83" s="17"/>
-      <c r="I83" s="31" t="s">
+      <c r="I83" s="23" t="s">
         <v>199</v>
       </c>
       <c r="J83" s="21"/>
-      <c r="K83" s="22"/>
+      <c r="K83" s="21"/>
       <c r="L83" s="21"/>
-      <c r="M83" s="22"/>
-      <c r="N83" s="22"/>
-      <c r="O83" s="22"/>
+      <c r="M83" s="21"/>
+      <c r="N83" s="21"/>
+      <c r="O83" s="21"/>
     </row>
     <row r="84" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="30"/>
+      <c r="A84" s="27"/>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
-      <c r="E84" s="25" t="s">
+      <c r="E84" s="18" t="s">
         <v>200</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="G84" s="22" t="s">
+      <c r="G84" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="H84" s="22" t="s">
+      <c r="H84" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="I84" s="31" t="s">
+      <c r="I84" s="23" t="s">
         <v>203</v>
       </c>
       <c r="J84" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K84" s="22" t="n">
+      <c r="K84" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L84" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="M84" s="22" t="n">
+      <c r="M84" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N84" s="22" t="s">
+      <c r="N84" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O84" s="22"/>
-    </row>
-    <row r="85" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="30"/>
+      <c r="O84" s="21"/>
+    </row>
+    <row r="85" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="27"/>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
-      <c r="E85" s="25"/>
+      <c r="E85" s="18"/>
       <c r="F85" s="17"/>
       <c r="G85" s="17"/>
       <c r="H85" s="17"/>
-      <c r="I85" s="31" t="s">
+      <c r="I85" s="23" t="s">
         <v>204</v>
       </c>
       <c r="J85" s="21"/>
-      <c r="K85" s="22"/>
+      <c r="K85" s="21"/>
       <c r="L85" s="21"/>
-      <c r="M85" s="22"/>
-      <c r="N85" s="22"/>
-      <c r="O85" s="22"/>
-    </row>
-    <row r="86" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="30"/>
+      <c r="M85" s="21"/>
+      <c r="N85" s="21"/>
+      <c r="O85" s="21"/>
+    </row>
+    <row r="86" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="27"/>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
-      <c r="E86" s="25"/>
+      <c r="E86" s="18"/>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
       <c r="H86" s="17"/>
-      <c r="I86" s="31" t="s">
+      <c r="I86" s="23" t="s">
         <v>205</v>
       </c>
       <c r="J86" s="21"/>
-      <c r="K86" s="22"/>
+      <c r="K86" s="21"/>
       <c r="L86" s="21"/>
-      <c r="M86" s="22"/>
-      <c r="N86" s="22"/>
-      <c r="O86" s="22"/>
-    </row>
-    <row r="87" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="30"/>
+      <c r="M86" s="21"/>
+      <c r="N86" s="21"/>
+      <c r="O86" s="21"/>
+    </row>
+    <row r="87" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="27"/>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
-      <c r="E87" s="25"/>
+      <c r="E87" s="18"/>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
       <c r="H87" s="17"/>
-      <c r="I87" s="31" t="s">
+      <c r="I87" s="23" t="s">
         <v>206</v>
       </c>
       <c r="J87" s="21"/>
-      <c r="K87" s="22"/>
+      <c r="K87" s="21"/>
       <c r="L87" s="21"/>
-      <c r="M87" s="22"/>
-      <c r="N87" s="22"/>
-      <c r="O87" s="22"/>
-    </row>
-    <row r="88" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="30"/>
+      <c r="M87" s="21"/>
+      <c r="N87" s="21"/>
+      <c r="O87" s="21"/>
+    </row>
+    <row r="88" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="27"/>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
-      <c r="E88" s="25"/>
+      <c r="E88" s="18"/>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
       <c r="H88" s="17"/>
-      <c r="I88" s="31" t="s">
+      <c r="I88" s="23" t="s">
         <v>198</v>
       </c>
       <c r="J88" s="21"/>
-      <c r="K88" s="22"/>
+      <c r="K88" s="21"/>
       <c r="L88" s="21"/>
-      <c r="M88" s="22"/>
-      <c r="N88" s="22"/>
-      <c r="O88" s="22"/>
+      <c r="M88" s="21"/>
+      <c r="N88" s="21"/>
+      <c r="O88" s="21"/>
     </row>
     <row r="89" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="30"/>
+      <c r="A89" s="27"/>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
-      <c r="E89" s="25" t="s">
+      <c r="E89" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="F89" s="22" t="s">
+      <c r="F89" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="G89" s="22" t="s">
+      <c r="G89" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="H89" s="22" t="s">
+      <c r="H89" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="I89" s="31" t="s">
+      <c r="I89" s="23" t="s">
         <v>210</v>
       </c>
       <c r="J89" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K89" s="22" t="n">
+      <c r="K89" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L89" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="M89" s="22" t="n">
+      <c r="M89" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N89" s="22" t="s">
+      <c r="N89" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O89" s="22"/>
-    </row>
-    <row r="90" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="30"/>
+      <c r="O89" s="21"/>
+    </row>
+    <row r="90" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="27"/>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="22"/>
-      <c r="G90" s="22"/>
-      <c r="H90" s="22"/>
-      <c r="I90" s="31" t="s">
+      <c r="E90" s="18"/>
+      <c r="F90" s="21"/>
+      <c r="G90" s="21"/>
+      <c r="H90" s="21"/>
+      <c r="I90" s="23" t="s">
         <v>212</v>
       </c>
       <c r="J90" s="21"/>
-      <c r="K90" s="22"/>
+      <c r="K90" s="21"/>
       <c r="L90" s="21"/>
-      <c r="M90" s="22"/>
-      <c r="N90" s="22"/>
-      <c r="O90" s="22"/>
-    </row>
-    <row r="91" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="30"/>
+      <c r="M90" s="21"/>
+      <c r="N90" s="21"/>
+      <c r="O90" s="21"/>
+    </row>
+    <row r="91" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="27"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
-      <c r="E91" s="25"/>
-      <c r="F91" s="22"/>
-      <c r="G91" s="22"/>
-      <c r="H91" s="22"/>
-      <c r="I91" s="31" t="s">
+      <c r="E91" s="18"/>
+      <c r="F91" s="21"/>
+      <c r="G91" s="21"/>
+      <c r="H91" s="21"/>
+      <c r="I91" s="23" t="s">
         <v>213</v>
       </c>
       <c r="J91" s="21"/>
-      <c r="K91" s="22"/>
+      <c r="K91" s="21"/>
       <c r="L91" s="21"/>
-      <c r="M91" s="22"/>
-      <c r="N91" s="22"/>
-      <c r="O91" s="22"/>
-    </row>
-    <row r="92" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="30"/>
+      <c r="M91" s="21"/>
+      <c r="N91" s="21"/>
+      <c r="O91" s="21"/>
+    </row>
+    <row r="92" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="27"/>
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
-      <c r="E92" s="25"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22"/>
-      <c r="H92" s="22"/>
-      <c r="I92" s="31" t="s">
+      <c r="E92" s="18"/>
+      <c r="F92" s="21"/>
+      <c r="G92" s="21"/>
+      <c r="H92" s="21"/>
+      <c r="I92" s="23" t="s">
         <v>198</v>
       </c>
       <c r="J92" s="21"/>
-      <c r="K92" s="22"/>
+      <c r="K92" s="21"/>
       <c r="L92" s="21"/>
-      <c r="M92" s="22"/>
-      <c r="N92" s="22"/>
-      <c r="O92" s="22"/>
-    </row>
-    <row r="93" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="30"/>
+      <c r="M92" s="21"/>
+      <c r="N92" s="21"/>
+      <c r="O92" s="21"/>
+    </row>
+    <row r="93" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="27"/>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22"/>
-      <c r="H93" s="22"/>
-      <c r="I93" s="31" t="s">
+      <c r="E93" s="18"/>
+      <c r="F93" s="21"/>
+      <c r="G93" s="21"/>
+      <c r="H93" s="21"/>
+      <c r="I93" s="23" t="s">
         <v>214</v>
       </c>
       <c r="J93" s="21"/>
-      <c r="K93" s="22"/>
+      <c r="K93" s="21"/>
       <c r="L93" s="21"/>
-      <c r="M93" s="22"/>
-      <c r="N93" s="22"/>
-      <c r="O93" s="22"/>
+      <c r="M93" s="21"/>
+      <c r="N93" s="21"/>
+      <c r="O93" s="21"/>
     </row>
     <row r="94" customFormat="false" ht="35.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="30"/>
+      <c r="A94" s="27"/>
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
-      <c r="E94" s="25" t="s">
+      <c r="E94" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="F94" s="22" t="s">
+      <c r="F94" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="G94" s="22" t="s">
+      <c r="G94" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="H94" s="22" t="s">
+      <c r="H94" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="I94" s="31" t="s">
+      <c r="I94" s="23" t="s">
         <v>219</v>
       </c>
       <c r="J94" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K94" s="22" t="n">
+      <c r="K94" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L94" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="M94" s="22" t="n">
+      <c r="M94" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N94" s="22" t="s">
+      <c r="N94" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O94" s="33"/>
-    </row>
-    <row r="95" customFormat="false" ht="39.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="30"/>
+      <c r="O94" s="29"/>
+    </row>
+    <row r="95" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="27"/>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
-      <c r="E95" s="25"/>
-      <c r="F95" s="22"/>
-      <c r="G95" s="22"/>
-      <c r="H95" s="22"/>
-      <c r="I95" s="31" t="s">
+      <c r="E95" s="18"/>
+      <c r="F95" s="21"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="21"/>
+      <c r="I95" s="23" t="s">
         <v>220</v>
       </c>
       <c r="J95" s="21"/>
-      <c r="K95" s="22"/>
+      <c r="K95" s="21"/>
       <c r="L95" s="21"/>
-      <c r="M95" s="22"/>
-      <c r="N95" s="22"/>
-      <c r="O95" s="22"/>
-    </row>
-    <row r="96" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="30"/>
+      <c r="M95" s="21"/>
+      <c r="N95" s="21"/>
+      <c r="O95" s="21"/>
+    </row>
+    <row r="96" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="27"/>
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
-      <c r="E96" s="25"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="22"/>
-      <c r="I96" s="31" t="s">
+      <c r="E96" s="18"/>
+      <c r="F96" s="21"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="21"/>
+      <c r="I96" s="23" t="s">
         <v>221</v>
       </c>
       <c r="J96" s="21"/>
-      <c r="K96" s="22"/>
+      <c r="K96" s="21"/>
       <c r="L96" s="21"/>
-      <c r="M96" s="22"/>
-      <c r="N96" s="22"/>
-      <c r="O96" s="22"/>
-    </row>
-    <row r="97" customFormat="false" ht="39.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="30"/>
+      <c r="M96" s="21"/>
+      <c r="N96" s="21"/>
+      <c r="O96" s="21"/>
+    </row>
+    <row r="97" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="27"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
-      <c r="E97" s="25"/>
-      <c r="F97" s="22"/>
-      <c r="G97" s="22"/>
-      <c r="H97" s="22"/>
-      <c r="I97" s="31" t="s">
+      <c r="E97" s="18"/>
+      <c r="F97" s="21"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="21"/>
+      <c r="I97" s="23" t="s">
         <v>222</v>
       </c>
       <c r="J97" s="21"/>
-      <c r="K97" s="22"/>
+      <c r="K97" s="21"/>
       <c r="L97" s="21"/>
-      <c r="M97" s="22"/>
-      <c r="N97" s="22"/>
-      <c r="O97" s="22"/>
-    </row>
-    <row r="98" customFormat="false" ht="39.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="30"/>
+      <c r="M97" s="21"/>
+      <c r="N97" s="21"/>
+      <c r="O97" s="21"/>
+    </row>
+    <row r="98" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="27"/>
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="31" t="s">
+      <c r="E98" s="18"/>
+      <c r="F98" s="21"/>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="23" t="s">
         <v>223</v>
       </c>
       <c r="J98" s="21"/>
-      <c r="K98" s="22"/>
+      <c r="K98" s="21"/>
       <c r="L98" s="21"/>
-      <c r="M98" s="22"/>
-      <c r="N98" s="22"/>
-      <c r="O98" s="22"/>
+      <c r="M98" s="21"/>
+      <c r="N98" s="21"/>
+      <c r="O98" s="21"/>
     </row>
     <row r="99" customFormat="false" ht="71.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="30"/>
+      <c r="A99" s="27"/>
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
-      <c r="E99" s="25" t="s">
+      <c r="E99" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F99" s="22" t="s">
+      <c r="F99" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="G99" s="34" t="s">
+      <c r="G99" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="H99" s="34" t="s">
+      <c r="H99" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="I99" s="35" t="s">
+      <c r="I99" s="30" t="s">
         <v>227</v>
       </c>
       <c r="J99" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K99" s="22" t="n">
+      <c r="K99" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L99" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="M99" s="22" t="n">
+      <c r="M99" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N99" s="22" t="s">
+      <c r="N99" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O99" s="22"/>
-    </row>
-    <row r="100" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="30"/>
+      <c r="O99" s="21"/>
+    </row>
+    <row r="100" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="27"/>
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
       <c r="E100" s="19"/>
-      <c r="F100" s="22"/>
-      <c r="G100" s="22"/>
-      <c r="H100" s="22"/>
-      <c r="I100" s="35" t="s">
+      <c r="F100" s="21"/>
+      <c r="G100" s="21"/>
+      <c r="H100" s="21"/>
+      <c r="I100" s="30" t="s">
         <v>228</v>
       </c>
       <c r="J100" s="21"/>
-      <c r="K100" s="22"/>
+      <c r="K100" s="21"/>
       <c r="L100" s="21"/>
-      <c r="M100" s="22"/>
-      <c r="N100" s="22"/>
-      <c r="O100" s="22"/>
-    </row>
-    <row r="101" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="30"/>
+      <c r="M100" s="21"/>
+      <c r="N100" s="21"/>
+      <c r="O100" s="21"/>
+    </row>
+    <row r="101" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="27"/>
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
-      <c r="F101" s="22"/>
-      <c r="G101" s="22"/>
-      <c r="H101" s="22"/>
-      <c r="I101" s="36" t="s">
+      <c r="F101" s="21"/>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="31" t="s">
         <v>229</v>
       </c>
       <c r="J101" s="21"/>
-      <c r="K101" s="22"/>
+      <c r="K101" s="21"/>
       <c r="L101" s="21"/>
-      <c r="M101" s="22"/>
-      <c r="N101" s="22"/>
-      <c r="O101" s="22"/>
-    </row>
-    <row r="102" customFormat="false" ht="47.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="30"/>
+      <c r="M101" s="21"/>
+      <c r="N101" s="21"/>
+      <c r="O101" s="21"/>
+    </row>
+    <row r="102" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="27"/>
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="19"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="22"/>
-      <c r="H102" s="22"/>
-      <c r="I102" s="35" t="s">
+      <c r="F102" s="21"/>
+      <c r="G102" s="21"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="30" t="s">
         <v>230</v>
       </c>
       <c r="J102" s="21"/>
-      <c r="K102" s="22"/>
+      <c r="K102" s="21"/>
       <c r="L102" s="21"/>
-      <c r="M102" s="22"/>
-      <c r="N102" s="22"/>
-      <c r="O102" s="22"/>
-    </row>
-    <row r="103" customFormat="false" ht="71.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="30"/>
+      <c r="M102" s="21"/>
+      <c r="N102" s="21"/>
+      <c r="O102" s="21"/>
+    </row>
+    <row r="103" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="27"/>
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
       <c r="E103" s="19"/>
-      <c r="F103" s="22"/>
-      <c r="G103" s="22"/>
-      <c r="H103" s="22"/>
-      <c r="I103" s="36" t="s">
+      <c r="F103" s="21"/>
+      <c r="G103" s="21"/>
+      <c r="H103" s="21"/>
+      <c r="I103" s="31" t="s">
         <v>231</v>
       </c>
       <c r="J103" s="21"/>
-      <c r="K103" s="22"/>
+      <c r="K103" s="21"/>
       <c r="L103" s="21"/>
-      <c r="M103" s="22"/>
-      <c r="N103" s="22"/>
-      <c r="O103" s="22"/>
+      <c r="M103" s="21"/>
+      <c r="N103" s="21"/>
+      <c r="O103" s="21"/>
     </row>
     <row r="104" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="37" t="s">
+      <c r="A104" s="32" t="s">
         <v>232</v>
       </c>
       <c r="B104" s="17" t="s">
@@ -6173,19 +6264,19 @@
       <c r="K104" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L104" s="22" t="s">
+      <c r="L104" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="M104" s="22" t="n">
+      <c r="M104" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N104" s="22" t="s">
+      <c r="N104" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O104" s="22"/>
-    </row>
-    <row r="105" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="37"/>
+      <c r="O104" s="21"/>
+    </row>
+    <row r="105" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="32"/>
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
@@ -6198,13 +6289,13 @@
       </c>
       <c r="J105" s="21"/>
       <c r="K105" s="21"/>
-      <c r="L105" s="22"/>
-      <c r="M105" s="22"/>
-      <c r="N105" s="22"/>
-      <c r="O105" s="22"/>
-    </row>
-    <row r="106" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="37"/>
+      <c r="L105" s="21"/>
+      <c r="M105" s="21"/>
+      <c r="N105" s="21"/>
+      <c r="O105" s="21"/>
+    </row>
+    <row r="106" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="32"/>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
@@ -6217,13 +6308,13 @@
       </c>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
-      <c r="L106" s="22"/>
-      <c r="M106" s="22"/>
-      <c r="N106" s="22"/>
-      <c r="O106" s="22"/>
-    </row>
-    <row r="107" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="37"/>
+      <c r="L106" s="21"/>
+      <c r="M106" s="21"/>
+      <c r="N106" s="21"/>
+      <c r="O106" s="21"/>
+    </row>
+    <row r="107" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="32"/>
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
@@ -6236,13 +6327,13 @@
       </c>
       <c r="J107" s="21"/>
       <c r="K107" s="21"/>
-      <c r="L107" s="22"/>
-      <c r="M107" s="22"/>
-      <c r="N107" s="22"/>
-      <c r="O107" s="22"/>
-    </row>
-    <row r="108" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="37"/>
+      <c r="L107" s="21"/>
+      <c r="M107" s="21"/>
+      <c r="N107" s="21"/>
+      <c r="O107" s="21"/>
+    </row>
+    <row r="108" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="32"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
@@ -6255,13 +6346,13 @@
       </c>
       <c r="J108" s="21"/>
       <c r="K108" s="21"/>
-      <c r="L108" s="22"/>
-      <c r="M108" s="22"/>
-      <c r="N108" s="22"/>
-      <c r="O108" s="22"/>
-    </row>
-    <row r="109" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="37"/>
+      <c r="L108" s="21"/>
+      <c r="M108" s="21"/>
+      <c r="N108" s="21"/>
+      <c r="O108" s="21"/>
+    </row>
+    <row r="109" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="32"/>
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -6269,18 +6360,18 @@
       <c r="F109" s="19"/>
       <c r="G109" s="19"/>
       <c r="H109" s="20"/>
-      <c r="I109" s="31" t="s">
+      <c r="I109" s="23" t="s">
         <v>245</v>
       </c>
       <c r="J109" s="21"/>
       <c r="K109" s="21"/>
-      <c r="L109" s="22"/>
-      <c r="M109" s="22"/>
-      <c r="N109" s="22"/>
-      <c r="O109" s="22"/>
-    </row>
-    <row r="110" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="37"/>
+      <c r="L109" s="21"/>
+      <c r="M109" s="21"/>
+      <c r="N109" s="21"/>
+      <c r="O109" s="21"/>
+    </row>
+    <row r="110" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="32"/>
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
       <c r="D110" s="17"/>
@@ -6293,13 +6384,13 @@
       </c>
       <c r="J110" s="21"/>
       <c r="K110" s="21"/>
-      <c r="L110" s="22"/>
-      <c r="M110" s="22"/>
-      <c r="N110" s="22"/>
-      <c r="O110" s="22"/>
+      <c r="L110" s="21"/>
+      <c r="M110" s="21"/>
+      <c r="N110" s="21"/>
+      <c r="O110" s="21"/>
     </row>
     <row r="111" customFormat="false" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="37"/>
+      <c r="A111" s="32"/>
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
@@ -6309,34 +6400,34 @@
       <c r="F111" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="G111" s="22" t="s">
+      <c r="G111" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="H111" s="22" t="s">
+      <c r="H111" s="21" t="s">
         <v>250</v>
       </c>
       <c r="I111" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="J111" s="22" t="s">
+      <c r="J111" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K111" s="22" t="n">
+      <c r="K111" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L111" s="22" t="s">
+      <c r="L111" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="M111" s="22" t="n">
+      <c r="M111" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N111" s="22" t="s">
+      <c r="N111" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O111" s="22"/>
-    </row>
-    <row r="112" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="37"/>
+      <c r="O111" s="21"/>
+    </row>
+    <row r="112" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="32"/>
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
       <c r="D112" s="17"/>
@@ -6347,15 +6438,15 @@
       <c r="I112" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="J112" s="22"/>
-      <c r="K112" s="22"/>
-      <c r="L112" s="22"/>
-      <c r="M112" s="22"/>
-      <c r="N112" s="22"/>
-      <c r="O112" s="22"/>
-    </row>
-    <row r="113" customFormat="false" ht="86" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="37"/>
+      <c r="J112" s="21"/>
+      <c r="K112" s="21"/>
+      <c r="L112" s="21"/>
+      <c r="M112" s="21"/>
+      <c r="N112" s="21"/>
+      <c r="O112" s="21"/>
+    </row>
+    <row r="113" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="32"/>
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
       <c r="D113" s="17"/>
@@ -6366,15 +6457,15 @@
       <c r="I113" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="J113" s="22"/>
-      <c r="K113" s="22"/>
-      <c r="L113" s="22"/>
-      <c r="M113" s="22"/>
-      <c r="N113" s="22"/>
-      <c r="O113" s="22"/>
-    </row>
-    <row r="114" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="37"/>
+      <c r="J113" s="21"/>
+      <c r="K113" s="21"/>
+      <c r="L113" s="21"/>
+      <c r="M113" s="21"/>
+      <c r="N113" s="21"/>
+      <c r="O113" s="21"/>
+    </row>
+    <row r="114" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="32"/>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
       <c r="D114" s="17"/>
@@ -6385,15 +6476,15 @@
       <c r="I114" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="J114" s="22"/>
-      <c r="K114" s="22"/>
-      <c r="L114" s="22"/>
-      <c r="M114" s="22"/>
-      <c r="N114" s="22"/>
-      <c r="O114" s="22"/>
-    </row>
-    <row r="115" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="37"/>
+      <c r="J114" s="21"/>
+      <c r="K114" s="21"/>
+      <c r="L114" s="21"/>
+      <c r="M114" s="21"/>
+      <c r="N114" s="21"/>
+      <c r="O114" s="21"/>
+    </row>
+    <row r="115" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="32"/>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
@@ -6404,15 +6495,15 @@
       <c r="I115" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="J115" s="22"/>
-      <c r="K115" s="22"/>
-      <c r="L115" s="22"/>
-      <c r="M115" s="22"/>
-      <c r="N115" s="22"/>
-      <c r="O115" s="22"/>
-    </row>
-    <row r="116" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="37"/>
+      <c r="J115" s="21"/>
+      <c r="K115" s="21"/>
+      <c r="L115" s="21"/>
+      <c r="M115" s="21"/>
+      <c r="N115" s="21"/>
+      <c r="O115" s="21"/>
+    </row>
+    <row r="116" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="32"/>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
@@ -6420,18 +6511,18 @@
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
       <c r="H116" s="17"/>
-      <c r="I116" s="31" t="s">
+      <c r="I116" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="J116" s="22"/>
-      <c r="K116" s="22"/>
-      <c r="L116" s="22"/>
-      <c r="M116" s="22"/>
-      <c r="N116" s="22"/>
-      <c r="O116" s="22"/>
-    </row>
-    <row r="117" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="37"/>
+      <c r="J116" s="21"/>
+      <c r="K116" s="21"/>
+      <c r="L116" s="21"/>
+      <c r="M116" s="21"/>
+      <c r="N116" s="21"/>
+      <c r="O116" s="21"/>
+    </row>
+    <row r="117" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="32"/>
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
       <c r="D117" s="17"/>
@@ -6442,15 +6533,15 @@
       <c r="I117" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="J117" s="22"/>
-      <c r="K117" s="22"/>
-      <c r="L117" s="22"/>
-      <c r="M117" s="22"/>
-      <c r="N117" s="22"/>
-      <c r="O117" s="22"/>
+      <c r="J117" s="21"/>
+      <c r="K117" s="21"/>
+      <c r="L117" s="21"/>
+      <c r="M117" s="21"/>
+      <c r="N117" s="21"/>
+      <c r="O117" s="21"/>
     </row>
     <row r="118" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="37"/>
+      <c r="A118" s="32"/>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
       <c r="D118" s="17"/>
@@ -6469,25 +6560,25 @@
       <c r="I118" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="J118" s="22" t="s">
+      <c r="J118" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K118" s="22" t="n">
+      <c r="K118" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L118" s="22" t="s">
+      <c r="L118" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="M118" s="22" t="n">
+      <c r="M118" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N118" s="22" t="s">
+      <c r="N118" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O118" s="22"/>
-    </row>
-    <row r="119" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="37"/>
+      <c r="O118" s="21"/>
+    </row>
+    <row r="119" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="32"/>
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
       <c r="D119" s="17"/>
@@ -6498,15 +6589,15 @@
       <c r="I119" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="J119" s="22"/>
-      <c r="K119" s="22"/>
-      <c r="L119" s="22"/>
-      <c r="M119" s="22"/>
-      <c r="N119" s="22"/>
-      <c r="O119" s="22"/>
-    </row>
-    <row r="120" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="37"/>
+      <c r="J119" s="21"/>
+      <c r="K119" s="21"/>
+      <c r="L119" s="21"/>
+      <c r="M119" s="21"/>
+      <c r="N119" s="21"/>
+      <c r="O119" s="21"/>
+    </row>
+    <row r="120" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="32"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
@@ -6517,15 +6608,15 @@
       <c r="I120" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="J120" s="22"/>
-      <c r="K120" s="22"/>
-      <c r="L120" s="22"/>
-      <c r="M120" s="22"/>
-      <c r="N120" s="22"/>
-      <c r="O120" s="22"/>
-    </row>
-    <row r="121" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="37"/>
+      <c r="J120" s="21"/>
+      <c r="K120" s="21"/>
+      <c r="L120" s="21"/>
+      <c r="M120" s="21"/>
+      <c r="N120" s="21"/>
+      <c r="O120" s="21"/>
+    </row>
+    <row r="121" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="32"/>
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
       <c r="D121" s="17"/>
@@ -6536,15 +6627,15 @@
       <c r="I121" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="J121" s="22"/>
-      <c r="K121" s="22"/>
-      <c r="L121" s="22"/>
-      <c r="M121" s="22"/>
-      <c r="N121" s="22"/>
-      <c r="O121" s="22"/>
-    </row>
-    <row r="122" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="37"/>
+      <c r="J121" s="21"/>
+      <c r="K121" s="21"/>
+      <c r="L121" s="21"/>
+      <c r="M121" s="21"/>
+      <c r="N121" s="21"/>
+      <c r="O121" s="21"/>
+    </row>
+    <row r="122" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="32"/>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
       <c r="D122" s="17"/>
@@ -6555,15 +6646,15 @@
       <c r="I122" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="J122" s="22"/>
-      <c r="K122" s="22"/>
-      <c r="L122" s="22"/>
-      <c r="M122" s="22"/>
-      <c r="N122" s="22"/>
-      <c r="O122" s="22"/>
-    </row>
-    <row r="123" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="37"/>
+      <c r="J122" s="21"/>
+      <c r="K122" s="21"/>
+      <c r="L122" s="21"/>
+      <c r="M122" s="21"/>
+      <c r="N122" s="21"/>
+      <c r="O122" s="21"/>
+    </row>
+    <row r="123" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="32"/>
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
       <c r="D123" s="17"/>
@@ -6574,15 +6665,15 @@
       <c r="I123" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="J123" s="22"/>
-      <c r="K123" s="22"/>
-      <c r="L123" s="22"/>
-      <c r="M123" s="22"/>
-      <c r="N123" s="22"/>
-      <c r="O123" s="22"/>
+      <c r="J123" s="21"/>
+      <c r="K123" s="21"/>
+      <c r="L123" s="21"/>
+      <c r="M123" s="21"/>
+      <c r="N123" s="21"/>
+      <c r="O123" s="21"/>
     </row>
     <row r="124" customFormat="false" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="37"/>
+      <c r="A124" s="32"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
       <c r="D124" s="17"/>
@@ -6601,25 +6692,25 @@
       <c r="I124" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="J124" s="22" t="s">
+      <c r="J124" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K124" s="22" t="n">
+      <c r="K124" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="L124" s="22" t="s">
+      <c r="L124" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="M124" s="22" t="n">
+      <c r="M124" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N124" s="22" t="s">
+      <c r="N124" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O124" s="22"/>
-    </row>
-    <row r="125" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="37"/>
+      <c r="O124" s="21"/>
+    </row>
+    <row r="125" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="32"/>
       <c r="B125" s="17"/>
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
@@ -6630,15 +6721,15 @@
       <c r="I125" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="J125" s="22"/>
-      <c r="K125" s="22"/>
-      <c r="L125" s="22"/>
-      <c r="M125" s="22"/>
-      <c r="N125" s="22"/>
-      <c r="O125" s="22"/>
-    </row>
-    <row r="126" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="37"/>
+      <c r="J125" s="21"/>
+      <c r="K125" s="21"/>
+      <c r="L125" s="21"/>
+      <c r="M125" s="21"/>
+      <c r="N125" s="21"/>
+      <c r="O125" s="21"/>
+    </row>
+    <row r="126" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="32"/>
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
       <c r="D126" s="17"/>
@@ -6646,18 +6737,18 @@
       <c r="F126" s="19"/>
       <c r="G126" s="19"/>
       <c r="H126" s="19"/>
-      <c r="I126" s="31" t="s">
+      <c r="I126" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="J126" s="22"/>
-      <c r="K126" s="22"/>
-      <c r="L126" s="22"/>
-      <c r="M126" s="22"/>
-      <c r="N126" s="22"/>
-      <c r="O126" s="22"/>
-    </row>
-    <row r="127" customFormat="false" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="37"/>
+      <c r="J126" s="21"/>
+      <c r="K126" s="21"/>
+      <c r="L126" s="21"/>
+      <c r="M126" s="21"/>
+      <c r="N126" s="21"/>
+      <c r="O126" s="21"/>
+    </row>
+    <row r="127" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="32"/>
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
       <c r="D127" s="17"/>
@@ -6668,15 +6759,15 @@
       <c r="I127" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="J127" s="22"/>
-      <c r="K127" s="22"/>
-      <c r="L127" s="22"/>
-      <c r="M127" s="22"/>
-      <c r="N127" s="22"/>
-      <c r="O127" s="22"/>
-    </row>
-    <row r="128" s="39" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="38" t="s">
+      <c r="J127" s="21"/>
+      <c r="K127" s="21"/>
+      <c r="L127" s="21"/>
+      <c r="M127" s="21"/>
+      <c r="N127" s="21"/>
+      <c r="O127" s="21"/>
+    </row>
+    <row r="128" s="34" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="33" t="s">
         <v>273</v>
       </c>
       <c r="B128" s="17" t="s">
@@ -6709,21 +6800,21 @@
       <c r="K128" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L128" s="22" t="s">
+      <c r="L128" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M128" s="22" t="n">
+      <c r="M128" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N128" s="22" t="s">
+      <c r="N128" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O128" s="22"/>
+      <c r="O128" s="21"/>
       <c r="XFC128" s="3"/>
       <c r="XFD128" s="1"/>
     </row>
-    <row r="129" s="40" customFormat="true" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="38"/>
+    <row r="129" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="33"/>
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
       <c r="D129" s="17"/>
@@ -6736,15 +6827,15 @@
       </c>
       <c r="J129" s="21"/>
       <c r="K129" s="21"/>
-      <c r="L129" s="22"/>
-      <c r="M129" s="22"/>
-      <c r="N129" s="22"/>
-      <c r="O129" s="22"/>
+      <c r="L129" s="21"/>
+      <c r="M129" s="21"/>
+      <c r="N129" s="21"/>
+      <c r="O129" s="21"/>
       <c r="XFC129" s="3"/>
       <c r="XFD129" s="1"/>
     </row>
-    <row r="130" s="40" customFormat="true" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="38"/>
+    <row r="130" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="33"/>
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
       <c r="D130" s="17"/>
@@ -6757,15 +6848,15 @@
       </c>
       <c r="J130" s="21"/>
       <c r="K130" s="21"/>
-      <c r="L130" s="22"/>
-      <c r="M130" s="22"/>
-      <c r="N130" s="22"/>
-      <c r="O130" s="22"/>
+      <c r="L130" s="21"/>
+      <c r="M130" s="21"/>
+      <c r="N130" s="21"/>
+      <c r="O130" s="21"/>
       <c r="XFC130" s="3"/>
       <c r="XFD130" s="1"/>
     </row>
-    <row r="131" s="40" customFormat="true" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="38"/>
+    <row r="131" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="33"/>
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
       <c r="D131" s="17"/>
@@ -6778,15 +6869,15 @@
       </c>
       <c r="J131" s="21"/>
       <c r="K131" s="21"/>
-      <c r="L131" s="22"/>
-      <c r="M131" s="22"/>
-      <c r="N131" s="22"/>
-      <c r="O131" s="22"/>
+      <c r="L131" s="21"/>
+      <c r="M131" s="21"/>
+      <c r="N131" s="21"/>
+      <c r="O131" s="21"/>
       <c r="XFC131" s="3"/>
       <c r="XFD131" s="1"/>
     </row>
-    <row r="132" s="40" customFormat="true" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="38"/>
+    <row r="132" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="33"/>
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
@@ -6799,15 +6890,15 @@
       </c>
       <c r="J132" s="21"/>
       <c r="K132" s="21"/>
-      <c r="L132" s="22"/>
-      <c r="M132" s="22"/>
-      <c r="N132" s="22"/>
-      <c r="O132" s="22"/>
+      <c r="L132" s="21"/>
+      <c r="M132" s="21"/>
+      <c r="N132" s="21"/>
+      <c r="O132" s="21"/>
       <c r="XFC132" s="3"/>
       <c r="XFD132" s="1"/>
     </row>
-    <row r="133" s="40" customFormat="true" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="38"/>
+    <row r="133" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="33"/>
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
@@ -6820,15 +6911,15 @@
       </c>
       <c r="J133" s="21"/>
       <c r="K133" s="21"/>
-      <c r="L133" s="22"/>
-      <c r="M133" s="22"/>
-      <c r="N133" s="22"/>
-      <c r="O133" s="22"/>
+      <c r="L133" s="21"/>
+      <c r="M133" s="21"/>
+      <c r="N133" s="21"/>
+      <c r="O133" s="21"/>
       <c r="XFC133" s="3"/>
       <c r="XFD133" s="1"/>
     </row>
-    <row r="134" s="40" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="38"/>
+    <row r="134" s="35" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="33"/>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
@@ -6847,27 +6938,27 @@
       <c r="I134" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="J134" s="22" t="s">
+      <c r="J134" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K134" s="22" t="n">
+      <c r="K134" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="L134" s="22" t="s">
+      <c r="L134" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="M134" s="22" t="n">
+      <c r="M134" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="N134" s="22" t="s">
+      <c r="N134" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O134" s="22"/>
+      <c r="O134" s="21"/>
       <c r="XFC134" s="3"/>
       <c r="XFD134" s="1"/>
     </row>
-    <row r="135" s="40" customFormat="true" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="38"/>
+    <row r="135" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="33"/>
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
       <c r="D135" s="17"/>
@@ -6878,17 +6969,17 @@
       <c r="I135" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="J135" s="22"/>
-      <c r="K135" s="22"/>
-      <c r="L135" s="22"/>
-      <c r="M135" s="22"/>
-      <c r="N135" s="22"/>
-      <c r="O135" s="22"/>
+      <c r="J135" s="21"/>
+      <c r="K135" s="21"/>
+      <c r="L135" s="21"/>
+      <c r="M135" s="21"/>
+      <c r="N135" s="21"/>
+      <c r="O135" s="21"/>
       <c r="XFC135" s="3"/>
       <c r="XFD135" s="1"/>
     </row>
-    <row r="136" s="40" customFormat="true" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="38"/>
+    <row r="136" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="33"/>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
       <c r="D136" s="17"/>
@@ -6899,17 +6990,17 @@
       <c r="I136" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="J136" s="22"/>
-      <c r="K136" s="22"/>
-      <c r="L136" s="22"/>
-      <c r="M136" s="22"/>
-      <c r="N136" s="22"/>
-      <c r="O136" s="22"/>
+      <c r="J136" s="21"/>
+      <c r="K136" s="21"/>
+      <c r="L136" s="21"/>
+      <c r="M136" s="21"/>
+      <c r="N136" s="21"/>
+      <c r="O136" s="21"/>
       <c r="XFC136" s="3"/>
       <c r="XFD136" s="1"/>
     </row>
-    <row r="137" s="40" customFormat="true" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="38"/>
+    <row r="137" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="33"/>
       <c r="B137" s="17"/>
       <c r="C137" s="17"/>
       <c r="D137" s="17"/>
@@ -6920,17 +7011,17 @@
       <c r="I137" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="J137" s="22"/>
-      <c r="K137" s="22"/>
-      <c r="L137" s="22"/>
-      <c r="M137" s="22"/>
-      <c r="N137" s="22"/>
-      <c r="O137" s="22"/>
+      <c r="J137" s="21"/>
+      <c r="K137" s="21"/>
+      <c r="L137" s="21"/>
+      <c r="M137" s="21"/>
+      <c r="N137" s="21"/>
+      <c r="O137" s="21"/>
       <c r="XFC137" s="3"/>
       <c r="XFD137" s="1"/>
     </row>
-    <row r="138" s="40" customFormat="true" ht="74" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="38"/>
+    <row r="138" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="33"/>
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
       <c r="D138" s="17"/>
@@ -6941,17 +7032,17 @@
       <c r="I138" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="J138" s="22"/>
-      <c r="K138" s="22"/>
-      <c r="L138" s="22"/>
-      <c r="M138" s="22"/>
-      <c r="N138" s="22"/>
-      <c r="O138" s="22"/>
+      <c r="J138" s="21"/>
+      <c r="K138" s="21"/>
+      <c r="L138" s="21"/>
+      <c r="M138" s="21"/>
+      <c r="N138" s="21"/>
+      <c r="O138" s="21"/>
       <c r="XFC138" s="3"/>
       <c r="XFD138" s="1"/>
     </row>
-    <row r="139" s="40" customFormat="true" ht="38" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="38"/>
+    <row r="139" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="33"/>
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
@@ -6962,12 +7053,12 @@
       <c r="I139" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="J139" s="22"/>
-      <c r="K139" s="22"/>
-      <c r="L139" s="22"/>
-      <c r="M139" s="22"/>
-      <c r="N139" s="22"/>
-      <c r="O139" s="22"/>
+      <c r="J139" s="21"/>
+      <c r="K139" s="21"/>
+      <c r="L139" s="21"/>
+      <c r="M139" s="21"/>
+      <c r="N139" s="21"/>
+      <c r="O139" s="21"/>
       <c r="XFC139" s="3"/>
       <c r="XFD139" s="1"/>
     </row>
@@ -7345,112 +7436,112 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="41" width="31.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="41" width="24.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="41" width="14.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="41" width="40.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="41" width="26.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="41" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="41" width="28.42"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="41" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="31.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="24.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="28.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="2" width="8.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="71.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" s="43" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-    </row>
-    <row r="3" s="43" customFormat="true" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="s">
+    <row r="2" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+    </row>
+    <row r="3" s="1" customFormat="true" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-    </row>
-    <row r="4" s="43" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45"/>
-    </row>
-    <row r="5" s="43" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="46" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="true" ht="38.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-    </row>
-    <row r="6" s="43" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+    </row>
+    <row r="6" s="1" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-    </row>
-    <row r="7" s="43" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+    </row>
+    <row r="7" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-    </row>
-    <row r="8" s="43" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="46" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+    </row>
+    <row r="8" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-    </row>
-    <row r="9" s="43" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+    </row>
+    <row r="9" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-    </row>
-    <row r="10" s="43" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="46" t="s">
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+    </row>
+    <row r="10" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-    </row>
-    <row r="11" s="43" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="46" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+    </row>
+    <row r="11" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-    </row>
-    <row r="12" s="43" customFormat="true" ht="50.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="48" t="s">
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="50.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -7458,259 +7549,259 @@
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="49"/>
+      <c r="E12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="39" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="51" t="s">
+      <c r="D16" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="40" t="s">
         <v>303</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="F16" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="G16" s="52" t="s">
+      <c r="G16" s="40" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="E17" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="F17" s="53" t="s">
+      <c r="F17" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="G17" s="53" t="s">
+      <c r="G17" s="23" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
+    <row r="18" customFormat="false" ht="77" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="D18" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="F18" s="53" t="s">
+      <c r="F18" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="G18" s="53" t="s">
+      <c r="G18" s="23" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="62.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="s">
+    <row r="19" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="53" t="s">
+      <c r="E19" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="F19" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="G19" s="53" t="s">
+      <c r="G19" s="23" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="62.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="46" t="s">
+    <row r="20" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="G20" s="53" t="s">
+      <c r="G20" s="23" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="62.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="46" t="s">
+    <row r="21" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="E21" s="53" t="s">
+      <c r="E21" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="F21" s="53" t="s">
+      <c r="F21" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="G21" s="53" t="s">
+      <c r="G21" s="23" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="62.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="46" t="s">
+    <row r="22" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="E22" s="53" t="s">
+      <c r="E22" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="G22" s="53" t="s">
+      <c r="G22" s="23" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="62.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="46" t="s">
+    <row r="23" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="E23" s="53" t="s">
+      <c r="E23" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="G23" s="53" t="s">
+      <c r="G23" s="23" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="53" t="s">
+      <c r="E24" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="G24" s="53" t="s">
+      <c r="G24" s="23" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="110" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46" t="s">
+    <row r="25" customFormat="false" ht="114.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="23" t="s">
         <v>358</v>
       </c>
-      <c r="E25" s="53" t="s">
+      <c r="E25" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="F25" s="53" t="s">
+      <c r="F25" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="G25" s="53" t="s">
+      <c r="G25" s="23" t="s">
         <v>361</v>
       </c>
     </row>
@@ -7748,236 +7839,236 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="55" width="29.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="55" width="49.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="55" width="18.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="5" style="56" width="8.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="56" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="41" width="29.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="41" width="49.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="41" width="18.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="5" style="41" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="41" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-    </row>
-    <row r="2" s="58" customFormat="true" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="57" t="s">
+      <c r="A1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+    </row>
+    <row r="2" s="3" customFormat="true" ht="68.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="0"/>
-    </row>
-    <row r="3" s="58" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="59"/>
-      <c r="D3" s="0"/>
-    </row>
-    <row r="4" s="58" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="60" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="42"/>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="5.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="43"/>
+      <c r="D3" s="42"/>
+    </row>
+    <row r="4" s="3" customFormat="true" ht="52.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="0"/>
-    </row>
-    <row r="5" s="58" customFormat="true" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="60" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="42"/>
+    </row>
+    <row r="5" s="3" customFormat="true" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="0"/>
-    </row>
-    <row r="6" s="58" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="60" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="42"/>
+    </row>
+    <row r="6" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="0"/>
-    </row>
-    <row r="7" s="58" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="60" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="42"/>
+    </row>
+    <row r="7" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="0"/>
-    </row>
-    <row r="8" s="58" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="60" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="42"/>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="0"/>
-    </row>
-    <row r="9" s="58" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="62" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="0"/>
-    </row>
-    <row r="10" s="58" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="62" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="42"/>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="0"/>
-    </row>
-    <row r="11" s="58" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="62" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="42"/>
+    </row>
+    <row r="11" s="3" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="44" t="s">
         <v>363</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="0"/>
-    </row>
-    <row r="12" s="58" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="60" t="s">
+      <c r="D11" s="42"/>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="0"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="64"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
+      <c r="A13" s="45"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="47" t="s">
         <v>364</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="41" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="48" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="49" t="s">
         <v>369</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="50" t="s">
         <v>370</v>
       </c>
-      <c r="C17" s="70" t="n">
+      <c r="C17" s="51" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="50" t="s">
         <v>372</v>
       </c>
-      <c r="C18" s="71" t="n">
+      <c r="C18" s="52" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="49" t="s">
         <v>373</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="50" t="s">
         <v>374</v>
       </c>
-      <c r="C19" s="71" t="n">
+      <c r="C19" s="52" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="49" t="s">
         <v>375</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="50" t="s">
         <v>376</v>
       </c>
-      <c r="C20" s="70" t="n">
+      <c r="C20" s="51" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="49" t="s">
         <v>377</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="50" t="s">
         <v>378</v>
       </c>
-      <c r="C21" s="70" t="n">
+      <c r="C21" s="51" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="50" t="s">
         <v>380</v>
       </c>
-      <c r="C22" s="70" t="n">
+      <c r="C22" s="51" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="68" t="s">
+    <row r="23" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="49" t="s">
         <v>381</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="50" t="s">
         <v>382</v>
       </c>
-      <c r="C23" s="70" t="n">
+      <c r="C23" s="51" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="53" t="s">
         <v>383</v>
       </c>
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="53" t="s">
         <v>384</v>
       </c>
-      <c r="C24" s="73" t="n">
+      <c r="C24" s="54" t="n">
         <f aca="false">SUM(C17:C23)</f>
         <v>139</v>
       </c>

--- a/public/docs/fase1/product_backlog_ajuptel.xlsx
+++ b/public/docs/fase1/product_backlog_ajuptel.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="BACKLOG" sheetId="1" state="visible" r:id="rId3"/>
@@ -280,7 +280,7 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">Por Iniciar</t>
+    <t xml:space="preserve">Completada</t>
   </si>
   <si>
     <t xml:space="preserve">• Mensaje de error claro si las credenciales son incorrectas (sin revelar si el usuario existe).</t>
@@ -2909,7 +2909,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2996,6 +2996,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3168,7 +3174,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3257,6 +3263,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3289,11 +3299,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3317,7 +3327,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3377,7 +3387,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3609,9 +3619,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1425960</xdr:colOff>
+      <xdr:colOff>1425600</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>858240</xdr:rowOff>
+      <xdr:rowOff>857880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3626,7 +3636,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="10617480" cy="858240"/>
+          <a:ext cx="10617120" cy="857880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3653,9 +3663,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2519640</xdr:colOff>
+      <xdr:colOff>2520000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>768600</xdr:rowOff>
+      <xdr:rowOff>768240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3670,7 +3680,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26640" y="195480"/>
-          <a:ext cx="7426440" cy="573120"/>
+          <a:ext cx="7426080" cy="572760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3697,9 +3707,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1043280</xdr:colOff>
+      <xdr:colOff>1042920</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>654840</xdr:rowOff>
+      <xdr:rowOff>654480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3714,7 +3724,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="95400"/>
-          <a:ext cx="6611760" cy="559440"/>
+          <a:ext cx="6611400" cy="559080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4226,7 +4236,7 @@
       <c r="M19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="21" t="s">
+      <c r="N19" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O19" s="21"/>
@@ -4301,7 +4311,7 @@
       <c r="M22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="21" t="s">
+      <c r="N22" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O22" s="21"/>
@@ -4346,7 +4356,7 @@
       <c r="O24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="23" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="17" t="s">
@@ -4385,13 +4395,13 @@
       <c r="M25" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="21" t="s">
+      <c r="N25" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22"/>
+      <c r="A26" s="23"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="19"/>
@@ -4410,7 +4420,7 @@
       <c r="O26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
+      <c r="A27" s="23"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="19"/>
@@ -4429,7 +4439,7 @@
       <c r="O27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="19"/>
@@ -4448,7 +4458,7 @@
       <c r="O28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="19"/>
@@ -4467,7 +4477,7 @@
       <c r="O29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="19"/>
@@ -4504,7 +4514,7 @@
       <c r="O30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="19"/>
@@ -4523,7 +4533,7 @@
       <c r="O31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="19"/>
@@ -4531,7 +4541,7 @@
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
-      <c r="I32" s="23" t="s">
+      <c r="I32" s="24" t="s">
         <v>80</v>
       </c>
       <c r="J32" s="21"/>
@@ -4542,7 +4552,7 @@
       <c r="O32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22"/>
+      <c r="A33" s="23"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="19"/>
@@ -4573,13 +4583,13 @@
       <c r="M33" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N33" s="21" t="s">
+      <c r="N33" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22"/>
+      <c r="A34" s="23"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="19"/>
@@ -4587,7 +4597,7 @@
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="24" t="s">
         <v>85</v>
       </c>
       <c r="J34" s="21"/>
@@ -4598,7 +4608,7 @@
       <c r="O34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22"/>
+      <c r="A35" s="23"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="19"/>
@@ -4606,7 +4616,7 @@
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
-      <c r="I35" s="23" t="s">
+      <c r="I35" s="24" t="s">
         <v>86</v>
       </c>
       <c r="J35" s="21"/>
@@ -4617,7 +4627,7 @@
       <c r="O35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22"/>
+      <c r="A36" s="23"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="19"/>
@@ -4633,7 +4643,7 @@
       <c r="H36" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="24" t="s">
         <v>91</v>
       </c>
       <c r="J36" s="21" t="s">
@@ -4648,13 +4658,13 @@
       <c r="M36" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="21" t="s">
+      <c r="N36" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22"/>
+      <c r="A37" s="23"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="19"/>
@@ -4662,7 +4672,7 @@
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
-      <c r="I37" s="23" t="s">
+      <c r="I37" s="24" t="s">
         <v>92</v>
       </c>
       <c r="J37" s="21"/>
@@ -4673,7 +4683,7 @@
       <c r="O37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22"/>
+      <c r="A38" s="23"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="19"/>
@@ -4681,7 +4691,7 @@
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
-      <c r="I38" s="23" t="s">
+      <c r="I38" s="24" t="s">
         <v>93</v>
       </c>
       <c r="J38" s="21"/>
@@ -4692,7 +4702,7 @@
       <c r="O38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="25" t="s">
         <v>94</v>
       </c>
       <c r="B39" s="19" t="s">
@@ -4731,13 +4741,13 @@
       <c r="M39" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N39" s="21" t="s">
+      <c r="N39" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="24"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
@@ -4745,7 +4755,7 @@
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
-      <c r="I40" s="23" t="s">
+      <c r="I40" s="24" t="s">
         <v>102</v>
       </c>
       <c r="J40" s="21"/>
@@ -4756,7 +4766,7 @@
       <c r="O40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
       <c r="D41" s="19"/>
@@ -4764,7 +4774,7 @@
       <c r="F41" s="19"/>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
-      <c r="I41" s="23" t="s">
+      <c r="I41" s="24" t="s">
         <v>103</v>
       </c>
       <c r="J41" s="21"/>
@@ -4775,7 +4785,7 @@
       <c r="O41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="24"/>
+      <c r="A42" s="25"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
@@ -4806,13 +4816,13 @@
       <c r="M42" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N42" s="21" t="s">
+      <c r="N42" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="24"/>
+      <c r="A43" s="25"/>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
@@ -4820,7 +4830,7 @@
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
       <c r="H43" s="19"/>
-      <c r="I43" s="23" t="s">
+      <c r="I43" s="24" t="s">
         <v>108</v>
       </c>
       <c r="J43" s="21"/>
@@ -4831,7 +4841,7 @@
       <c r="O43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="24"/>
+      <c r="A44" s="25"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
@@ -4839,7 +4849,7 @@
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
       <c r="H44" s="19"/>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="24" t="s">
         <v>109</v>
       </c>
       <c r="J44" s="21"/>
@@ -4850,7 +4860,7 @@
       <c r="O44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="24"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
@@ -4881,13 +4891,13 @@
       <c r="M45" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N45" s="21" t="s">
+      <c r="N45" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O45" s="21"/>
     </row>
     <row r="46" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="24"/>
+      <c r="A46" s="25"/>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
@@ -4906,7 +4916,7 @@
       <c r="O46" s="21"/>
     </row>
     <row r="47" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="24"/>
+      <c r="A47" s="25"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
@@ -4925,7 +4935,7 @@
       <c r="O47" s="21"/>
     </row>
     <row r="48" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="24"/>
+      <c r="A48" s="25"/>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
@@ -4944,7 +4954,7 @@
       <c r="O48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="24"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
@@ -4963,7 +4973,7 @@
       <c r="O49" s="21"/>
     </row>
     <row r="50" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="24"/>
+      <c r="A50" s="25"/>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
       <c r="D50" s="19"/>
@@ -4982,7 +4992,7 @@
       <c r="O50" s="21"/>
     </row>
     <row r="51" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="24"/>
+      <c r="A51" s="25"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
@@ -4998,7 +5008,7 @@
       <c r="H51" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="I51" s="23" t="s">
+      <c r="I51" s="24" t="s">
         <v>123</v>
       </c>
       <c r="J51" s="21" t="s">
@@ -5013,13 +5023,13 @@
       <c r="M51" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N51" s="21" t="s">
+      <c r="N51" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="24"/>
+      <c r="A52" s="25"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
       <c r="D52" s="19"/>
@@ -5027,7 +5037,7 @@
       <c r="F52" s="19"/>
       <c r="G52" s="19"/>
       <c r="H52" s="19"/>
-      <c r="I52" s="23" t="s">
+      <c r="I52" s="24" t="s">
         <v>125</v>
       </c>
       <c r="J52" s="21"/>
@@ -5038,7 +5048,7 @@
       <c r="O52" s="21"/>
     </row>
     <row r="53" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="24"/>
+      <c r="A53" s="25"/>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
@@ -5046,7 +5056,7 @@
       <c r="F53" s="19"/>
       <c r="G53" s="19"/>
       <c r="H53" s="19"/>
-      <c r="I53" s="23" t="s">
+      <c r="I53" s="24" t="s">
         <v>126</v>
       </c>
       <c r="J53" s="21"/>
@@ -5057,7 +5067,7 @@
       <c r="O53" s="21"/>
     </row>
     <row r="54" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="24"/>
+      <c r="A54" s="25"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
       <c r="D54" s="19"/>
@@ -5065,7 +5075,7 @@
       <c r="F54" s="19"/>
       <c r="G54" s="19"/>
       <c r="H54" s="19"/>
-      <c r="I54" s="23" t="s">
+      <c r="I54" s="24" t="s">
         <v>127</v>
       </c>
       <c r="J54" s="21"/>
@@ -5076,7 +5086,7 @@
       <c r="O54" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="24"/>
+      <c r="A55" s="25"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
@@ -5084,7 +5094,7 @@
       <c r="F55" s="19"/>
       <c r="G55" s="19"/>
       <c r="H55" s="19"/>
-      <c r="I55" s="23" t="s">
+      <c r="I55" s="24" t="s">
         <v>128</v>
       </c>
       <c r="J55" s="21"/>
@@ -5095,7 +5105,7 @@
       <c r="O55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="26" t="s">
         <v>129</v>
       </c>
       <c r="B56" s="19" t="s">
@@ -5134,13 +5144,13 @@
       <c r="M56" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N56" s="21" t="s">
+      <c r="N56" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O56" s="21"/>
     </row>
     <row r="57" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="25"/>
+      <c r="A57" s="26"/>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
@@ -5148,7 +5158,7 @@
       <c r="F57" s="19"/>
       <c r="G57" s="19"/>
       <c r="H57" s="19"/>
-      <c r="I57" s="23" t="s">
+      <c r="I57" s="24" t="s">
         <v>138</v>
       </c>
       <c r="J57" s="21"/>
@@ -5159,7 +5169,7 @@
       <c r="O57" s="21"/>
     </row>
     <row r="58" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="25"/>
+      <c r="A58" s="26"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
@@ -5167,7 +5177,7 @@
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
-      <c r="I58" s="23" t="s">
+      <c r="I58" s="24" t="s">
         <v>139</v>
       </c>
       <c r="J58" s="21"/>
@@ -5178,7 +5188,7 @@
       <c r="O58" s="21"/>
     </row>
     <row r="59" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="25"/>
+      <c r="A59" s="26"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
@@ -5186,7 +5196,7 @@
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
-      <c r="I59" s="23" t="s">
+      <c r="I59" s="24" t="s">
         <v>140</v>
       </c>
       <c r="J59" s="21"/>
@@ -5197,7 +5207,7 @@
       <c r="O59" s="21"/>
     </row>
     <row r="60" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="25"/>
+      <c r="A60" s="26"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
@@ -5228,13 +5238,13 @@
       <c r="M60" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N60" s="21" t="s">
+      <c r="N60" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="25"/>
+      <c r="A61" s="26"/>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
@@ -5242,7 +5252,7 @@
       <c r="F61" s="19"/>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
-      <c r="I61" s="23" t="s">
+      <c r="I61" s="24" t="s">
         <v>147</v>
       </c>
       <c r="J61" s="21"/>
@@ -5253,7 +5263,7 @@
       <c r="O61" s="21"/>
     </row>
     <row r="62" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="25"/>
+      <c r="A62" s="26"/>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
@@ -5261,7 +5271,7 @@
       <c r="F62" s="19"/>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
-      <c r="I62" s="23" t="s">
+      <c r="I62" s="24" t="s">
         <v>148</v>
       </c>
       <c r="J62" s="21"/>
@@ -5272,7 +5282,7 @@
       <c r="O62" s="21"/>
     </row>
     <row r="63" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="26" t="s">
+      <c r="A63" s="27" t="s">
         <v>149</v>
       </c>
       <c r="B63" s="19" t="s">
@@ -5311,13 +5321,13 @@
       <c r="M63" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N63" s="21" t="s">
+      <c r="N63" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O63" s="21"/>
     </row>
     <row r="64" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="26"/>
+      <c r="A64" s="27"/>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
@@ -5325,7 +5335,7 @@
       <c r="F64" s="19"/>
       <c r="G64" s="19"/>
       <c r="H64" s="19"/>
-      <c r="I64" s="23" t="s">
+      <c r="I64" s="24" t="s">
         <v>159</v>
       </c>
       <c r="J64" s="21"/>
@@ -5336,7 +5346,7 @@
       <c r="O64" s="21"/>
     </row>
     <row r="65" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="26"/>
+      <c r="A65" s="27"/>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
@@ -5344,7 +5354,7 @@
       <c r="F65" s="19"/>
       <c r="G65" s="19"/>
       <c r="H65" s="19"/>
-      <c r="I65" s="23" t="s">
+      <c r="I65" s="24" t="s">
         <v>160</v>
       </c>
       <c r="J65" s="21"/>
@@ -5355,7 +5365,7 @@
       <c r="O65" s="21"/>
     </row>
     <row r="66" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="26"/>
+      <c r="A66" s="27"/>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
@@ -5386,13 +5396,13 @@
       <c r="M66" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N66" s="21" t="s">
+      <c r="N66" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O66" s="21"/>
     </row>
     <row r="67" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="26"/>
+      <c r="A67" s="27"/>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
@@ -5400,7 +5410,7 @@
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
-      <c r="I67" s="23" t="s">
+      <c r="I67" s="24" t="s">
         <v>165</v>
       </c>
       <c r="J67" s="21"/>
@@ -5411,7 +5421,7 @@
       <c r="O67" s="21"/>
     </row>
     <row r="68" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="26"/>
+      <c r="A68" s="27"/>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
@@ -5419,7 +5429,7 @@
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
       <c r="H68" s="19"/>
-      <c r="I68" s="23" t="s">
+      <c r="I68" s="24" t="s">
         <v>166</v>
       </c>
       <c r="J68" s="21"/>
@@ -5430,7 +5440,7 @@
       <c r="O68" s="21"/>
     </row>
     <row r="69" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="28" t="s">
         <v>167</v>
       </c>
       <c r="B69" s="19" t="s">
@@ -5469,13 +5479,13 @@
       <c r="M69" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N69" s="21" t="s">
+      <c r="N69" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="27"/>
+      <c r="A70" s="28"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
@@ -5494,7 +5504,7 @@
       <c r="O70" s="21"/>
     </row>
     <row r="71" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="27"/>
+      <c r="A71" s="28"/>
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
@@ -5513,7 +5523,7 @@
       <c r="O71" s="21"/>
     </row>
     <row r="72" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="27"/>
+      <c r="A72" s="28"/>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
@@ -5521,7 +5531,7 @@
       <c r="F72" s="18"/>
       <c r="G72" s="18"/>
       <c r="H72" s="18"/>
-      <c r="I72" s="23" t="s">
+      <c r="I72" s="24" t="s">
         <v>178</v>
       </c>
       <c r="J72" s="21"/>
@@ -5532,7 +5542,7 @@
       <c r="O72" s="21"/>
     </row>
     <row r="73" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="27"/>
+      <c r="A73" s="28"/>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
@@ -5540,7 +5550,7 @@
       <c r="F73" s="18"/>
       <c r="G73" s="18"/>
       <c r="H73" s="18"/>
-      <c r="I73" s="23" t="s">
+      <c r="I73" s="24" t="s">
         <v>179</v>
       </c>
       <c r="J73" s="21"/>
@@ -5551,7 +5561,7 @@
       <c r="O73" s="21"/>
     </row>
     <row r="74" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="27"/>
+      <c r="A74" s="28"/>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
@@ -5582,13 +5592,13 @@
       <c r="M74" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N74" s="21" t="s">
+      <c r="N74" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O74" s="21"/>
     </row>
     <row r="75" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="27"/>
+      <c r="A75" s="28"/>
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
@@ -5607,7 +5617,7 @@
       <c r="O75" s="21"/>
     </row>
     <row r="76" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="27"/>
+      <c r="A76" s="28"/>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
@@ -5626,7 +5636,7 @@
       <c r="O76" s="21"/>
     </row>
     <row r="77" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="27"/>
+      <c r="A77" s="28"/>
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
@@ -5645,7 +5655,7 @@
       <c r="O77" s="21"/>
     </row>
     <row r="78" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="27"/>
+      <c r="A78" s="28"/>
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
@@ -5653,7 +5663,7 @@
       <c r="F78" s="18"/>
       <c r="G78" s="18"/>
       <c r="H78" s="18"/>
-      <c r="I78" s="23" t="s">
+      <c r="I78" s="24" t="s">
         <v>189</v>
       </c>
       <c r="J78" s="21"/>
@@ -5663,8 +5673,8 @@
       <c r="N78" s="21"/>
       <c r="O78" s="21"/>
     </row>
-    <row r="79" s="28" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="27"/>
+    <row r="79" s="29" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="28"/>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
@@ -5680,7 +5690,7 @@
       <c r="H79" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="I79" s="23" t="s">
+      <c r="I79" s="24" t="s">
         <v>194</v>
       </c>
       <c r="J79" s="21" t="s">
@@ -5695,7 +5705,7 @@
       <c r="M79" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N79" s="21" t="s">
+      <c r="N79" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O79" s="21"/>
@@ -5703,7 +5713,7 @@
       <c r="XFD79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="27"/>
+      <c r="A80" s="28"/>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
@@ -5711,7 +5721,7 @@
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
       <c r="H80" s="17"/>
-      <c r="I80" s="23" t="s">
+      <c r="I80" s="24" t="s">
         <v>196</v>
       </c>
       <c r="J80" s="21"/>
@@ -5722,7 +5732,7 @@
       <c r="O80" s="21"/>
     </row>
     <row r="81" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="27"/>
+      <c r="A81" s="28"/>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
@@ -5730,7 +5740,7 @@
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
       <c r="H81" s="17"/>
-      <c r="I81" s="23" t="s">
+      <c r="I81" s="24" t="s">
         <v>197</v>
       </c>
       <c r="J81" s="21"/>
@@ -5741,7 +5751,7 @@
       <c r="O81" s="21"/>
     </row>
     <row r="82" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="27"/>
+      <c r="A82" s="28"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
@@ -5749,7 +5759,7 @@
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
       <c r="H82" s="17"/>
-      <c r="I82" s="23" t="s">
+      <c r="I82" s="24" t="s">
         <v>198</v>
       </c>
       <c r="J82" s="21"/>
@@ -5760,7 +5770,7 @@
       <c r="O82" s="21"/>
     </row>
     <row r="83" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="27"/>
+      <c r="A83" s="28"/>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
@@ -5768,7 +5778,7 @@
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
       <c r="H83" s="17"/>
-      <c r="I83" s="23" t="s">
+      <c r="I83" s="24" t="s">
         <v>199</v>
       </c>
       <c r="J83" s="21"/>
@@ -5779,7 +5789,7 @@
       <c r="O83" s="21"/>
     </row>
     <row r="84" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="27"/>
+      <c r="A84" s="28"/>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
@@ -5795,7 +5805,7 @@
       <c r="H84" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="I84" s="23" t="s">
+      <c r="I84" s="24" t="s">
         <v>203</v>
       </c>
       <c r="J84" s="21" t="s">
@@ -5810,13 +5820,13 @@
       <c r="M84" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N84" s="21" t="s">
+      <c r="N84" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O84" s="21"/>
     </row>
     <row r="85" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="27"/>
+      <c r="A85" s="28"/>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
@@ -5824,7 +5834,7 @@
       <c r="F85" s="17"/>
       <c r="G85" s="17"/>
       <c r="H85" s="17"/>
-      <c r="I85" s="23" t="s">
+      <c r="I85" s="24" t="s">
         <v>204</v>
       </c>
       <c r="J85" s="21"/>
@@ -5835,7 +5845,7 @@
       <c r="O85" s="21"/>
     </row>
     <row r="86" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="27"/>
+      <c r="A86" s="28"/>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
@@ -5843,7 +5853,7 @@
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
       <c r="H86" s="17"/>
-      <c r="I86" s="23" t="s">
+      <c r="I86" s="24" t="s">
         <v>205</v>
       </c>
       <c r="J86" s="21"/>
@@ -5854,7 +5864,7 @@
       <c r="O86" s="21"/>
     </row>
     <row r="87" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="27"/>
+      <c r="A87" s="28"/>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
@@ -5862,7 +5872,7 @@
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
       <c r="H87" s="17"/>
-      <c r="I87" s="23" t="s">
+      <c r="I87" s="24" t="s">
         <v>206</v>
       </c>
       <c r="J87" s="21"/>
@@ -5873,7 +5883,7 @@
       <c r="O87" s="21"/>
     </row>
     <row r="88" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="27"/>
+      <c r="A88" s="28"/>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
@@ -5881,7 +5891,7 @@
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
       <c r="H88" s="17"/>
-      <c r="I88" s="23" t="s">
+      <c r="I88" s="24" t="s">
         <v>198</v>
       </c>
       <c r="J88" s="21"/>
@@ -5892,7 +5902,7 @@
       <c r="O88" s="21"/>
     </row>
     <row r="89" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="27"/>
+      <c r="A89" s="28"/>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
@@ -5908,7 +5918,7 @@
       <c r="H89" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="I89" s="23" t="s">
+      <c r="I89" s="24" t="s">
         <v>210</v>
       </c>
       <c r="J89" s="21" t="s">
@@ -5923,13 +5933,13 @@
       <c r="M89" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N89" s="21" t="s">
+      <c r="N89" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O89" s="21"/>
     </row>
     <row r="90" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="27"/>
+      <c r="A90" s="28"/>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
@@ -5937,7 +5947,7 @@
       <c r="F90" s="21"/>
       <c r="G90" s="21"/>
       <c r="H90" s="21"/>
-      <c r="I90" s="23" t="s">
+      <c r="I90" s="24" t="s">
         <v>212</v>
       </c>
       <c r="J90" s="21"/>
@@ -5948,7 +5958,7 @@
       <c r="O90" s="21"/>
     </row>
     <row r="91" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="27"/>
+      <c r="A91" s="28"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
@@ -5956,7 +5966,7 @@
       <c r="F91" s="21"/>
       <c r="G91" s="21"/>
       <c r="H91" s="21"/>
-      <c r="I91" s="23" t="s">
+      <c r="I91" s="24" t="s">
         <v>213</v>
       </c>
       <c r="J91" s="21"/>
@@ -5967,7 +5977,7 @@
       <c r="O91" s="21"/>
     </row>
     <row r="92" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="27"/>
+      <c r="A92" s="28"/>
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
@@ -5975,7 +5985,7 @@
       <c r="F92" s="21"/>
       <c r="G92" s="21"/>
       <c r="H92" s="21"/>
-      <c r="I92" s="23" t="s">
+      <c r="I92" s="24" t="s">
         <v>198</v>
       </c>
       <c r="J92" s="21"/>
@@ -5986,7 +5996,7 @@
       <c r="O92" s="21"/>
     </row>
     <row r="93" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="27"/>
+      <c r="A93" s="28"/>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
@@ -5994,7 +6004,7 @@
       <c r="F93" s="21"/>
       <c r="G93" s="21"/>
       <c r="H93" s="21"/>
-      <c r="I93" s="23" t="s">
+      <c r="I93" s="24" t="s">
         <v>214</v>
       </c>
       <c r="J93" s="21"/>
@@ -6005,7 +6015,7 @@
       <c r="O93" s="21"/>
     </row>
     <row r="94" customFormat="false" ht="35.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="27"/>
+      <c r="A94" s="28"/>
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
@@ -6021,7 +6031,7 @@
       <c r="H94" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="I94" s="23" t="s">
+      <c r="I94" s="24" t="s">
         <v>219</v>
       </c>
       <c r="J94" s="21" t="s">
@@ -6036,13 +6046,13 @@
       <c r="M94" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N94" s="21" t="s">
+      <c r="N94" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="O94" s="29"/>
+      <c r="O94" s="30"/>
     </row>
     <row r="95" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="27"/>
+      <c r="A95" s="28"/>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
@@ -6050,7 +6060,7 @@
       <c r="F95" s="21"/>
       <c r="G95" s="21"/>
       <c r="H95" s="21"/>
-      <c r="I95" s="23" t="s">
+      <c r="I95" s="24" t="s">
         <v>220</v>
       </c>
       <c r="J95" s="21"/>
@@ -6061,7 +6071,7 @@
       <c r="O95" s="21"/>
     </row>
     <row r="96" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="27"/>
+      <c r="A96" s="28"/>
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
@@ -6069,7 +6079,7 @@
       <c r="F96" s="21"/>
       <c r="G96" s="21"/>
       <c r="H96" s="21"/>
-      <c r="I96" s="23" t="s">
+      <c r="I96" s="24" t="s">
         <v>221</v>
       </c>
       <c r="J96" s="21"/>
@@ -6080,7 +6090,7 @@
       <c r="O96" s="21"/>
     </row>
     <row r="97" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="27"/>
+      <c r="A97" s="28"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
@@ -6088,7 +6098,7 @@
       <c r="F97" s="21"/>
       <c r="G97" s="21"/>
       <c r="H97" s="21"/>
-      <c r="I97" s="23" t="s">
+      <c r="I97" s="24" t="s">
         <v>222</v>
       </c>
       <c r="J97" s="21"/>
@@ -6099,7 +6109,7 @@
       <c r="O97" s="21"/>
     </row>
     <row r="98" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="27"/>
+      <c r="A98" s="28"/>
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
@@ -6107,7 +6117,7 @@
       <c r="F98" s="21"/>
       <c r="G98" s="21"/>
       <c r="H98" s="21"/>
-      <c r="I98" s="23" t="s">
+      <c r="I98" s="24" t="s">
         <v>223</v>
       </c>
       <c r="J98" s="21"/>
@@ -6118,7 +6128,7 @@
       <c r="O98" s="21"/>
     </row>
     <row r="99" customFormat="false" ht="71.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="27"/>
+      <c r="A99" s="28"/>
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
@@ -6134,7 +6144,7 @@
       <c r="H99" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="I99" s="30" t="s">
+      <c r="I99" s="31" t="s">
         <v>227</v>
       </c>
       <c r="J99" s="21" t="s">
@@ -6149,13 +6159,13 @@
       <c r="M99" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N99" s="21" t="s">
+      <c r="N99" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O99" s="21"/>
     </row>
     <row r="100" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="27"/>
+      <c r="A100" s="28"/>
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
@@ -6163,7 +6173,7 @@
       <c r="F100" s="21"/>
       <c r="G100" s="21"/>
       <c r="H100" s="21"/>
-      <c r="I100" s="30" t="s">
+      <c r="I100" s="31" t="s">
         <v>228</v>
       </c>
       <c r="J100" s="21"/>
@@ -6174,7 +6184,7 @@
       <c r="O100" s="21"/>
     </row>
     <row r="101" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="27"/>
+      <c r="A101" s="28"/>
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
@@ -6182,7 +6192,7 @@
       <c r="F101" s="21"/>
       <c r="G101" s="21"/>
       <c r="H101" s="21"/>
-      <c r="I101" s="31" t="s">
+      <c r="I101" s="32" t="s">
         <v>229</v>
       </c>
       <c r="J101" s="21"/>
@@ -6193,7 +6203,7 @@
       <c r="O101" s="21"/>
     </row>
     <row r="102" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="27"/>
+      <c r="A102" s="28"/>
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
@@ -6201,7 +6211,7 @@
       <c r="F102" s="21"/>
       <c r="G102" s="21"/>
       <c r="H102" s="21"/>
-      <c r="I102" s="30" t="s">
+      <c r="I102" s="31" t="s">
         <v>230</v>
       </c>
       <c r="J102" s="21"/>
@@ -6212,7 +6222,7 @@
       <c r="O102" s="21"/>
     </row>
     <row r="103" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="27"/>
+      <c r="A103" s="28"/>
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
@@ -6220,7 +6230,7 @@
       <c r="F103" s="21"/>
       <c r="G103" s="21"/>
       <c r="H103" s="21"/>
-      <c r="I103" s="31" t="s">
+      <c r="I103" s="32" t="s">
         <v>231</v>
       </c>
       <c r="J103" s="21"/>
@@ -6231,7 +6241,7 @@
       <c r="O103" s="21"/>
     </row>
     <row r="104" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="32" t="s">
+      <c r="A104" s="33" t="s">
         <v>232</v>
       </c>
       <c r="B104" s="17" t="s">
@@ -6270,13 +6280,13 @@
       <c r="M104" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N104" s="21" t="s">
+      <c r="N104" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O104" s="21"/>
     </row>
     <row r="105" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="32"/>
+      <c r="A105" s="33"/>
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
@@ -6295,7 +6305,7 @@
       <c r="O105" s="21"/>
     </row>
     <row r="106" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="32"/>
+      <c r="A106" s="33"/>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
@@ -6314,7 +6324,7 @@
       <c r="O106" s="21"/>
     </row>
     <row r="107" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="32"/>
+      <c r="A107" s="33"/>
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
@@ -6333,7 +6343,7 @@
       <c r="O107" s="21"/>
     </row>
     <row r="108" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="32"/>
+      <c r="A108" s="33"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
@@ -6352,7 +6362,7 @@
       <c r="O108" s="21"/>
     </row>
     <row r="109" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="32"/>
+      <c r="A109" s="33"/>
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -6360,7 +6370,7 @@
       <c r="F109" s="19"/>
       <c r="G109" s="19"/>
       <c r="H109" s="20"/>
-      <c r="I109" s="23" t="s">
+      <c r="I109" s="24" t="s">
         <v>245</v>
       </c>
       <c r="J109" s="21"/>
@@ -6371,7 +6381,7 @@
       <c r="O109" s="21"/>
     </row>
     <row r="110" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="32"/>
+      <c r="A110" s="33"/>
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
       <c r="D110" s="17"/>
@@ -6390,7 +6400,7 @@
       <c r="O110" s="21"/>
     </row>
     <row r="111" customFormat="false" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="32"/>
+      <c r="A111" s="33"/>
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
@@ -6421,13 +6431,13 @@
       <c r="M111" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N111" s="21" t="s">
+      <c r="N111" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O111" s="21"/>
     </row>
     <row r="112" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="32"/>
+      <c r="A112" s="33"/>
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
       <c r="D112" s="17"/>
@@ -6446,7 +6456,7 @@
       <c r="O112" s="21"/>
     </row>
     <row r="113" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="32"/>
+      <c r="A113" s="33"/>
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
       <c r="D113" s="17"/>
@@ -6465,7 +6475,7 @@
       <c r="O113" s="21"/>
     </row>
     <row r="114" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="32"/>
+      <c r="A114" s="33"/>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
       <c r="D114" s="17"/>
@@ -6484,7 +6494,7 @@
       <c r="O114" s="21"/>
     </row>
     <row r="115" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="32"/>
+      <c r="A115" s="33"/>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
@@ -6503,7 +6513,7 @@
       <c r="O115" s="21"/>
     </row>
     <row r="116" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="32"/>
+      <c r="A116" s="33"/>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
@@ -6511,7 +6521,7 @@
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
       <c r="H116" s="17"/>
-      <c r="I116" s="23" t="s">
+      <c r="I116" s="24" t="s">
         <v>256</v>
       </c>
       <c r="J116" s="21"/>
@@ -6522,7 +6532,7 @@
       <c r="O116" s="21"/>
     </row>
     <row r="117" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="32"/>
+      <c r="A117" s="33"/>
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
       <c r="D117" s="17"/>
@@ -6541,7 +6551,7 @@
       <c r="O117" s="21"/>
     </row>
     <row r="118" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="32"/>
+      <c r="A118" s="33"/>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
       <c r="D118" s="17"/>
@@ -6572,13 +6582,13 @@
       <c r="M118" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N118" s="21" t="s">
+      <c r="N118" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O118" s="21"/>
     </row>
     <row r="119" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="32"/>
+      <c r="A119" s="33"/>
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
       <c r="D119" s="17"/>
@@ -6597,7 +6607,7 @@
       <c r="O119" s="21"/>
     </row>
     <row r="120" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="32"/>
+      <c r="A120" s="33"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
@@ -6616,7 +6626,7 @@
       <c r="O120" s="21"/>
     </row>
     <row r="121" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="32"/>
+      <c r="A121" s="33"/>
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
       <c r="D121" s="17"/>
@@ -6635,7 +6645,7 @@
       <c r="O121" s="21"/>
     </row>
     <row r="122" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="32"/>
+      <c r="A122" s="33"/>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
       <c r="D122" s="17"/>
@@ -6654,7 +6664,7 @@
       <c r="O122" s="21"/>
     </row>
     <row r="123" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="32"/>
+      <c r="A123" s="33"/>
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
       <c r="D123" s="17"/>
@@ -6673,7 +6683,7 @@
       <c r="O123" s="21"/>
     </row>
     <row r="124" customFormat="false" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="32"/>
+      <c r="A124" s="33"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
       <c r="D124" s="17"/>
@@ -6704,13 +6714,13 @@
       <c r="M124" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N124" s="21" t="s">
+      <c r="N124" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O124" s="21"/>
     </row>
     <row r="125" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="32"/>
+      <c r="A125" s="33"/>
       <c r="B125" s="17"/>
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
@@ -6729,7 +6739,7 @@
       <c r="O125" s="21"/>
     </row>
     <row r="126" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="32"/>
+      <c r="A126" s="33"/>
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
       <c r="D126" s="17"/>
@@ -6737,7 +6747,7 @@
       <c r="F126" s="19"/>
       <c r="G126" s="19"/>
       <c r="H126" s="19"/>
-      <c r="I126" s="23" t="s">
+      <c r="I126" s="24" t="s">
         <v>271</v>
       </c>
       <c r="J126" s="21"/>
@@ -6748,7 +6758,7 @@
       <c r="O126" s="21"/>
     </row>
     <row r="127" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="32"/>
+      <c r="A127" s="33"/>
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
       <c r="D127" s="17"/>
@@ -6766,8 +6776,8 @@
       <c r="N127" s="21"/>
       <c r="O127" s="21"/>
     </row>
-    <row r="128" s="34" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="33" t="s">
+    <row r="128" s="35" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="34" t="s">
         <v>273</v>
       </c>
       <c r="B128" s="17" t="s">
@@ -6806,15 +6816,15 @@
       <c r="M128" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N128" s="21" t="s">
+      <c r="N128" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O128" s="21"/>
       <c r="XFC128" s="3"/>
       <c r="XFD128" s="1"/>
     </row>
-    <row r="129" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="33"/>
+    <row r="129" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="34"/>
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
       <c r="D129" s="17"/>
@@ -6834,8 +6844,8 @@
       <c r="XFC129" s="3"/>
       <c r="XFD129" s="1"/>
     </row>
-    <row r="130" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="33"/>
+    <row r="130" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="34"/>
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
       <c r="D130" s="17"/>
@@ -6855,8 +6865,8 @@
       <c r="XFC130" s="3"/>
       <c r="XFD130" s="1"/>
     </row>
-    <row r="131" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="33"/>
+    <row r="131" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="34"/>
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
       <c r="D131" s="17"/>
@@ -6876,8 +6886,8 @@
       <c r="XFC131" s="3"/>
       <c r="XFD131" s="1"/>
     </row>
-    <row r="132" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="33"/>
+    <row r="132" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="34"/>
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
@@ -6897,8 +6907,8 @@
       <c r="XFC132" s="3"/>
       <c r="XFD132" s="1"/>
     </row>
-    <row r="133" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="33"/>
+    <row r="133" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="34"/>
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
@@ -6918,8 +6928,8 @@
       <c r="XFC133" s="3"/>
       <c r="XFD133" s="1"/>
     </row>
-    <row r="134" s="35" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="33"/>
+    <row r="134" s="36" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="34"/>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
@@ -6950,15 +6960,15 @@
       <c r="M134" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="N134" s="21" t="s">
+      <c r="N134" s="22" t="s">
         <v>45</v>
       </c>
       <c r="O134" s="21"/>
       <c r="XFC134" s="3"/>
       <c r="XFD134" s="1"/>
     </row>
-    <row r="135" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="33"/>
+    <row r="135" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="34"/>
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
       <c r="D135" s="17"/>
@@ -6978,8 +6988,8 @@
       <c r="XFC135" s="3"/>
       <c r="XFD135" s="1"/>
     </row>
-    <row r="136" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="33"/>
+    <row r="136" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="34"/>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
       <c r="D136" s="17"/>
@@ -6999,8 +7009,8 @@
       <c r="XFC136" s="3"/>
       <c r="XFD136" s="1"/>
     </row>
-    <row r="137" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="33"/>
+    <row r="137" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="34"/>
       <c r="B137" s="17"/>
       <c r="C137" s="17"/>
       <c r="D137" s="17"/>
@@ -7020,8 +7030,8 @@
       <c r="XFC137" s="3"/>
       <c r="XFD137" s="1"/>
     </row>
-    <row r="138" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="33"/>
+    <row r="138" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="34"/>
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
       <c r="D138" s="17"/>
@@ -7041,8 +7051,8 @@
       <c r="XFC138" s="3"/>
       <c r="XFD138" s="1"/>
     </row>
-    <row r="139" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="33"/>
+    <row r="139" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="34"/>
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
@@ -7448,13 +7458,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="71.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
@@ -7474,71 +7484,71 @@
       <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="50.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
@@ -7549,52 +7559,52 @@
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="37"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="40" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="40" t="s">
         <v>302</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="41" t="s">
         <v>305</v>
       </c>
     </row>
@@ -7608,16 +7618,16 @@
       <c r="C17" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="24" t="s">
         <v>310</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="24" t="s">
         <v>311</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="24" t="s">
         <v>312</v>
       </c>
     </row>
@@ -7631,16 +7641,16 @@
       <c r="C18" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="24" t="s">
         <v>315</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="24" t="s">
         <v>317</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="24" t="s">
         <v>318</v>
       </c>
     </row>
@@ -7654,16 +7664,16 @@
       <c r="C19" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="24" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="24" t="s">
         <v>324</v>
       </c>
     </row>
@@ -7677,16 +7687,16 @@
       <c r="C20" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="24" t="s">
         <v>327</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="24" t="s">
         <v>328</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="24" t="s">
         <v>329</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="24" t="s">
         <v>330</v>
       </c>
     </row>
@@ -7700,16 +7710,16 @@
       <c r="C21" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="24" t="s">
         <v>333</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="24" t="s">
         <v>334</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="24" t="s">
         <v>335</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="24" t="s">
         <v>336</v>
       </c>
     </row>
@@ -7723,16 +7733,16 @@
       <c r="C22" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="24" t="s">
         <v>340</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="24" t="s">
         <v>341</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="24" t="s">
         <v>342</v>
       </c>
     </row>
@@ -7746,16 +7756,16 @@
       <c r="C23" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="24" t="s">
         <v>346</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="24" t="s">
         <v>347</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="24" t="s">
         <v>348</v>
       </c>
     </row>
@@ -7769,16 +7779,16 @@
       <c r="C24" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="24" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="24" t="s">
         <v>352</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="24" t="s">
         <v>353</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="24" t="s">
         <v>354</v>
       </c>
     </row>
@@ -7792,16 +7802,16 @@
       <c r="C25" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="24" t="s">
         <v>359</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="24" t="s">
         <v>360</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="24" t="s">
         <v>361</v>
       </c>
     </row>
@@ -7839,236 +7849,236 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="41" width="29.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="41" width="49.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="41" width="18.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="5" style="41" width="8.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="41" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="42" width="29.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="42" width="49.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="42" width="18.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="5" style="42" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="42" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
     </row>
     <row r="2" s="3" customFormat="true" ht="68.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="42"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="5.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43"/>
-      <c r="D3" s="42"/>
+      <c r="A3" s="44"/>
+      <c r="D3" s="43"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="52.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="45" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="42"/>
+      <c r="D4" s="43"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="45" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="42"/>
+      <c r="D5" s="43"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="45" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="42"/>
+      <c r="D6" s="43"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="45" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="42"/>
+      <c r="D7" s="43"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="45" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="43"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="45" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="43"/>
     </row>
     <row r="10" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="45" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="43"/>
     </row>
     <row r="11" s="3" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="45" t="s">
         <v>363</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="42"/>
+      <c r="D11" s="43"/>
     </row>
     <row r="12" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="45" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="42"/>
+      <c r="D12" s="43"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>364</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="42" t="s">
         <v>365</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="42" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="49" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="50" t="s">
         <v>369</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="51" t="s">
         <v>370</v>
       </c>
-      <c r="C17" s="51" t="n">
+      <c r="C17" s="52" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="50" t="s">
         <v>371</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="51" t="s">
         <v>372</v>
       </c>
-      <c r="C18" s="52" t="n">
+      <c r="C18" s="53" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="50" t="s">
         <v>373</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="C19" s="52" t="n">
+      <c r="C19" s="53" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="50" t="s">
         <v>375</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="51" t="s">
         <v>376</v>
       </c>
-      <c r="C20" s="51" t="n">
+      <c r="C20" s="52" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="50" t="s">
         <v>377</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="51" t="s">
         <v>378</v>
       </c>
-      <c r="C21" s="51" t="n">
+      <c r="C21" s="52" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="50" t="s">
         <v>379</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="51" t="s">
         <v>380</v>
       </c>
-      <c r="C22" s="51" t="n">
+      <c r="C22" s="52" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="50" t="s">
         <v>381</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="51" t="s">
         <v>382</v>
       </c>
-      <c r="C23" s="51" t="n">
+      <c r="C23" s="52" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="54" t="s">
         <v>383</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="54" t="s">
         <v>384</v>
       </c>
-      <c r="C24" s="54" t="n">
+      <c r="C24" s="55" t="n">
         <f aca="false">SUM(C17:C23)</f>
         <v>139</v>
       </c>

--- a/public/docs/fase1/product_backlog_ajuptel.xlsx
+++ b/public/docs/fase1/product_backlog_ajuptel.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BACKLOG" sheetId="1" state="visible" r:id="rId3"/>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">Actividades/Historias</t>
   </si>
   <si>
-    <t xml:space="preserve">No se estiman puntos de historias</t>
+    <t xml:space="preserve">Observaciones</t>
   </si>
   <si>
     <t xml:space="preserve">Fase de Preparación Técnica </t>
@@ -2909,7 +2909,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2996,12 +2996,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3174,7 +3168,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3263,10 +3257,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3299,11 +3289,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3327,7 +3317,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3387,7 +3377,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3619,9 +3609,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1425600</xdr:colOff>
+      <xdr:colOff>1425240</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>857880</xdr:rowOff>
+      <xdr:rowOff>857520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3636,7 +3626,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="10617120" cy="857880"/>
+          <a:ext cx="10616760" cy="857520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3663,9 +3653,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2520000</xdr:colOff>
+      <xdr:colOff>2519640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>768240</xdr:rowOff>
+      <xdr:rowOff>767880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3680,7 +3670,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26640" y="195480"/>
-          <a:ext cx="7426080" cy="572760"/>
+          <a:ext cx="7425720" cy="572400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3707,9 +3697,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1042920</xdr:colOff>
+      <xdr:colOff>1042560</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>654480</xdr:rowOff>
+      <xdr:rowOff>654120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3724,7 +3714,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="95400"/>
-          <a:ext cx="6611400" cy="559080"/>
+          <a:ext cx="6611040" cy="558720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4236,7 +4226,7 @@
       <c r="M19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="22" t="s">
+      <c r="N19" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O19" s="21"/>
@@ -4311,7 +4301,7 @@
       <c r="M22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="22" t="s">
+      <c r="N22" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O22" s="21"/>
@@ -4356,7 +4346,7 @@
       <c r="O24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="17" t="s">
@@ -4395,13 +4385,13 @@
       <c r="M25" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="22" t="s">
+      <c r="N25" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23"/>
+      <c r="A26" s="22"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="19"/>
@@ -4420,7 +4410,7 @@
       <c r="O26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23"/>
+      <c r="A27" s="22"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="19"/>
@@ -4439,7 +4429,7 @@
       <c r="O27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="19"/>
@@ -4458,7 +4448,7 @@
       <c r="O28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="19"/>
@@ -4477,7 +4467,7 @@
       <c r="O29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="19"/>
@@ -4514,7 +4504,7 @@
       <c r="O30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="19"/>
@@ -4533,7 +4523,7 @@
       <c r="O31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="19"/>
@@ -4541,7 +4531,7 @@
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
-      <c r="I32" s="24" t="s">
+      <c r="I32" s="23" t="s">
         <v>80</v>
       </c>
       <c r="J32" s="21"/>
@@ -4552,7 +4542,7 @@
       <c r="O32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="19"/>
@@ -4583,13 +4573,13 @@
       <c r="M33" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N33" s="22" t="s">
+      <c r="N33" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="19"/>
@@ -4597,7 +4587,7 @@
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
-      <c r="I34" s="24" t="s">
+      <c r="I34" s="23" t="s">
         <v>85</v>
       </c>
       <c r="J34" s="21"/>
@@ -4608,7 +4598,7 @@
       <c r="O34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="19"/>
@@ -4616,7 +4606,7 @@
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
-      <c r="I35" s="24" t="s">
+      <c r="I35" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J35" s="21"/>
@@ -4627,7 +4617,7 @@
       <c r="O35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="19"/>
@@ -4643,7 +4633,7 @@
       <c r="H36" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I36" s="24" t="s">
+      <c r="I36" s="23" t="s">
         <v>91</v>
       </c>
       <c r="J36" s="21" t="s">
@@ -4658,13 +4648,13 @@
       <c r="M36" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="22" t="s">
+      <c r="N36" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="19"/>
@@ -4672,7 +4662,7 @@
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
-      <c r="I37" s="24" t="s">
+      <c r="I37" s="23" t="s">
         <v>92</v>
       </c>
       <c r="J37" s="21"/>
@@ -4683,7 +4673,7 @@
       <c r="O37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="19"/>
@@ -4691,7 +4681,7 @@
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
-      <c r="I38" s="24" t="s">
+      <c r="I38" s="23" t="s">
         <v>93</v>
       </c>
       <c r="J38" s="21"/>
@@ -4702,7 +4692,7 @@
       <c r="O38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="24" t="s">
         <v>94</v>
       </c>
       <c r="B39" s="19" t="s">
@@ -4741,13 +4731,13 @@
       <c r="M39" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N39" s="22" t="s">
+      <c r="N39" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="25"/>
+      <c r="A40" s="24"/>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
@@ -4755,7 +4745,7 @@
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
-      <c r="I40" s="24" t="s">
+      <c r="I40" s="23" t="s">
         <v>102</v>
       </c>
       <c r="J40" s="21"/>
@@ -4766,7 +4756,7 @@
       <c r="O40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25"/>
+      <c r="A41" s="24"/>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
       <c r="D41" s="19"/>
@@ -4774,7 +4764,7 @@
       <c r="F41" s="19"/>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
-      <c r="I41" s="24" t="s">
+      <c r="I41" s="23" t="s">
         <v>103</v>
       </c>
       <c r="J41" s="21"/>
@@ -4785,7 +4775,7 @@
       <c r="O41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25"/>
+      <c r="A42" s="24"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
@@ -4816,13 +4806,13 @@
       <c r="M42" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N42" s="22" t="s">
+      <c r="N42" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="25"/>
+      <c r="A43" s="24"/>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
@@ -4830,7 +4820,7 @@
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
       <c r="H43" s="19"/>
-      <c r="I43" s="24" t="s">
+      <c r="I43" s="23" t="s">
         <v>108</v>
       </c>
       <c r="J43" s="21"/>
@@ -4841,7 +4831,7 @@
       <c r="O43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="25"/>
+      <c r="A44" s="24"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
@@ -4849,7 +4839,7 @@
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
       <c r="H44" s="19"/>
-      <c r="I44" s="24" t="s">
+      <c r="I44" s="23" t="s">
         <v>109</v>
       </c>
       <c r="J44" s="21"/>
@@ -4860,7 +4850,7 @@
       <c r="O44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="25"/>
+      <c r="A45" s="24"/>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
@@ -4891,13 +4881,13 @@
       <c r="M45" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N45" s="22" t="s">
+      <c r="N45" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O45" s="21"/>
     </row>
     <row r="46" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="25"/>
+      <c r="A46" s="24"/>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
@@ -4916,7 +4906,7 @@
       <c r="O46" s="21"/>
     </row>
     <row r="47" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="25"/>
+      <c r="A47" s="24"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
@@ -4935,7 +4925,7 @@
       <c r="O47" s="21"/>
     </row>
     <row r="48" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="25"/>
+      <c r="A48" s="24"/>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
@@ -4954,7 +4944,7 @@
       <c r="O48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="25"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
@@ -4973,7 +4963,7 @@
       <c r="O49" s="21"/>
     </row>
     <row r="50" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="25"/>
+      <c r="A50" s="24"/>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
       <c r="D50" s="19"/>
@@ -4992,7 +4982,7 @@
       <c r="O50" s="21"/>
     </row>
     <row r="51" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="25"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
@@ -5008,7 +4998,7 @@
       <c r="H51" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="I51" s="24" t="s">
+      <c r="I51" s="23" t="s">
         <v>123</v>
       </c>
       <c r="J51" s="21" t="s">
@@ -5023,13 +5013,13 @@
       <c r="M51" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N51" s="22" t="s">
+      <c r="N51" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="25"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
       <c r="D52" s="19"/>
@@ -5037,7 +5027,7 @@
       <c r="F52" s="19"/>
       <c r="G52" s="19"/>
       <c r="H52" s="19"/>
-      <c r="I52" s="24" t="s">
+      <c r="I52" s="23" t="s">
         <v>125</v>
       </c>
       <c r="J52" s="21"/>
@@ -5048,7 +5038,7 @@
       <c r="O52" s="21"/>
     </row>
     <row r="53" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="25"/>
+      <c r="A53" s="24"/>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
@@ -5056,7 +5046,7 @@
       <c r="F53" s="19"/>
       <c r="G53" s="19"/>
       <c r="H53" s="19"/>
-      <c r="I53" s="24" t="s">
+      <c r="I53" s="23" t="s">
         <v>126</v>
       </c>
       <c r="J53" s="21"/>
@@ -5067,7 +5057,7 @@
       <c r="O53" s="21"/>
     </row>
     <row r="54" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="25"/>
+      <c r="A54" s="24"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
       <c r="D54" s="19"/>
@@ -5075,7 +5065,7 @@
       <c r="F54" s="19"/>
       <c r="G54" s="19"/>
       <c r="H54" s="19"/>
-      <c r="I54" s="24" t="s">
+      <c r="I54" s="23" t="s">
         <v>127</v>
       </c>
       <c r="J54" s="21"/>
@@ -5086,7 +5076,7 @@
       <c r="O54" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="25"/>
+      <c r="A55" s="24"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
@@ -5094,7 +5084,7 @@
       <c r="F55" s="19"/>
       <c r="G55" s="19"/>
       <c r="H55" s="19"/>
-      <c r="I55" s="24" t="s">
+      <c r="I55" s="23" t="s">
         <v>128</v>
       </c>
       <c r="J55" s="21"/>
@@ -5105,7 +5095,7 @@
       <c r="O55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="26" t="s">
+      <c r="A56" s="25" t="s">
         <v>129</v>
       </c>
       <c r="B56" s="19" t="s">
@@ -5144,13 +5134,13 @@
       <c r="M56" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N56" s="22" t="s">
+      <c r="N56" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O56" s="21"/>
     </row>
     <row r="57" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="26"/>
+      <c r="A57" s="25"/>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
@@ -5158,7 +5148,7 @@
       <c r="F57" s="19"/>
       <c r="G57" s="19"/>
       <c r="H57" s="19"/>
-      <c r="I57" s="24" t="s">
+      <c r="I57" s="23" t="s">
         <v>138</v>
       </c>
       <c r="J57" s="21"/>
@@ -5169,7 +5159,7 @@
       <c r="O57" s="21"/>
     </row>
     <row r="58" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="26"/>
+      <c r="A58" s="25"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
@@ -5177,7 +5167,7 @@
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
-      <c r="I58" s="24" t="s">
+      <c r="I58" s="23" t="s">
         <v>139</v>
       </c>
       <c r="J58" s="21"/>
@@ -5188,7 +5178,7 @@
       <c r="O58" s="21"/>
     </row>
     <row r="59" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="26"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
@@ -5196,7 +5186,7 @@
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
-      <c r="I59" s="24" t="s">
+      <c r="I59" s="23" t="s">
         <v>140</v>
       </c>
       <c r="J59" s="21"/>
@@ -5207,7 +5197,7 @@
       <c r="O59" s="21"/>
     </row>
     <row r="60" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="26"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
@@ -5238,13 +5228,13 @@
       <c r="M60" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N60" s="22" t="s">
+      <c r="N60" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="26"/>
+      <c r="A61" s="25"/>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
@@ -5252,7 +5242,7 @@
       <c r="F61" s="19"/>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
-      <c r="I61" s="24" t="s">
+      <c r="I61" s="23" t="s">
         <v>147</v>
       </c>
       <c r="J61" s="21"/>
@@ -5263,7 +5253,7 @@
       <c r="O61" s="21"/>
     </row>
     <row r="62" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="26"/>
+      <c r="A62" s="25"/>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
@@ -5271,7 +5261,7 @@
       <c r="F62" s="19"/>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
-      <c r="I62" s="24" t="s">
+      <c r="I62" s="23" t="s">
         <v>148</v>
       </c>
       <c r="J62" s="21"/>
@@ -5282,7 +5272,7 @@
       <c r="O62" s="21"/>
     </row>
     <row r="63" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="26" t="s">
         <v>149</v>
       </c>
       <c r="B63" s="19" t="s">
@@ -5321,13 +5311,13 @@
       <c r="M63" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N63" s="22" t="s">
+      <c r="N63" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O63" s="21"/>
     </row>
     <row r="64" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="27"/>
+      <c r="A64" s="26"/>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
@@ -5335,7 +5325,7 @@
       <c r="F64" s="19"/>
       <c r="G64" s="19"/>
       <c r="H64" s="19"/>
-      <c r="I64" s="24" t="s">
+      <c r="I64" s="23" t="s">
         <v>159</v>
       </c>
       <c r="J64" s="21"/>
@@ -5346,7 +5336,7 @@
       <c r="O64" s="21"/>
     </row>
     <row r="65" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="27"/>
+      <c r="A65" s="26"/>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
@@ -5354,7 +5344,7 @@
       <c r="F65" s="19"/>
       <c r="G65" s="19"/>
       <c r="H65" s="19"/>
-      <c r="I65" s="24" t="s">
+      <c r="I65" s="23" t="s">
         <v>160</v>
       </c>
       <c r="J65" s="21"/>
@@ -5365,7 +5355,7 @@
       <c r="O65" s="21"/>
     </row>
     <row r="66" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="27"/>
+      <c r="A66" s="26"/>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
@@ -5396,13 +5386,13 @@
       <c r="M66" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N66" s="22" t="s">
+      <c r="N66" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O66" s="21"/>
     </row>
     <row r="67" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="27"/>
+      <c r="A67" s="26"/>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
@@ -5410,7 +5400,7 @@
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
-      <c r="I67" s="24" t="s">
+      <c r="I67" s="23" t="s">
         <v>165</v>
       </c>
       <c r="J67" s="21"/>
@@ -5421,7 +5411,7 @@
       <c r="O67" s="21"/>
     </row>
     <row r="68" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="27"/>
+      <c r="A68" s="26"/>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
@@ -5429,7 +5419,7 @@
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
       <c r="H68" s="19"/>
-      <c r="I68" s="24" t="s">
+      <c r="I68" s="23" t="s">
         <v>166</v>
       </c>
       <c r="J68" s="21"/>
@@ -5440,7 +5430,7 @@
       <c r="O68" s="21"/>
     </row>
     <row r="69" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="28" t="s">
+      <c r="A69" s="27" t="s">
         <v>167</v>
       </c>
       <c r="B69" s="19" t="s">
@@ -5479,13 +5469,13 @@
       <c r="M69" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N69" s="22" t="s">
+      <c r="N69" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="28"/>
+      <c r="A70" s="27"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
@@ -5504,7 +5494,7 @@
       <c r="O70" s="21"/>
     </row>
     <row r="71" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="28"/>
+      <c r="A71" s="27"/>
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
@@ -5523,7 +5513,7 @@
       <c r="O71" s="21"/>
     </row>
     <row r="72" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="28"/>
+      <c r="A72" s="27"/>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
@@ -5531,7 +5521,7 @@
       <c r="F72" s="18"/>
       <c r="G72" s="18"/>
       <c r="H72" s="18"/>
-      <c r="I72" s="24" t="s">
+      <c r="I72" s="23" t="s">
         <v>178</v>
       </c>
       <c r="J72" s="21"/>
@@ -5542,7 +5532,7 @@
       <c r="O72" s="21"/>
     </row>
     <row r="73" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="28"/>
+      <c r="A73" s="27"/>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
@@ -5550,7 +5540,7 @@
       <c r="F73" s="18"/>
       <c r="G73" s="18"/>
       <c r="H73" s="18"/>
-      <c r="I73" s="24" t="s">
+      <c r="I73" s="23" t="s">
         <v>179</v>
       </c>
       <c r="J73" s="21"/>
@@ -5561,7 +5551,7 @@
       <c r="O73" s="21"/>
     </row>
     <row r="74" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="28"/>
+      <c r="A74" s="27"/>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
@@ -5592,13 +5582,13 @@
       <c r="M74" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N74" s="22" t="s">
+      <c r="N74" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O74" s="21"/>
     </row>
     <row r="75" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="28"/>
+      <c r="A75" s="27"/>
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
@@ -5617,7 +5607,7 @@
       <c r="O75" s="21"/>
     </row>
     <row r="76" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="28"/>
+      <c r="A76" s="27"/>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
@@ -5636,7 +5626,7 @@
       <c r="O76" s="21"/>
     </row>
     <row r="77" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="28"/>
+      <c r="A77" s="27"/>
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
@@ -5655,7 +5645,7 @@
       <c r="O77" s="21"/>
     </row>
     <row r="78" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="28"/>
+      <c r="A78" s="27"/>
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
@@ -5663,7 +5653,7 @@
       <c r="F78" s="18"/>
       <c r="G78" s="18"/>
       <c r="H78" s="18"/>
-      <c r="I78" s="24" t="s">
+      <c r="I78" s="23" t="s">
         <v>189</v>
       </c>
       <c r="J78" s="21"/>
@@ -5673,8 +5663,8 @@
       <c r="N78" s="21"/>
       <c r="O78" s="21"/>
     </row>
-    <row r="79" s="29" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="28"/>
+    <row r="79" s="28" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="27"/>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
@@ -5690,7 +5680,7 @@
       <c r="H79" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="I79" s="24" t="s">
+      <c r="I79" s="23" t="s">
         <v>194</v>
       </c>
       <c r="J79" s="21" t="s">
@@ -5705,7 +5695,7 @@
       <c r="M79" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N79" s="22" t="s">
+      <c r="N79" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O79" s="21"/>
@@ -5713,7 +5703,7 @@
       <c r="XFD79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="28"/>
+      <c r="A80" s="27"/>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
@@ -5721,7 +5711,7 @@
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
       <c r="H80" s="17"/>
-      <c r="I80" s="24" t="s">
+      <c r="I80" s="23" t="s">
         <v>196</v>
       </c>
       <c r="J80" s="21"/>
@@ -5732,7 +5722,7 @@
       <c r="O80" s="21"/>
     </row>
     <row r="81" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="28"/>
+      <c r="A81" s="27"/>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
@@ -5740,7 +5730,7 @@
       <c r="F81" s="17"/>
       <c r="G81" s="17"/>
       <c r="H81" s="17"/>
-      <c r="I81" s="24" t="s">
+      <c r="I81" s="23" t="s">
         <v>197</v>
       </c>
       <c r="J81" s="21"/>
@@ -5751,7 +5741,7 @@
       <c r="O81" s="21"/>
     </row>
     <row r="82" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="28"/>
+      <c r="A82" s="27"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
@@ -5759,7 +5749,7 @@
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
       <c r="H82" s="17"/>
-      <c r="I82" s="24" t="s">
+      <c r="I82" s="23" t="s">
         <v>198</v>
       </c>
       <c r="J82" s="21"/>
@@ -5770,7 +5760,7 @@
       <c r="O82" s="21"/>
     </row>
     <row r="83" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="28"/>
+      <c r="A83" s="27"/>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
@@ -5778,7 +5768,7 @@
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
       <c r="H83" s="17"/>
-      <c r="I83" s="24" t="s">
+      <c r="I83" s="23" t="s">
         <v>199</v>
       </c>
       <c r="J83" s="21"/>
@@ -5789,7 +5779,7 @@
       <c r="O83" s="21"/>
     </row>
     <row r="84" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="28"/>
+      <c r="A84" s="27"/>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
@@ -5805,7 +5795,7 @@
       <c r="H84" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="I84" s="24" t="s">
+      <c r="I84" s="23" t="s">
         <v>203</v>
       </c>
       <c r="J84" s="21" t="s">
@@ -5820,13 +5810,13 @@
       <c r="M84" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="N84" s="22" t="s">
+      <c r="N84" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O84" s="21"/>
     </row>
     <row r="85" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="28"/>
+      <c r="A85" s="27"/>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
@@ -5834,7 +5824,7 @@
       <c r="F85" s="17"/>
       <c r="G85" s="17"/>
       <c r="H85" s="17"/>
-      <c r="I85" s="24" t="s">
+      <c r="I85" s="23" t="s">
         <v>204</v>
       </c>
       <c r="J85" s="21"/>
@@ -5845,7 +5835,7 @@
       <c r="O85" s="21"/>
     </row>
     <row r="86" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="28"/>
+      <c r="A86" s="27"/>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
@@ -5853,7 +5843,7 @@
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
       <c r="H86" s="17"/>
-      <c r="I86" s="24" t="s">
+      <c r="I86" s="23" t="s">
         <v>205</v>
       </c>
       <c r="J86" s="21"/>
@@ -5864,7 +5854,7 @@
       <c r="O86" s="21"/>
     </row>
     <row r="87" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="28"/>
+      <c r="A87" s="27"/>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
@@ -5872,7 +5862,7 @@
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
       <c r="H87" s="17"/>
-      <c r="I87" s="24" t="s">
+      <c r="I87" s="23" t="s">
         <v>206</v>
       </c>
       <c r="J87" s="21"/>
@@ -5883,7 +5873,7 @@
       <c r="O87" s="21"/>
     </row>
     <row r="88" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="28"/>
+      <c r="A88" s="27"/>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
@@ -5891,7 +5881,7 @@
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
       <c r="H88" s="17"/>
-      <c r="I88" s="24" t="s">
+      <c r="I88" s="23" t="s">
         <v>198</v>
       </c>
       <c r="J88" s="21"/>
@@ -5902,7 +5892,7 @@
       <c r="O88" s="21"/>
     </row>
     <row r="89" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="28"/>
+      <c r="A89" s="27"/>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
@@ -5918,7 +5908,7 @@
       <c r="H89" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="I89" s="24" t="s">
+      <c r="I89" s="23" t="s">
         <v>210</v>
       </c>
       <c r="J89" s="21" t="s">
@@ -5933,13 +5923,13 @@
       <c r="M89" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N89" s="22" t="s">
+      <c r="N89" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O89" s="21"/>
     </row>
     <row r="90" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="28"/>
+      <c r="A90" s="27"/>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
@@ -5947,7 +5937,7 @@
       <c r="F90" s="21"/>
       <c r="G90" s="21"/>
       <c r="H90" s="21"/>
-      <c r="I90" s="24" t="s">
+      <c r="I90" s="23" t="s">
         <v>212</v>
       </c>
       <c r="J90" s="21"/>
@@ -5958,7 +5948,7 @@
       <c r="O90" s="21"/>
     </row>
     <row r="91" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="28"/>
+      <c r="A91" s="27"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
@@ -5966,7 +5956,7 @@
       <c r="F91" s="21"/>
       <c r="G91" s="21"/>
       <c r="H91" s="21"/>
-      <c r="I91" s="24" t="s">
+      <c r="I91" s="23" t="s">
         <v>213</v>
       </c>
       <c r="J91" s="21"/>
@@ -5977,7 +5967,7 @@
       <c r="O91" s="21"/>
     </row>
     <row r="92" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="28"/>
+      <c r="A92" s="27"/>
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
@@ -5985,7 +5975,7 @@
       <c r="F92" s="21"/>
       <c r="G92" s="21"/>
       <c r="H92" s="21"/>
-      <c r="I92" s="24" t="s">
+      <c r="I92" s="23" t="s">
         <v>198</v>
       </c>
       <c r="J92" s="21"/>
@@ -5996,7 +5986,7 @@
       <c r="O92" s="21"/>
     </row>
     <row r="93" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="28"/>
+      <c r="A93" s="27"/>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
@@ -6004,7 +5994,7 @@
       <c r="F93" s="21"/>
       <c r="G93" s="21"/>
       <c r="H93" s="21"/>
-      <c r="I93" s="24" t="s">
+      <c r="I93" s="23" t="s">
         <v>214</v>
       </c>
       <c r="J93" s="21"/>
@@ -6015,7 +6005,7 @@
       <c r="O93" s="21"/>
     </row>
     <row r="94" customFormat="false" ht="35.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="28"/>
+      <c r="A94" s="27"/>
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
@@ -6031,7 +6021,7 @@
       <c r="H94" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="I94" s="24" t="s">
+      <c r="I94" s="23" t="s">
         <v>219</v>
       </c>
       <c r="J94" s="21" t="s">
@@ -6046,13 +6036,13 @@
       <c r="M94" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N94" s="22" t="s">
+      <c r="N94" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O94" s="30"/>
+      <c r="O94" s="29"/>
     </row>
     <row r="95" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="28"/>
+      <c r="A95" s="27"/>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
@@ -6060,7 +6050,7 @@
       <c r="F95" s="21"/>
       <c r="G95" s="21"/>
       <c r="H95" s="21"/>
-      <c r="I95" s="24" t="s">
+      <c r="I95" s="23" t="s">
         <v>220</v>
       </c>
       <c r="J95" s="21"/>
@@ -6071,7 +6061,7 @@
       <c r="O95" s="21"/>
     </row>
     <row r="96" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="28"/>
+      <c r="A96" s="27"/>
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
@@ -6079,7 +6069,7 @@
       <c r="F96" s="21"/>
       <c r="G96" s="21"/>
       <c r="H96" s="21"/>
-      <c r="I96" s="24" t="s">
+      <c r="I96" s="23" t="s">
         <v>221</v>
       </c>
       <c r="J96" s="21"/>
@@ -6090,7 +6080,7 @@
       <c r="O96" s="21"/>
     </row>
     <row r="97" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="28"/>
+      <c r="A97" s="27"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
@@ -6098,7 +6088,7 @@
       <c r="F97" s="21"/>
       <c r="G97" s="21"/>
       <c r="H97" s="21"/>
-      <c r="I97" s="24" t="s">
+      <c r="I97" s="23" t="s">
         <v>222</v>
       </c>
       <c r="J97" s="21"/>
@@ -6109,7 +6099,7 @@
       <c r="O97" s="21"/>
     </row>
     <row r="98" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="28"/>
+      <c r="A98" s="27"/>
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
@@ -6117,7 +6107,7 @@
       <c r="F98" s="21"/>
       <c r="G98" s="21"/>
       <c r="H98" s="21"/>
-      <c r="I98" s="24" t="s">
+      <c r="I98" s="23" t="s">
         <v>223</v>
       </c>
       <c r="J98" s="21"/>
@@ -6128,7 +6118,7 @@
       <c r="O98" s="21"/>
     </row>
     <row r="99" customFormat="false" ht="71.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="28"/>
+      <c r="A99" s="27"/>
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
@@ -6144,7 +6134,7 @@
       <c r="H99" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="I99" s="31" t="s">
+      <c r="I99" s="30" t="s">
         <v>227</v>
       </c>
       <c r="J99" s="21" t="s">
@@ -6159,13 +6149,13 @@
       <c r="M99" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N99" s="22" t="s">
+      <c r="N99" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O99" s="21"/>
     </row>
     <row r="100" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="28"/>
+      <c r="A100" s="27"/>
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
@@ -6173,7 +6163,7 @@
       <c r="F100" s="21"/>
       <c r="G100" s="21"/>
       <c r="H100" s="21"/>
-      <c r="I100" s="31" t="s">
+      <c r="I100" s="30" t="s">
         <v>228</v>
       </c>
       <c r="J100" s="21"/>
@@ -6184,7 +6174,7 @@
       <c r="O100" s="21"/>
     </row>
     <row r="101" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="28"/>
+      <c r="A101" s="27"/>
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
@@ -6192,7 +6182,7 @@
       <c r="F101" s="21"/>
       <c r="G101" s="21"/>
       <c r="H101" s="21"/>
-      <c r="I101" s="32" t="s">
+      <c r="I101" s="31" t="s">
         <v>229</v>
       </c>
       <c r="J101" s="21"/>
@@ -6203,7 +6193,7 @@
       <c r="O101" s="21"/>
     </row>
     <row r="102" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="28"/>
+      <c r="A102" s="27"/>
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
@@ -6211,7 +6201,7 @@
       <c r="F102" s="21"/>
       <c r="G102" s="21"/>
       <c r="H102" s="21"/>
-      <c r="I102" s="31" t="s">
+      <c r="I102" s="30" t="s">
         <v>230</v>
       </c>
       <c r="J102" s="21"/>
@@ -6222,7 +6212,7 @@
       <c r="O102" s="21"/>
     </row>
     <row r="103" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="28"/>
+      <c r="A103" s="27"/>
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
@@ -6230,7 +6220,7 @@
       <c r="F103" s="21"/>
       <c r="G103" s="21"/>
       <c r="H103" s="21"/>
-      <c r="I103" s="32" t="s">
+      <c r="I103" s="31" t="s">
         <v>231</v>
       </c>
       <c r="J103" s="21"/>
@@ -6241,7 +6231,7 @@
       <c r="O103" s="21"/>
     </row>
     <row r="104" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="33" t="s">
+      <c r="A104" s="32" t="s">
         <v>232</v>
       </c>
       <c r="B104" s="17" t="s">
@@ -6280,13 +6270,13 @@
       <c r="M104" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N104" s="22" t="s">
+      <c r="N104" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O104" s="21"/>
     </row>
     <row r="105" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="33"/>
+      <c r="A105" s="32"/>
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
@@ -6305,7 +6295,7 @@
       <c r="O105" s="21"/>
     </row>
     <row r="106" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="33"/>
+      <c r="A106" s="32"/>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
@@ -6324,7 +6314,7 @@
       <c r="O106" s="21"/>
     </row>
     <row r="107" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="33"/>
+      <c r="A107" s="32"/>
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
@@ -6343,7 +6333,7 @@
       <c r="O107" s="21"/>
     </row>
     <row r="108" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="33"/>
+      <c r="A108" s="32"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
@@ -6362,7 +6352,7 @@
       <c r="O108" s="21"/>
     </row>
     <row r="109" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="33"/>
+      <c r="A109" s="32"/>
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -6370,7 +6360,7 @@
       <c r="F109" s="19"/>
       <c r="G109" s="19"/>
       <c r="H109" s="20"/>
-      <c r="I109" s="24" t="s">
+      <c r="I109" s="23" t="s">
         <v>245</v>
       </c>
       <c r="J109" s="21"/>
@@ -6381,7 +6371,7 @@
       <c r="O109" s="21"/>
     </row>
     <row r="110" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="33"/>
+      <c r="A110" s="32"/>
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
       <c r="D110" s="17"/>
@@ -6400,7 +6390,7 @@
       <c r="O110" s="21"/>
     </row>
     <row r="111" customFormat="false" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="33"/>
+      <c r="A111" s="32"/>
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
@@ -6431,13 +6421,13 @@
       <c r="M111" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N111" s="22" t="s">
+      <c r="N111" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O111" s="21"/>
     </row>
     <row r="112" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="33"/>
+      <c r="A112" s="32"/>
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
       <c r="D112" s="17"/>
@@ -6456,7 +6446,7 @@
       <c r="O112" s="21"/>
     </row>
     <row r="113" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="33"/>
+      <c r="A113" s="32"/>
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
       <c r="D113" s="17"/>
@@ -6475,7 +6465,7 @@
       <c r="O113" s="21"/>
     </row>
     <row r="114" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="33"/>
+      <c r="A114" s="32"/>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
       <c r="D114" s="17"/>
@@ -6494,7 +6484,7 @@
       <c r="O114" s="21"/>
     </row>
     <row r="115" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="33"/>
+      <c r="A115" s="32"/>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
@@ -6513,7 +6503,7 @@
       <c r="O115" s="21"/>
     </row>
     <row r="116" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="33"/>
+      <c r="A116" s="32"/>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
@@ -6521,7 +6511,7 @@
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
       <c r="H116" s="17"/>
-      <c r="I116" s="24" t="s">
+      <c r="I116" s="23" t="s">
         <v>256</v>
       </c>
       <c r="J116" s="21"/>
@@ -6532,7 +6522,7 @@
       <c r="O116" s="21"/>
     </row>
     <row r="117" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="33"/>
+      <c r="A117" s="32"/>
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
       <c r="D117" s="17"/>
@@ -6551,7 +6541,7 @@
       <c r="O117" s="21"/>
     </row>
     <row r="118" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="33"/>
+      <c r="A118" s="32"/>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
       <c r="D118" s="17"/>
@@ -6582,13 +6572,13 @@
       <c r="M118" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N118" s="22" t="s">
+      <c r="N118" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O118" s="21"/>
     </row>
     <row r="119" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="33"/>
+      <c r="A119" s="32"/>
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
       <c r="D119" s="17"/>
@@ -6607,7 +6597,7 @@
       <c r="O119" s="21"/>
     </row>
     <row r="120" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="33"/>
+      <c r="A120" s="32"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
@@ -6626,7 +6616,7 @@
       <c r="O120" s="21"/>
     </row>
     <row r="121" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="33"/>
+      <c r="A121" s="32"/>
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
       <c r="D121" s="17"/>
@@ -6645,7 +6635,7 @@
       <c r="O121" s="21"/>
     </row>
     <row r="122" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="33"/>
+      <c r="A122" s="32"/>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
       <c r="D122" s="17"/>
@@ -6664,7 +6654,7 @@
       <c r="O122" s="21"/>
     </row>
     <row r="123" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="33"/>
+      <c r="A123" s="32"/>
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
       <c r="D123" s="17"/>
@@ -6683,7 +6673,7 @@
       <c r="O123" s="21"/>
     </row>
     <row r="124" customFormat="false" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="33"/>
+      <c r="A124" s="32"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
       <c r="D124" s="17"/>
@@ -6714,13 +6704,13 @@
       <c r="M124" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="N124" s="22" t="s">
+      <c r="N124" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O124" s="21"/>
     </row>
     <row r="125" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="33"/>
+      <c r="A125" s="32"/>
       <c r="B125" s="17"/>
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
@@ -6739,7 +6729,7 @@
       <c r="O125" s="21"/>
     </row>
     <row r="126" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="33"/>
+      <c r="A126" s="32"/>
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
       <c r="D126" s="17"/>
@@ -6747,7 +6737,7 @@
       <c r="F126" s="19"/>
       <c r="G126" s="19"/>
       <c r="H126" s="19"/>
-      <c r="I126" s="24" t="s">
+      <c r="I126" s="23" t="s">
         <v>271</v>
       </c>
       <c r="J126" s="21"/>
@@ -6758,7 +6748,7 @@
       <c r="O126" s="21"/>
     </row>
     <row r="127" customFormat="false" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="33"/>
+      <c r="A127" s="32"/>
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
       <c r="D127" s="17"/>
@@ -6776,8 +6766,8 @@
       <c r="N127" s="21"/>
       <c r="O127" s="21"/>
     </row>
-    <row r="128" s="35" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="34" t="s">
+    <row r="128" s="34" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="33" t="s">
         <v>273</v>
       </c>
       <c r="B128" s="17" t="s">
@@ -6816,15 +6806,15 @@
       <c r="M128" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N128" s="22" t="s">
+      <c r="N128" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O128" s="21"/>
       <c r="XFC128" s="3"/>
       <c r="XFD128" s="1"/>
     </row>
-    <row r="129" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="34"/>
+    <row r="129" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="33"/>
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
       <c r="D129" s="17"/>
@@ -6844,8 +6834,8 @@
       <c r="XFC129" s="3"/>
       <c r="XFD129" s="1"/>
     </row>
-    <row r="130" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="34"/>
+    <row r="130" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="33"/>
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
       <c r="D130" s="17"/>
@@ -6865,8 +6855,8 @@
       <c r="XFC130" s="3"/>
       <c r="XFD130" s="1"/>
     </row>
-    <row r="131" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="34"/>
+    <row r="131" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="33"/>
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
       <c r="D131" s="17"/>
@@ -6886,8 +6876,8 @@
       <c r="XFC131" s="3"/>
       <c r="XFD131" s="1"/>
     </row>
-    <row r="132" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="34"/>
+    <row r="132" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="33"/>
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
@@ -6907,8 +6897,8 @@
       <c r="XFC132" s="3"/>
       <c r="XFD132" s="1"/>
     </row>
-    <row r="133" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="34"/>
+    <row r="133" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="33"/>
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
@@ -6928,8 +6918,8 @@
       <c r="XFC133" s="3"/>
       <c r="XFD133" s="1"/>
     </row>
-    <row r="134" s="36" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="34"/>
+    <row r="134" s="35" customFormat="true" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="33"/>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
@@ -6960,15 +6950,15 @@
       <c r="M134" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="N134" s="22" t="s">
+      <c r="N134" s="21" t="s">
         <v>45</v>
       </c>
       <c r="O134" s="21"/>
       <c r="XFC134" s="3"/>
       <c r="XFD134" s="1"/>
     </row>
-    <row r="135" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="34"/>
+    <row r="135" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="33"/>
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
       <c r="D135" s="17"/>
@@ -6988,8 +6978,8 @@
       <c r="XFC135" s="3"/>
       <c r="XFD135" s="1"/>
     </row>
-    <row r="136" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="34"/>
+    <row r="136" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="33"/>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
       <c r="D136" s="17"/>
@@ -7009,8 +6999,8 @@
       <c r="XFC136" s="3"/>
       <c r="XFD136" s="1"/>
     </row>
-    <row r="137" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="34"/>
+    <row r="137" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="33"/>
       <c r="B137" s="17"/>
       <c r="C137" s="17"/>
       <c r="D137" s="17"/>
@@ -7030,8 +7020,8 @@
       <c r="XFC137" s="3"/>
       <c r="XFD137" s="1"/>
     </row>
-    <row r="138" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="34"/>
+    <row r="138" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="33"/>
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
       <c r="D138" s="17"/>
@@ -7051,8 +7041,8 @@
       <c r="XFC138" s="3"/>
       <c r="XFD138" s="1"/>
     </row>
-    <row r="139" s="36" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="34"/>
+    <row r="139" s="35" customFormat="true" ht="99.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="33"/>
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
@@ -7458,13 +7448,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="71.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
@@ -7484,71 +7474,71 @@
       <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="50.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
@@ -7559,56 +7549,56 @@
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="38"/>
+      <c r="E12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="39" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="40" t="s">
         <v>303</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="40" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="64.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="62.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>306</v>
       </c>
@@ -7618,16 +7608,16 @@
       <c r="C17" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="23" t="s">
         <v>312</v>
       </c>
     </row>
@@ -7641,16 +7631,16 @@
       <c r="C18" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="23" t="s">
         <v>318</v>
       </c>
     </row>
@@ -7664,16 +7654,16 @@
       <c r="C19" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="23" t="s">
         <v>324</v>
       </c>
     </row>
@@ -7687,16 +7677,16 @@
       <c r="C20" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="23" t="s">
         <v>330</v>
       </c>
     </row>
@@ -7710,16 +7700,16 @@
       <c r="C21" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="23" t="s">
         <v>336</v>
       </c>
     </row>
@@ -7733,16 +7723,16 @@
       <c r="C22" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="23" t="s">
         <v>342</v>
       </c>
     </row>
@@ -7756,16 +7746,16 @@
       <c r="C23" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="23" t="s">
         <v>348</v>
       </c>
     </row>
@@ -7779,16 +7769,16 @@
       <c r="C24" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="23" t="s">
         <v>354</v>
       </c>
     </row>
@@ -7802,16 +7792,16 @@
       <c r="C25" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="23" t="s">
         <v>358</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="G25" s="24" t="s">
+      <c r="G25" s="23" t="s">
         <v>361</v>
       </c>
     </row>
@@ -7849,236 +7839,236 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="42" width="29.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="42" width="49.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="42" width="18.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="5" style="42" width="8.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="42" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="41" width="29.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="41" width="49.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="41" width="18.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="5" style="41" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="41" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+      <c r="A1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
     </row>
     <row r="2" s="3" customFormat="true" ht="68.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="43"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="5.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44"/>
-      <c r="D3" s="43"/>
+      <c r="A3" s="43"/>
+      <c r="D3" s="42"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="52.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="43"/>
+      <c r="D4" s="42"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="43"/>
+      <c r="D5" s="42"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="44" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="43"/>
+      <c r="D6" s="42"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="43"/>
+      <c r="D7" s="42"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="44" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="43"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="43"/>
+      <c r="D9" s="42"/>
     </row>
     <row r="10" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="43"/>
+      <c r="D10" s="42"/>
     </row>
     <row r="11" s="3" customFormat="true" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="44" t="s">
         <v>363</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="43"/>
+      <c r="D11" s="42"/>
     </row>
     <row r="12" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="44" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="43"/>
+      <c r="D12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
+      <c r="A13" s="45"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="47" t="s">
         <v>364</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="41" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="48" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="49" t="s">
         <v>369</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="50" t="s">
         <v>370</v>
       </c>
-      <c r="C17" s="52" t="n">
+      <c r="C17" s="51" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="50" t="s">
         <v>372</v>
       </c>
-      <c r="C18" s="53" t="n">
+      <c r="C18" s="52" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="49" t="s">
         <v>373</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
         <v>374</v>
       </c>
-      <c r="C19" s="53" t="n">
+      <c r="C19" s="52" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="49" t="s">
         <v>375</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="50" t="s">
         <v>376</v>
       </c>
-      <c r="C20" s="52" t="n">
+      <c r="C20" s="51" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="49" t="s">
         <v>377</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="50" t="s">
         <v>378</v>
       </c>
-      <c r="C21" s="52" t="n">
+      <c r="C21" s="51" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="50" t="s">
         <v>380</v>
       </c>
-      <c r="C22" s="52" t="n">
+      <c r="C22" s="51" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="49" t="s">
         <v>381</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="50" t="s">
         <v>382</v>
       </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="51" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="53" t="s">
         <v>383</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="53" t="s">
         <v>384</v>
       </c>
-      <c r="C24" s="55" t="n">
+      <c r="C24" s="54" t="n">
         <f aca="false">SUM(C17:C23)</f>
         <v>139</v>
       </c>
